--- a/data/KTTX_TIN12.xlsx
+++ b/data/KTTX_TIN12.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tdtam\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WEBH2T\GITHUB 2026\KIEM TRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01EED341-A0B6-43BD-8DEA-0BD553C6CD6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF038625-F681-4B55-8CA7-88D6F13B90E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HUONG_DAN" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1713" uniqueCount="716">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1714" uniqueCount="717">
   <si>
     <t>Mục</t>
   </si>
@@ -2186,6 +2186,9 @@
   </si>
   <si>
     <t>Q0429</t>
+  </si>
+  <si>
+    <t>8/10/2026</t>
   </si>
 </sst>
 </file>
@@ -2263,7 +2266,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2272,7 +2275,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2287,7 +2289,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2730,31 +2740,31 @@
       <c r="A2" s="3" t="s">
         <v>570</v>
       </c>
-      <c r="B2" s="7">
-        <v>1</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" s="7" t="s">
+      <c r="B2" s="6">
+        <v>1</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="I2" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J2" s="7" t="s">
+      <c r="I2" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -2762,31 +2772,31 @@
       <c r="A3" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="B3" s="7">
-        <v>1</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" s="7" t="s">
+      <c r="B3" s="6">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="6" t="s">
         <v>321</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -2794,31 +2804,31 @@
       <c r="A4" s="3" t="s">
         <v>572</v>
       </c>
-      <c r="B4" s="7">
-        <v>1</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="7" t="s">
+      <c r="B4" s="6">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="I4" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J4" s="7" t="s">
+      <c r="I4" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -2826,31 +2836,31 @@
       <c r="A5" s="3" t="s">
         <v>573</v>
       </c>
-      <c r="B5" s="7">
-        <v>1</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" s="7" t="s">
+      <c r="B5" s="6">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="6" t="s">
         <v>325</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="I5" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" s="7" t="s">
+      <c r="I5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -2858,31 +2868,31 @@
       <c r="A6" s="3" t="s">
         <v>574</v>
       </c>
-      <c r="B6" s="7">
-        <v>1</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" s="7" t="s">
+      <c r="B6" s="6">
+        <v>1</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="6" t="s">
         <v>332</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="I6" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6" s="7" t="s">
+      <c r="I6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -2890,31 +2900,31 @@
       <c r="A7" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="B7" s="7">
-        <v>1</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="7" t="s">
+      <c r="B7" s="6">
+        <v>1</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="6" t="s">
         <v>337</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="I7" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J7" s="7" t="s">
+      <c r="I7" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -2922,31 +2932,31 @@
       <c r="A8" s="3" t="s">
         <v>576</v>
       </c>
-      <c r="B8" s="7">
-        <v>1</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="7" t="s">
+      <c r="B8" s="6">
+        <v>1</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="I8" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J8" s="7" t="s">
+      <c r="I8" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -2954,31 +2964,31 @@
       <c r="A9" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="B9" s="7">
-        <v>1</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" s="7" t="s">
+      <c r="B9" s="6">
+        <v>1</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="6" t="s">
         <v>345</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="6" t="s">
         <v>348</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="I9" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="J9" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -2986,31 +2996,31 @@
       <c r="A10" s="3" t="s">
         <v>578</v>
       </c>
-      <c r="B10" s="7">
-        <v>1</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" s="7" t="s">
+      <c r="B10" s="6">
+        <v>1</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="6" t="s">
         <v>352</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="I10" s="7" t="s">
+      <c r="I10" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J10" s="7" t="s">
+      <c r="J10" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -3018,31 +3028,31 @@
       <c r="A11" s="3" t="s">
         <v>579</v>
       </c>
-      <c r="B11" s="7">
-        <v>1</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="7" t="s">
+      <c r="B11" s="6">
+        <v>1</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="H11" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="I11" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J11" s="7" t="s">
+      <c r="I11" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J11" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -3050,31 +3060,31 @@
       <c r="A12" s="3" t="s">
         <v>580</v>
       </c>
-      <c r="B12" s="7">
-        <v>1</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" s="7" t="s">
+      <c r="B12" s="6">
+        <v>1</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>355</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="6" t="s">
         <v>356</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="6" t="s">
         <v>358</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="6" t="s">
         <v>359</v>
       </c>
-      <c r="I12" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J12" s="7" t="s">
+      <c r="I12" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J12" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -3082,31 +3092,31 @@
       <c r="A13" s="3" t="s">
         <v>581</v>
       </c>
-      <c r="B13" s="7">
-        <v>1</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" s="7" t="s">
+      <c r="B13" s="6">
+        <v>1</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="6" t="s">
         <v>360</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="6" t="s">
         <v>362</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="H13" s="7" t="s">
+      <c r="H13" s="6" t="s">
         <v>364</v>
       </c>
-      <c r="I13" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J13" s="7" t="s">
+      <c r="I13" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J13" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -3114,31 +3124,31 @@
       <c r="A14" s="3" t="s">
         <v>582</v>
       </c>
-      <c r="B14" s="7">
-        <v>1</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" s="7" t="s">
+      <c r="B14" s="6">
+        <v>1</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="G14" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="H14" s="7" t="s">
+      <c r="H14" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="I14" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J14" s="7" t="s">
+      <c r="I14" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J14" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -3146,31 +3156,31 @@
       <c r="A15" s="3" t="s">
         <v>583</v>
       </c>
-      <c r="B15" s="7">
-        <v>1</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15" s="7" t="s">
+      <c r="B15" s="6">
+        <v>1</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="G15" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="H15" s="7" t="s">
+      <c r="H15" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="I15" s="7" t="s">
+      <c r="I15" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J15" s="7" t="s">
+      <c r="J15" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -3178,31 +3188,31 @@
       <c r="A16" s="3" t="s">
         <v>584</v>
       </c>
-      <c r="B16" s="7">
-        <v>1</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" s="7" t="s">
+      <c r="B16" s="6">
+        <v>1</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="G16" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="H16" s="7" t="s">
+      <c r="H16" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="I16" s="7" t="s">
+      <c r="I16" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J16" s="7" t="s">
+      <c r="J16" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -3210,31 +3220,31 @@
       <c r="A17" s="3" t="s">
         <v>585</v>
       </c>
-      <c r="B17" s="7">
-        <v>1</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D17" s="7" t="s">
+      <c r="B17" s="6">
+        <v>1</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="G17" s="7" t="s">
+      <c r="G17" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="H17" s="7" t="s">
+      <c r="H17" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="I17" s="7" t="s">
+      <c r="I17" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J17" s="7" t="s">
+      <c r="J17" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -3242,31 +3252,31 @@
       <c r="A18" s="3" t="s">
         <v>586</v>
       </c>
-      <c r="B18" s="7">
-        <v>1</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D18" s="7" t="s">
+      <c r="B18" s="6">
+        <v>1</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="G18" s="7" t="s">
+      <c r="G18" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="H18" s="7" t="s">
+      <c r="H18" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="I18" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J18" s="7" t="s">
+      <c r="I18" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J18" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -3274,31 +3284,31 @@
       <c r="A19" s="3" t="s">
         <v>587</v>
       </c>
-      <c r="B19" s="7">
-        <v>1</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D19" s="7" t="s">
+      <c r="B19" s="6">
+        <v>1</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="G19" s="7" t="s">
+      <c r="G19" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="H19" s="7" t="s">
+      <c r="H19" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="I19" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J19" s="7" t="s">
+      <c r="I19" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J19" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -3306,31 +3316,31 @@
       <c r="A20" s="3" t="s">
         <v>588</v>
       </c>
-      <c r="B20" s="7">
-        <v>1</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D20" s="7" t="s">
+      <c r="B20" s="6">
+        <v>1</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F20" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="G20" s="7" t="s">
+      <c r="G20" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="H20" s="7" t="s">
+      <c r="H20" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="I20" s="7" t="s">
+      <c r="I20" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J20" s="7" t="s">
+      <c r="J20" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -3338,31 +3348,31 @@
       <c r="A21" s="3" t="s">
         <v>589</v>
       </c>
-      <c r="B21" s="7">
-        <v>1</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D21" s="7" t="s">
+      <c r="B21" s="6">
+        <v>1</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="F21" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="G21" s="7" t="s">
+      <c r="G21" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="H21" s="7" t="s">
+      <c r="H21" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="I21" s="7" t="s">
+      <c r="I21" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J21" s="7" t="s">
+      <c r="J21" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -3370,31 +3380,31 @@
       <c r="A22" s="3" t="s">
         <v>590</v>
       </c>
-      <c r="B22" s="7">
-        <v>1</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22" s="7" t="s">
+      <c r="B22" s="6">
+        <v>1</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E22" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="F22" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="G22" s="7" t="s">
+      <c r="G22" s="6" t="s">
         <v>285</v>
       </c>
-      <c r="H22" s="7" t="s">
+      <c r="H22" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="I22" s="7" t="s">
+      <c r="I22" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J22" s="7" t="s">
+      <c r="J22" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -3402,31 +3412,31 @@
       <c r="A23" s="3" t="s">
         <v>591</v>
       </c>
-      <c r="B23" s="7">
-        <v>1</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D23" s="7" t="s">
+      <c r="B23" s="6">
+        <v>1</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="E23" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="F23" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="G23" s="7" t="s">
+      <c r="G23" s="6" t="s">
         <v>290</v>
       </c>
-      <c r="H23" s="7" t="s">
+      <c r="H23" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="I23" s="7" t="s">
+      <c r="I23" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J23" s="7" t="s">
+      <c r="J23" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -3434,31 +3444,31 @@
       <c r="A24" s="3" t="s">
         <v>592</v>
       </c>
-      <c r="B24" s="7">
-        <v>1</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D24" s="7" t="s">
+      <c r="B24" s="6">
+        <v>1</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D24" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E24" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="F24" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="G24" s="7" t="s">
+      <c r="G24" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="H24" s="7" t="s">
+      <c r="H24" s="6" t="s">
         <v>296</v>
       </c>
-      <c r="I24" s="7" t="s">
+      <c r="I24" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J24" s="7" t="s">
+      <c r="J24" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -3466,31 +3476,31 @@
       <c r="A25" s="3" t="s">
         <v>593</v>
       </c>
-      <c r="B25" s="7">
-        <v>1</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D25" s="7" t="s">
+      <c r="B25" s="6">
+        <v>1</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D25" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="E25" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="F25" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="G25" s="7" t="s">
+      <c r="G25" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="H25" s="7" t="s">
+      <c r="H25" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="I25" s="7" t="s">
+      <c r="I25" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J25" s="7" t="s">
+      <c r="J25" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -3498,31 +3508,31 @@
       <c r="A26" s="3" t="s">
         <v>594</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="6">
         <v>2</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D26" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="E26" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="F26" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="G26" s="7" t="s">
+      <c r="G26" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="H26" s="7" t="s">
+      <c r="H26" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="I26" s="7" t="s">
+      <c r="I26" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="J26" s="8">
+      <c r="J26" s="7">
         <v>1</v>
       </c>
     </row>
@@ -3530,31 +3540,31 @@
       <c r="A27" s="3" t="s">
         <v>595</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="6">
         <v>2</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D27" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="E27" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="F27" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="G27" s="7" t="s">
+      <c r="G27" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="H27" s="7" t="s">
+      <c r="H27" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="I27" s="7" t="s">
+      <c r="I27" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="J27" s="8">
+      <c r="J27" s="7">
         <v>1</v>
       </c>
     </row>
@@ -3562,31 +3572,31 @@
       <c r="A28" s="3" t="s">
         <v>596</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B28" s="6">
         <v>2</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="D28" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="E28" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="F28" s="7" t="s">
+      <c r="F28" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="G28" s="7" t="s">
+      <c r="G28" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="H28" s="7" t="s">
+      <c r="H28" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="I28" s="7" t="s">
+      <c r="I28" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="J28" s="8">
+      <c r="J28" s="7">
         <v>1</v>
       </c>
     </row>
@@ -3594,23 +3604,23 @@
       <c r="A29" s="3" t="s">
         <v>597</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B29" s="6">
         <v>3</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7" t="s">
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="J29" s="7" t="s">
+      <c r="J29" s="6" t="s">
         <v>566</v>
       </c>
     </row>
@@ -3618,23 +3628,23 @@
       <c r="A30" s="3" t="s">
         <v>598</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B30" s="6">
         <v>3</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C30" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="D30" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
-      <c r="I30" s="7" t="s">
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="J30" s="7" t="s">
+      <c r="J30" s="6" t="s">
         <v>566</v>
       </c>
     </row>
@@ -3642,31 +3652,31 @@
       <c r="A31" s="3" t="s">
         <v>599</v>
       </c>
-      <c r="B31" s="7">
-        <v>1</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D31" s="7" t="s">
+      <c r="B31" s="6">
+        <v>1</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D31" s="6" t="s">
         <v>379</v>
       </c>
-      <c r="E31" s="7" t="s">
+      <c r="E31" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="F31" s="7" t="s">
+      <c r="F31" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="G31" s="7" t="s">
+      <c r="G31" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="H31" s="7" t="s">
+      <c r="H31" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="I31" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J31" s="7" t="s">
+      <c r="I31" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J31" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -3674,31 +3684,31 @@
       <c r="A32" s="3" t="s">
         <v>600</v>
       </c>
-      <c r="B32" s="7">
-        <v>1</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D32" s="7" t="s">
+      <c r="B32" s="6">
+        <v>1</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D32" s="6" t="s">
         <v>380</v>
       </c>
-      <c r="E32" s="7" t="s">
+      <c r="E32" s="6" t="s">
         <v>381</v>
       </c>
-      <c r="F32" s="7" t="s">
+      <c r="F32" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="G32" s="7" t="s">
+      <c r="G32" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="H32" s="7" t="s">
+      <c r="H32" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="I32" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J32" s="7" t="s">
+      <c r="I32" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J32" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -3706,31 +3716,31 @@
       <c r="A33" s="3" t="s">
         <v>601</v>
       </c>
-      <c r="B33" s="7">
-        <v>1</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D33" s="7" t="s">
+      <c r="B33" s="6">
+        <v>1</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D33" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="E33" s="7" t="s">
+      <c r="E33" s="6" t="s">
         <v>383</v>
       </c>
-      <c r="F33" s="7" t="s">
+      <c r="F33" s="6" t="s">
         <v>384</v>
       </c>
-      <c r="G33" s="7" t="s">
+      <c r="G33" s="6" t="s">
         <v>385</v>
       </c>
-      <c r="H33" s="7" t="s">
+      <c r="H33" s="6" t="s">
         <v>386</v>
       </c>
-      <c r="I33" s="7" t="s">
+      <c r="I33" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J33" s="7" t="s">
+      <c r="J33" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -3738,31 +3748,31 @@
       <c r="A34" s="3" t="s">
         <v>602</v>
       </c>
-      <c r="B34" s="7">
-        <v>1</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D34" s="7" t="s">
+      <c r="B34" s="6">
+        <v>1</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D34" s="6" t="s">
         <v>387</v>
       </c>
-      <c r="E34" s="7" t="s">
+      <c r="E34" s="6" t="s">
         <v>388</v>
       </c>
-      <c r="F34" s="7" t="s">
+      <c r="F34" s="6" t="s">
         <v>389</v>
       </c>
-      <c r="G34" s="7" t="s">
+      <c r="G34" s="6" t="s">
         <v>390</v>
       </c>
-      <c r="H34" s="7" t="s">
+      <c r="H34" s="6" t="s">
         <v>391</v>
       </c>
-      <c r="I34" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J34" s="7" t="s">
+      <c r="I34" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J34" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -3770,31 +3780,31 @@
       <c r="A35" s="3" t="s">
         <v>603</v>
       </c>
-      <c r="B35" s="7">
-        <v>1</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D35" s="7" t="s">
+      <c r="B35" s="6">
+        <v>1</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D35" s="6" t="s">
         <v>392</v>
       </c>
-      <c r="E35" s="7" t="s">
+      <c r="E35" s="6" t="s">
         <v>393</v>
       </c>
-      <c r="F35" s="7" t="s">
+      <c r="F35" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="G35" s="7" t="s">
+      <c r="G35" s="6" t="s">
         <v>395</v>
       </c>
-      <c r="H35" s="7" t="s">
+      <c r="H35" s="6" t="s">
         <v>396</v>
       </c>
-      <c r="I35" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J35" s="7" t="s">
+      <c r="I35" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J35" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -3802,31 +3812,31 @@
       <c r="A36" s="3" t="s">
         <v>604</v>
       </c>
-      <c r="B36" s="7">
-        <v>1</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D36" s="7" t="s">
+      <c r="B36" s="6">
+        <v>1</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D36" s="6" t="s">
         <v>397</v>
       </c>
-      <c r="E36" s="7" t="s">
+      <c r="E36" s="6" t="s">
         <v>398</v>
       </c>
-      <c r="F36" s="7" t="s">
+      <c r="F36" s="6" t="s">
         <v>399</v>
       </c>
-      <c r="G36" s="7" t="s">
+      <c r="G36" s="6" t="s">
         <v>400</v>
       </c>
-      <c r="H36" s="7" t="s">
+      <c r="H36" s="6" t="s">
         <v>401</v>
       </c>
-      <c r="I36" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J36" s="7" t="s">
+      <c r="I36" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J36" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -3834,31 +3844,31 @@
       <c r="A37" s="3" t="s">
         <v>605</v>
       </c>
-      <c r="B37" s="7">
-        <v>1</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D37" s="7" t="s">
+      <c r="B37" s="6">
+        <v>1</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D37" s="6" t="s">
         <v>402</v>
       </c>
-      <c r="E37" s="7" t="s">
+      <c r="E37" s="6" t="s">
         <v>403</v>
       </c>
-      <c r="F37" s="7" t="s">
+      <c r="F37" s="6" t="s">
         <v>404</v>
       </c>
-      <c r="G37" s="7" t="s">
+      <c r="G37" s="6" t="s">
         <v>405</v>
       </c>
-      <c r="H37" s="7" t="s">
+      <c r="H37" s="6" t="s">
         <v>406</v>
       </c>
-      <c r="I37" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J37" s="7" t="s">
+      <c r="I37" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J37" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -3866,31 +3876,31 @@
       <c r="A38" s="3" t="s">
         <v>606</v>
       </c>
-      <c r="B38" s="7">
-        <v>1</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D38" s="7" t="s">
+      <c r="B38" s="6">
+        <v>1</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D38" s="6" t="s">
         <v>407</v>
       </c>
-      <c r="E38" s="7" t="s">
+      <c r="E38" s="6" t="s">
         <v>408</v>
       </c>
-      <c r="F38" s="7" t="s">
+      <c r="F38" s="6" t="s">
         <v>409</v>
       </c>
-      <c r="G38" s="7" t="s">
+      <c r="G38" s="6" t="s">
         <v>410</v>
       </c>
-      <c r="H38" s="7" t="s">
+      <c r="H38" s="6" t="s">
         <v>411</v>
       </c>
-      <c r="I38" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J38" s="7" t="s">
+      <c r="I38" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J38" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -3898,31 +3908,31 @@
       <c r="A39" s="3" t="s">
         <v>607</v>
       </c>
-      <c r="B39" s="7">
-        <v>1</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D39" s="7" t="s">
+      <c r="B39" s="6">
+        <v>1</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D39" s="6" t="s">
         <v>412</v>
       </c>
-      <c r="E39" s="7" t="s">
+      <c r="E39" s="6" t="s">
         <v>413</v>
       </c>
-      <c r="F39" s="7" t="s">
+      <c r="F39" s="6" t="s">
         <v>414</v>
       </c>
-      <c r="G39" s="7" t="s">
+      <c r="G39" s="6" t="s">
         <v>415</v>
       </c>
-      <c r="H39" s="7" t="s">
+      <c r="H39" s="6" t="s">
         <v>416</v>
       </c>
-      <c r="I39" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J39" s="7" t="s">
+      <c r="I39" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J39" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -3930,31 +3940,31 @@
       <c r="A40" s="3" t="s">
         <v>608</v>
       </c>
-      <c r="B40" s="7">
-        <v>1</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D40" s="7" t="s">
+      <c r="B40" s="6">
+        <v>1</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D40" s="6" t="s">
         <v>417</v>
       </c>
-      <c r="E40" s="7" t="s">
+      <c r="E40" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="F40" s="7" t="s">
+      <c r="F40" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="G40" s="7" t="s">
+      <c r="G40" s="6" t="s">
         <v>352</v>
       </c>
-      <c r="H40" s="7" t="s">
+      <c r="H40" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="I40" s="7" t="s">
+      <c r="I40" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J40" s="7" t="s">
+      <c r="J40" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -3962,31 +3972,31 @@
       <c r="A41" s="3" t="s">
         <v>609</v>
       </c>
-      <c r="B41" s="7">
-        <v>1</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D41" s="7" t="s">
+      <c r="B41" s="6">
+        <v>1</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D41" s="6" t="s">
         <v>418</v>
       </c>
-      <c r="E41" s="7" t="s">
+      <c r="E41" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="F41" s="7" t="s">
+      <c r="F41" s="6" t="s">
         <v>419</v>
       </c>
-      <c r="G41" s="7" t="s">
+      <c r="G41" s="6" t="s">
         <v>420</v>
       </c>
-      <c r="H41" s="7" t="s">
+      <c r="H41" s="6" t="s">
         <v>421</v>
       </c>
-      <c r="I41" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J41" s="7" t="s">
+      <c r="I41" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J41" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -3994,31 +4004,31 @@
       <c r="A42" s="3" t="s">
         <v>610</v>
       </c>
-      <c r="B42" s="7">
-        <v>1</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D42" s="7" t="s">
+      <c r="B42" s="6">
+        <v>1</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D42" s="6" t="s">
         <v>422</v>
       </c>
-      <c r="E42" s="7" t="s">
+      <c r="E42" s="6" t="s">
         <v>423</v>
       </c>
-      <c r="F42" s="7" t="s">
+      <c r="F42" s="6" t="s">
         <v>424</v>
       </c>
-      <c r="G42" s="7" t="s">
+      <c r="G42" s="6" t="s">
         <v>425</v>
       </c>
-      <c r="H42" s="7" t="s">
+      <c r="H42" s="6" t="s">
         <v>426</v>
       </c>
-      <c r="I42" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J42" s="7" t="s">
+      <c r="I42" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J42" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -4026,31 +4036,31 @@
       <c r="A43" s="3" t="s">
         <v>611</v>
       </c>
-      <c r="B43" s="7">
-        <v>1</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D43" s="7" t="s">
+      <c r="B43" s="6">
+        <v>1</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D43" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="E43" s="7" t="s">
+      <c r="E43" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="F43" s="7" t="s">
+      <c r="F43" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="G43" s="7" t="s">
+      <c r="G43" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="H43" s="7" t="s">
+      <c r="H43" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="I43" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J43" s="7" t="s">
+      <c r="I43" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J43" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -4058,31 +4068,31 @@
       <c r="A44" s="3" t="s">
         <v>612</v>
       </c>
-      <c r="B44" s="7">
-        <v>1</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D44" s="7" t="s">
+      <c r="B44" s="6">
+        <v>1</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D44" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="E44" s="7" t="s">
+      <c r="E44" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="F44" s="7" t="s">
+      <c r="F44" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="G44" s="7" t="s">
+      <c r="G44" s="6" t="s">
         <v>321</v>
       </c>
-      <c r="H44" s="7" t="s">
+      <c r="H44" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="I44" s="7" t="s">
+      <c r="I44" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J44" s="7" t="s">
+      <c r="J44" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -4090,31 +4100,31 @@
       <c r="A45" s="3" t="s">
         <v>613</v>
       </c>
-      <c r="B45" s="7">
-        <v>1</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D45" s="7" t="s">
+      <c r="B45" s="6">
+        <v>1</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D45" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="E45" s="7" t="s">
+      <c r="E45" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="F45" s="7" t="s">
+      <c r="F45" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="G45" s="7" t="s">
+      <c r="G45" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="H45" s="7" t="s">
+      <c r="H45" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="I45" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J45" s="7" t="s">
+      <c r="I45" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J45" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -4122,31 +4132,31 @@
       <c r="A46" s="3" t="s">
         <v>614</v>
       </c>
-      <c r="B46" s="7">
-        <v>1</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D46" s="7" t="s">
+      <c r="B46" s="6">
+        <v>1</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D46" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="E46" s="7" t="s">
+      <c r="E46" s="6" t="s">
         <v>325</v>
       </c>
-      <c r="F46" s="7" t="s">
+      <c r="F46" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="G46" s="7" t="s">
+      <c r="G46" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="H46" s="7" t="s">
+      <c r="H46" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="I46" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J46" s="7" t="s">
+      <c r="I46" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J46" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -4154,31 +4164,31 @@
       <c r="A47" s="3" t="s">
         <v>615</v>
       </c>
-      <c r="B47" s="7">
-        <v>1</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D47" s="7" t="s">
+      <c r="B47" s="6">
+        <v>1</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D47" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="E47" s="7" t="s">
+      <c r="E47" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="F47" s="7" t="s">
+      <c r="F47" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="G47" s="7" t="s">
+      <c r="G47" s="6" t="s">
         <v>332</v>
       </c>
-      <c r="H47" s="7" t="s">
+      <c r="H47" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="I47" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J47" s="7" t="s">
+      <c r="I47" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J47" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -4186,31 +4196,31 @@
       <c r="A48" s="3" t="s">
         <v>616</v>
       </c>
-      <c r="B48" s="7">
-        <v>1</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D48" s="7" t="s">
+      <c r="B48" s="6">
+        <v>1</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D48" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="E48" s="7" t="s">
+      <c r="E48" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="F48" s="7" t="s">
+      <c r="F48" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="G48" s="7" t="s">
+      <c r="G48" s="6" t="s">
         <v>337</v>
       </c>
-      <c r="H48" s="7" t="s">
+      <c r="H48" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="I48" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J48" s="7" t="s">
+      <c r="I48" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J48" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -4218,31 +4228,31 @@
       <c r="A49" s="3" t="s">
         <v>617</v>
       </c>
-      <c r="B49" s="7">
-        <v>1</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D49" s="7" t="s">
+      <c r="B49" s="6">
+        <v>1</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D49" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="E49" s="7" t="s">
+      <c r="E49" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="F49" s="7" t="s">
+      <c r="F49" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="G49" s="7" t="s">
+      <c r="G49" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="H49" s="7" t="s">
+      <c r="H49" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="I49" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J49" s="7" t="s">
+      <c r="I49" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J49" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -4250,31 +4260,31 @@
       <c r="A50" s="3" t="s">
         <v>618</v>
       </c>
-      <c r="B50" s="7">
-        <v>1</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D50" s="7" t="s">
+      <c r="B50" s="6">
+        <v>1</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D50" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="E50" s="7" t="s">
+      <c r="E50" s="6" t="s">
         <v>345</v>
       </c>
-      <c r="F50" s="7" t="s">
+      <c r="F50" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="G50" s="7" t="s">
+      <c r="G50" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="H50" s="7" t="s">
+      <c r="H50" s="6" t="s">
         <v>348</v>
       </c>
-      <c r="I50" s="7" t="s">
+      <c r="I50" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J50" s="7" t="s">
+      <c r="J50" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -4282,31 +4292,31 @@
       <c r="A51" s="3" t="s">
         <v>619</v>
       </c>
-      <c r="B51" s="7">
-        <v>1</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D51" s="7" t="s">
+      <c r="B51" s="6">
+        <v>1</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D51" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="E51" s="7" t="s">
+      <c r="E51" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="F51" s="7" t="s">
+      <c r="F51" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="G51" s="7" t="s">
+      <c r="G51" s="6" t="s">
         <v>352</v>
       </c>
-      <c r="H51" s="7" t="s">
+      <c r="H51" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="I51" s="7" t="s">
+      <c r="I51" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J51" s="7" t="s">
+      <c r="J51" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -4314,31 +4324,31 @@
       <c r="A52" s="3" t="s">
         <v>620</v>
       </c>
-      <c r="B52" s="7">
-        <v>1</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D52" s="7" t="s">
+      <c r="B52" s="6">
+        <v>1</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D52" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="E52" s="7" t="s">
+      <c r="E52" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="F52" s="7" t="s">
+      <c r="F52" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="G52" s="7" t="s">
+      <c r="G52" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="H52" s="7" t="s">
+      <c r="H52" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="I52" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J52" s="7" t="s">
+      <c r="I52" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J52" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -4346,31 +4356,31 @@
       <c r="A53" s="3" t="s">
         <v>621</v>
       </c>
-      <c r="B53" s="7">
-        <v>1</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D53" s="7" t="s">
+      <c r="B53" s="6">
+        <v>1</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D53" s="6" t="s">
         <v>355</v>
       </c>
-      <c r="E53" s="7" t="s">
+      <c r="E53" s="6" t="s">
         <v>356</v>
       </c>
-      <c r="F53" s="7" t="s">
+      <c r="F53" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="G53" s="7" t="s">
+      <c r="G53" s="6" t="s">
         <v>358</v>
       </c>
-      <c r="H53" s="7" t="s">
+      <c r="H53" s="6" t="s">
         <v>359</v>
       </c>
-      <c r="I53" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J53" s="7" t="s">
+      <c r="I53" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J53" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -4378,31 +4388,31 @@
       <c r="A54" s="3" t="s">
         <v>622</v>
       </c>
-      <c r="B54" s="7">
-        <v>1</v>
-      </c>
-      <c r="C54" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D54" s="7" t="s">
+      <c r="B54" s="6">
+        <v>1</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D54" s="6" t="s">
         <v>360</v>
       </c>
-      <c r="E54" s="7" t="s">
+      <c r="E54" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="F54" s="7" t="s">
+      <c r="F54" s="6" t="s">
         <v>362</v>
       </c>
-      <c r="G54" s="7" t="s">
+      <c r="G54" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="H54" s="7" t="s">
+      <c r="H54" s="6" t="s">
         <v>364</v>
       </c>
-      <c r="I54" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J54" s="7" t="s">
+      <c r="I54" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J54" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -4410,31 +4420,31 @@
       <c r="A55" s="3" t="s">
         <v>623</v>
       </c>
-      <c r="B55" s="7">
+      <c r="B55" s="6">
         <v>2</v>
       </c>
-      <c r="C55" s="7" t="s">
+      <c r="C55" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D55" s="7" t="s">
+      <c r="D55" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="E55" s="7" t="s">
+      <c r="E55" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="F55" s="7" t="s">
+      <c r="F55" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="G55" s="7" t="s">
+      <c r="G55" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="H55" s="7" t="s">
+      <c r="H55" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="I55" s="7" t="s">
+      <c r="I55" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="J55" s="8">
+      <c r="J55" s="7">
         <v>1</v>
       </c>
     </row>
@@ -4442,31 +4452,31 @@
       <c r="A56" s="3" t="s">
         <v>624</v>
       </c>
-      <c r="B56" s="7">
+      <c r="B56" s="6">
         <v>2</v>
       </c>
-      <c r="C56" s="7" t="s">
+      <c r="C56" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D56" s="7" t="s">
+      <c r="D56" s="6" t="s">
         <v>427</v>
       </c>
-      <c r="E56" s="7" t="s">
+      <c r="E56" s="6" t="s">
         <v>428</v>
       </c>
-      <c r="F56" s="7" t="s">
+      <c r="F56" s="6" t="s">
         <v>429</v>
       </c>
-      <c r="G56" s="7" t="s">
+      <c r="G56" s="6" t="s">
         <v>430</v>
       </c>
-      <c r="H56" s="7" t="s">
+      <c r="H56" s="6" t="s">
         <v>431</v>
       </c>
-      <c r="I56" s="7" t="s">
+      <c r="I56" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="J56" s="8">
+      <c r="J56" s="7">
         <v>1</v>
       </c>
     </row>
@@ -4474,31 +4484,31 @@
       <c r="A57" s="3" t="s">
         <v>625</v>
       </c>
-      <c r="B57" s="7">
+      <c r="B57" s="6">
         <v>2</v>
       </c>
-      <c r="C57" s="7" t="s">
+      <c r="C57" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D57" s="7" t="s">
+      <c r="D57" s="6" t="s">
         <v>370</v>
       </c>
-      <c r="E57" s="7" t="s">
+      <c r="E57" s="6" t="s">
         <v>371</v>
       </c>
-      <c r="F57" s="7" t="s">
+      <c r="F57" s="6" t="s">
         <v>372</v>
       </c>
-      <c r="G57" s="7" t="s">
+      <c r="G57" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="H57" s="7" t="s">
+      <c r="H57" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="I57" s="7" t="s">
+      <c r="I57" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="J57" s="8">
+      <c r="J57" s="7">
         <v>1</v>
       </c>
     </row>
@@ -4506,23 +4516,23 @@
       <c r="A58" s="3" t="s">
         <v>626</v>
       </c>
-      <c r="B58" s="7">
+      <c r="B58" s="6">
         <v>3</v>
       </c>
-      <c r="C58" s="7" t="s">
+      <c r="C58" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D58" s="7" t="s">
+      <c r="D58" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="E58" s="7"/>
-      <c r="F58" s="7"/>
-      <c r="G58" s="7"/>
-      <c r="H58" s="7"/>
-      <c r="I58" s="7" t="s">
+      <c r="E58" s="6"/>
+      <c r="F58" s="6"/>
+      <c r="G58" s="6"/>
+      <c r="H58" s="6"/>
+      <c r="I58" s="6" t="s">
         <v>376</v>
       </c>
-      <c r="J58" s="8" t="s">
+      <c r="J58" s="7" t="s">
         <v>566</v>
       </c>
     </row>
@@ -4530,23 +4540,23 @@
       <c r="A59" s="3" t="s">
         <v>627</v>
       </c>
-      <c r="B59" s="7">
+      <c r="B59" s="6">
         <v>3</v>
       </c>
-      <c r="C59" s="7" t="s">
+      <c r="C59" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D59" s="7" t="s">
+      <c r="D59" s="6" t="s">
         <v>377</v>
       </c>
-      <c r="E59" s="7"/>
-      <c r="F59" s="7"/>
-      <c r="G59" s="7"/>
-      <c r="H59" s="7"/>
-      <c r="I59" s="7" t="s">
+      <c r="E59" s="6"/>
+      <c r="F59" s="6"/>
+      <c r="G59" s="6"/>
+      <c r="H59" s="6"/>
+      <c r="I59" s="6" t="s">
         <v>378</v>
       </c>
-      <c r="J59" s="8" t="s">
+      <c r="J59" s="7" t="s">
         <v>566</v>
       </c>
     </row>
@@ -4554,31 +4564,31 @@
       <c r="A60" s="3" t="s">
         <v>628</v>
       </c>
-      <c r="B60" s="7">
-        <v>1</v>
-      </c>
-      <c r="C60" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D60" s="7" t="s">
+      <c r="B60" s="6">
+        <v>1</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D60" s="6" t="s">
         <v>439</v>
       </c>
-      <c r="E60" s="7" t="s">
+      <c r="E60" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="F60" s="7" t="s">
+      <c r="F60" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="G60" s="7" t="s">
+      <c r="G60" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="H60" s="7" t="s">
+      <c r="H60" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="I60" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J60" s="7" t="s">
+      <c r="I60" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J60" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -4586,31 +4596,31 @@
       <c r="A61" s="3" t="s">
         <v>629</v>
       </c>
-      <c r="B61" s="7">
-        <v>1</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D61" s="7" t="s">
+      <c r="B61" s="6">
+        <v>1</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D61" s="6" t="s">
         <v>440</v>
       </c>
-      <c r="E61" s="7" t="s">
+      <c r="E61" s="6" t="s">
         <v>441</v>
       </c>
-      <c r="F61" s="7" t="s">
+      <c r="F61" s="6" t="s">
         <v>442</v>
       </c>
-      <c r="G61" s="7" t="s">
+      <c r="G61" s="6" t="s">
         <v>443</v>
       </c>
-      <c r="H61" s="7" t="s">
+      <c r="H61" s="6" t="s">
         <v>444</v>
       </c>
-      <c r="I61" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J61" s="7" t="s">
+      <c r="I61" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J61" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -4618,31 +4628,31 @@
       <c r="A62" s="3" t="s">
         <v>630</v>
       </c>
-      <c r="B62" s="7">
-        <v>1</v>
-      </c>
-      <c r="C62" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D62" s="7" t="s">
+      <c r="B62" s="6">
+        <v>1</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D62" s="6" t="s">
         <v>445</v>
       </c>
-      <c r="E62" s="7" t="s">
+      <c r="E62" s="6" t="s">
         <v>446</v>
       </c>
-      <c r="F62" s="7" t="s">
+      <c r="F62" s="6" t="s">
         <v>447</v>
       </c>
-      <c r="G62" s="7" t="s">
+      <c r="G62" s="6" t="s">
         <v>448</v>
       </c>
-      <c r="H62" s="7" t="s">
+      <c r="H62" s="6" t="s">
         <v>449</v>
       </c>
-      <c r="I62" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J62" s="7" t="s">
+      <c r="I62" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J62" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -4650,31 +4660,31 @@
       <c r="A63" s="3" t="s">
         <v>631</v>
       </c>
-      <c r="B63" s="7">
-        <v>1</v>
-      </c>
-      <c r="C63" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D63" s="7" t="s">
+      <c r="B63" s="6">
+        <v>1</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D63" s="6" t="s">
         <v>450</v>
       </c>
-      <c r="E63" s="7" t="s">
+      <c r="E63" s="6" t="s">
         <v>451</v>
       </c>
-      <c r="F63" s="7" t="s">
+      <c r="F63" s="6" t="s">
         <v>452</v>
       </c>
-      <c r="G63" s="7" t="s">
+      <c r="G63" s="6" t="s">
         <v>453</v>
       </c>
-      <c r="H63" s="7" t="s">
+      <c r="H63" s="6" t="s">
         <v>454</v>
       </c>
-      <c r="I63" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J63" s="7" t="s">
+      <c r="I63" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J63" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -4682,31 +4692,31 @@
       <c r="A64" s="3" t="s">
         <v>632</v>
       </c>
-      <c r="B64" s="7">
-        <v>1</v>
-      </c>
-      <c r="C64" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D64" s="7" t="s">
+      <c r="B64" s="6">
+        <v>1</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D64" s="6" t="s">
         <v>455</v>
       </c>
-      <c r="E64" s="7" t="s">
+      <c r="E64" s="6" t="s">
         <v>456</v>
       </c>
-      <c r="F64" s="7" t="s">
+      <c r="F64" s="6" t="s">
         <v>457</v>
       </c>
-      <c r="G64" s="7" t="s">
+      <c r="G64" s="6" t="s">
         <v>458</v>
       </c>
-      <c r="H64" s="7" t="s">
+      <c r="H64" s="6" t="s">
         <v>459</v>
       </c>
-      <c r="I64" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J64" s="7" t="s">
+      <c r="I64" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J64" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -4714,31 +4724,31 @@
       <c r="A65" s="3" t="s">
         <v>633</v>
       </c>
-      <c r="B65" s="7">
-        <v>1</v>
-      </c>
-      <c r="C65" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D65" s="7" t="s">
+      <c r="B65" s="6">
+        <v>1</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D65" s="6" t="s">
         <v>460</v>
       </c>
-      <c r="E65" s="7" t="s">
+      <c r="E65" s="6" t="s">
         <v>461</v>
       </c>
-      <c r="F65" s="7" t="s">
+      <c r="F65" s="6" t="s">
         <v>462</v>
       </c>
-      <c r="G65" s="7" t="s">
+      <c r="G65" s="6" t="s">
         <v>463</v>
       </c>
-      <c r="H65" s="7" t="s">
+      <c r="H65" s="6" t="s">
         <v>464</v>
       </c>
-      <c r="I65" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J65" s="7" t="s">
+      <c r="I65" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J65" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -4746,31 +4756,31 @@
       <c r="A66" s="3" t="s">
         <v>634</v>
       </c>
-      <c r="B66" s="7">
-        <v>1</v>
-      </c>
-      <c r="C66" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D66" s="7" t="s">
+      <c r="B66" s="6">
+        <v>1</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D66" s="6" t="s">
         <v>465</v>
       </c>
-      <c r="E66" s="7" t="s">
+      <c r="E66" s="6" t="s">
         <v>466</v>
       </c>
-      <c r="F66" s="7" t="s">
+      <c r="F66" s="6" t="s">
         <v>467</v>
       </c>
-      <c r="G66" s="7" t="s">
+      <c r="G66" s="6" t="s">
         <v>468</v>
       </c>
-      <c r="H66" s="7" t="s">
+      <c r="H66" s="6" t="s">
         <v>469</v>
       </c>
-      <c r="I66" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J66" s="7" t="s">
+      <c r="I66" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J66" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -4778,31 +4788,31 @@
       <c r="A67" s="3" t="s">
         <v>635</v>
       </c>
-      <c r="B67" s="7">
-        <v>1</v>
-      </c>
-      <c r="C67" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D67" s="7" t="s">
+      <c r="B67" s="6">
+        <v>1</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D67" s="6" t="s">
         <v>470</v>
       </c>
-      <c r="E67" s="7" t="s">
+      <c r="E67" s="6" t="s">
         <v>471</v>
       </c>
-      <c r="F67" s="7" t="s">
+      <c r="F67" s="6" t="s">
         <v>472</v>
       </c>
-      <c r="G67" s="7" t="s">
+      <c r="G67" s="6" t="s">
         <v>473</v>
       </c>
-      <c r="H67" s="7" t="s">
+      <c r="H67" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="I67" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J67" s="7" t="s">
+      <c r="I67" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J67" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -4810,31 +4820,31 @@
       <c r="A68" s="3" t="s">
         <v>636</v>
       </c>
-      <c r="B68" s="7">
-        <v>1</v>
-      </c>
-      <c r="C68" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D68" s="7" t="s">
+      <c r="B68" s="6">
+        <v>1</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D68" s="6" t="s">
         <v>475</v>
       </c>
-      <c r="E68" s="7" t="s">
+      <c r="E68" s="6" t="s">
         <v>476</v>
       </c>
-      <c r="F68" s="7" t="s">
+      <c r="F68" s="6" t="s">
         <v>477</v>
       </c>
-      <c r="G68" s="7" t="s">
+      <c r="G68" s="6" t="s">
         <v>478</v>
       </c>
-      <c r="H68" s="7" t="s">
+      <c r="H68" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="I68" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J68" s="7" t="s">
+      <c r="I68" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J68" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -4842,31 +4852,31 @@
       <c r="A69" s="3" t="s">
         <v>637</v>
       </c>
-      <c r="B69" s="7">
-        <v>1</v>
-      </c>
-      <c r="C69" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D69" s="7" t="s">
+      <c r="B69" s="6">
+        <v>1</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D69" s="6" t="s">
         <v>480</v>
       </c>
-      <c r="E69" s="7" t="s">
+      <c r="E69" s="6" t="s">
         <v>481</v>
       </c>
-      <c r="F69" s="7" t="s">
+      <c r="F69" s="6" t="s">
         <v>482</v>
       </c>
-      <c r="G69" s="7" t="s">
+      <c r="G69" s="6" t="s">
         <v>483</v>
       </c>
-      <c r="H69" s="7" t="s">
+      <c r="H69" s="6" t="s">
         <v>484</v>
       </c>
-      <c r="I69" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J69" s="7" t="s">
+      <c r="I69" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J69" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -4874,31 +4884,31 @@
       <c r="A70" s="3" t="s">
         <v>638</v>
       </c>
-      <c r="B70" s="7">
-        <v>1</v>
-      </c>
-      <c r="C70" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D70" s="7" t="s">
+      <c r="B70" s="6">
+        <v>1</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D70" s="6" t="s">
         <v>485</v>
       </c>
-      <c r="E70" s="7" t="s">
+      <c r="E70" s="6" t="s">
         <v>486</v>
       </c>
-      <c r="F70" s="7" t="s">
+      <c r="F70" s="6" t="s">
         <v>487</v>
       </c>
-      <c r="G70" s="7" t="s">
+      <c r="G70" s="6" t="s">
         <v>488</v>
       </c>
-      <c r="H70" s="7" t="s">
+      <c r="H70" s="6" t="s">
         <v>489</v>
       </c>
-      <c r="I70" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J70" s="7" t="s">
+      <c r="I70" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J70" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -4906,31 +4916,31 @@
       <c r="A71" s="3" t="s">
         <v>639</v>
       </c>
-      <c r="B71" s="7">
-        <v>1</v>
-      </c>
-      <c r="C71" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D71" s="7" t="s">
+      <c r="B71" s="6">
+        <v>1</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D71" s="6" t="s">
         <v>490</v>
       </c>
-      <c r="E71" s="7" t="s">
+      <c r="E71" s="6" t="s">
         <v>491</v>
       </c>
-      <c r="F71" s="7" t="s">
+      <c r="F71" s="6" t="s">
         <v>492</v>
       </c>
-      <c r="G71" s="7" t="s">
+      <c r="G71" s="6" t="s">
         <v>493</v>
       </c>
-      <c r="H71" s="7" t="s">
+      <c r="H71" s="6" t="s">
         <v>494</v>
       </c>
-      <c r="I71" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J71" s="7" t="s">
+      <c r="I71" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J71" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -4938,31 +4948,31 @@
       <c r="A72" s="3" t="s">
         <v>640</v>
       </c>
-      <c r="B72" s="7">
-        <v>1</v>
-      </c>
-      <c r="C72" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D72" s="7" t="s">
+      <c r="B72" s="6">
+        <v>1</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D72" s="6" t="s">
         <v>379</v>
       </c>
-      <c r="E72" s="7" t="s">
+      <c r="E72" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="F72" s="7" t="s">
+      <c r="F72" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="G72" s="7" t="s">
+      <c r="G72" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="H72" s="7" t="s">
+      <c r="H72" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="I72" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J72" s="7" t="s">
+      <c r="I72" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J72" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -4970,31 +4980,31 @@
       <c r="A73" s="3" t="s">
         <v>641</v>
       </c>
-      <c r="B73" s="7">
-        <v>1</v>
-      </c>
-      <c r="C73" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D73" s="7" t="s">
+      <c r="B73" s="6">
+        <v>1</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D73" s="6" t="s">
         <v>380</v>
       </c>
-      <c r="E73" s="7" t="s">
+      <c r="E73" s="6" t="s">
         <v>381</v>
       </c>
-      <c r="F73" s="7" t="s">
+      <c r="F73" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="G73" s="7" t="s">
+      <c r="G73" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="H73" s="7" t="s">
+      <c r="H73" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="I73" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J73" s="7" t="s">
+      <c r="I73" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J73" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -5002,31 +5012,31 @@
       <c r="A74" s="3" t="s">
         <v>642</v>
       </c>
-      <c r="B74" s="7">
-        <v>1</v>
-      </c>
-      <c r="C74" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D74" s="7" t="s">
+      <c r="B74" s="6">
+        <v>1</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D74" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="E74" s="7" t="s">
+      <c r="E74" s="6" t="s">
         <v>383</v>
       </c>
-      <c r="F74" s="7" t="s">
+      <c r="F74" s="6" t="s">
         <v>384</v>
       </c>
-      <c r="G74" s="7" t="s">
+      <c r="G74" s="6" t="s">
         <v>385</v>
       </c>
-      <c r="H74" s="7" t="s">
+      <c r="H74" s="6" t="s">
         <v>386</v>
       </c>
-      <c r="I74" s="7" t="s">
+      <c r="I74" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J74" s="7" t="s">
+      <c r="J74" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -5034,31 +5044,31 @@
       <c r="A75" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="B75" s="7">
-        <v>1</v>
-      </c>
-      <c r="C75" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D75" s="7" t="s">
+      <c r="B75" s="6">
+        <v>1</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D75" s="6" t="s">
         <v>387</v>
       </c>
-      <c r="E75" s="7" t="s">
+      <c r="E75" s="6" t="s">
         <v>388</v>
       </c>
-      <c r="F75" s="7" t="s">
+      <c r="F75" s="6" t="s">
         <v>389</v>
       </c>
-      <c r="G75" s="7" t="s">
+      <c r="G75" s="6" t="s">
         <v>390</v>
       </c>
-      <c r="H75" s="7" t="s">
+      <c r="H75" s="6" t="s">
         <v>391</v>
       </c>
-      <c r="I75" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J75" s="7" t="s">
+      <c r="I75" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J75" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -5066,31 +5076,31 @@
       <c r="A76" s="3" t="s">
         <v>644</v>
       </c>
-      <c r="B76" s="7">
-        <v>1</v>
-      </c>
-      <c r="C76" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D76" s="7" t="s">
+      <c r="B76" s="6">
+        <v>1</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D76" s="6" t="s">
         <v>392</v>
       </c>
-      <c r="E76" s="7" t="s">
+      <c r="E76" s="6" t="s">
         <v>393</v>
       </c>
-      <c r="F76" s="7" t="s">
+      <c r="F76" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="G76" s="7" t="s">
+      <c r="G76" s="6" t="s">
         <v>395</v>
       </c>
-      <c r="H76" s="7" t="s">
+      <c r="H76" s="6" t="s">
         <v>396</v>
       </c>
-      <c r="I76" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J76" s="7" t="s">
+      <c r="I76" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J76" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -5098,31 +5108,31 @@
       <c r="A77" s="3" t="s">
         <v>645</v>
       </c>
-      <c r="B77" s="7">
-        <v>1</v>
-      </c>
-      <c r="C77" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D77" s="7" t="s">
+      <c r="B77" s="6">
+        <v>1</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D77" s="6" t="s">
         <v>397</v>
       </c>
-      <c r="E77" s="7" t="s">
+      <c r="E77" s="6" t="s">
         <v>398</v>
       </c>
-      <c r="F77" s="7" t="s">
+      <c r="F77" s="6" t="s">
         <v>399</v>
       </c>
-      <c r="G77" s="7" t="s">
+      <c r="G77" s="6" t="s">
         <v>400</v>
       </c>
-      <c r="H77" s="7" t="s">
+      <c r="H77" s="6" t="s">
         <v>401</v>
       </c>
-      <c r="I77" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J77" s="7" t="s">
+      <c r="I77" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J77" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -5130,31 +5140,31 @@
       <c r="A78" s="3" t="s">
         <v>646</v>
       </c>
-      <c r="B78" s="7">
-        <v>1</v>
-      </c>
-      <c r="C78" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D78" s="7" t="s">
+      <c r="B78" s="6">
+        <v>1</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D78" s="6" t="s">
         <v>402</v>
       </c>
-      <c r="E78" s="7" t="s">
+      <c r="E78" s="6" t="s">
         <v>403</v>
       </c>
-      <c r="F78" s="7" t="s">
+      <c r="F78" s="6" t="s">
         <v>404</v>
       </c>
-      <c r="G78" s="7" t="s">
+      <c r="G78" s="6" t="s">
         <v>405</v>
       </c>
-      <c r="H78" s="7" t="s">
+      <c r="H78" s="6" t="s">
         <v>406</v>
       </c>
-      <c r="I78" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J78" s="7" t="s">
+      <c r="I78" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J78" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -5162,31 +5172,31 @@
       <c r="A79" s="3" t="s">
         <v>647</v>
       </c>
-      <c r="B79" s="7">
-        <v>1</v>
-      </c>
-      <c r="C79" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D79" s="7" t="s">
+      <c r="B79" s="6">
+        <v>1</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D79" s="6" t="s">
         <v>407</v>
       </c>
-      <c r="E79" s="7" t="s">
+      <c r="E79" s="6" t="s">
         <v>408</v>
       </c>
-      <c r="F79" s="7" t="s">
+      <c r="F79" s="6" t="s">
         <v>409</v>
       </c>
-      <c r="G79" s="7" t="s">
+      <c r="G79" s="6" t="s">
         <v>410</v>
       </c>
-      <c r="H79" s="7" t="s">
+      <c r="H79" s="6" t="s">
         <v>411</v>
       </c>
-      <c r="I79" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J79" s="7" t="s">
+      <c r="I79" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J79" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -5194,31 +5204,31 @@
       <c r="A80" s="3" t="s">
         <v>648</v>
       </c>
-      <c r="B80" s="7">
-        <v>1</v>
-      </c>
-      <c r="C80" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D80" s="7" t="s">
+      <c r="B80" s="6">
+        <v>1</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D80" s="6" t="s">
         <v>412</v>
       </c>
-      <c r="E80" s="7" t="s">
+      <c r="E80" s="6" t="s">
         <v>413</v>
       </c>
-      <c r="F80" s="7" t="s">
+      <c r="F80" s="6" t="s">
         <v>414</v>
       </c>
-      <c r="G80" s="7" t="s">
+      <c r="G80" s="6" t="s">
         <v>415</v>
       </c>
-      <c r="H80" s="7" t="s">
+      <c r="H80" s="6" t="s">
         <v>416</v>
       </c>
-      <c r="I80" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J80" s="7" t="s">
+      <c r="I80" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J80" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -5226,31 +5236,31 @@
       <c r="A81" s="3" t="s">
         <v>649</v>
       </c>
-      <c r="B81" s="7">
-        <v>1</v>
-      </c>
-      <c r="C81" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D81" s="7" t="s">
+      <c r="B81" s="6">
+        <v>1</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D81" s="6" t="s">
         <v>417</v>
       </c>
-      <c r="E81" s="7" t="s">
+      <c r="E81" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="F81" s="7" t="s">
+      <c r="F81" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="G81" s="7" t="s">
+      <c r="G81" s="6" t="s">
         <v>352</v>
       </c>
-      <c r="H81" s="7" t="s">
+      <c r="H81" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="I81" s="7" t="s">
+      <c r="I81" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J81" s="7" t="s">
+      <c r="J81" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -5258,31 +5268,31 @@
       <c r="A82" s="3" t="s">
         <v>650</v>
       </c>
-      <c r="B82" s="7">
-        <v>1</v>
-      </c>
-      <c r="C82" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D82" s="7" t="s">
+      <c r="B82" s="6">
+        <v>1</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D82" s="6" t="s">
         <v>418</v>
       </c>
-      <c r="E82" s="7" t="s">
+      <c r="E82" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="F82" s="7" t="s">
+      <c r="F82" s="6" t="s">
         <v>419</v>
       </c>
-      <c r="G82" s="7" t="s">
+      <c r="G82" s="6" t="s">
         <v>420</v>
       </c>
-      <c r="H82" s="7" t="s">
+      <c r="H82" s="6" t="s">
         <v>421</v>
       </c>
-      <c r="I82" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J82" s="7" t="s">
+      <c r="I82" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J82" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -5290,31 +5300,31 @@
       <c r="A83" s="3" t="s">
         <v>651</v>
       </c>
-      <c r="B83" s="7">
-        <v>1</v>
-      </c>
-      <c r="C83" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D83" s="7" t="s">
+      <c r="B83" s="6">
+        <v>1</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D83" s="6" t="s">
         <v>422</v>
       </c>
-      <c r="E83" s="7" t="s">
+      <c r="E83" s="6" t="s">
         <v>423</v>
       </c>
-      <c r="F83" s="7" t="s">
+      <c r="F83" s="6" t="s">
         <v>424</v>
       </c>
-      <c r="G83" s="7" t="s">
+      <c r="G83" s="6" t="s">
         <v>425</v>
       </c>
-      <c r="H83" s="7" t="s">
+      <c r="H83" s="6" t="s">
         <v>426</v>
       </c>
-      <c r="I83" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J83" s="7" t="s">
+      <c r="I83" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J83" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -5322,31 +5332,31 @@
       <c r="A84" s="3" t="s">
         <v>652</v>
       </c>
-      <c r="B84" s="7">
+      <c r="B84" s="6">
         <v>2</v>
       </c>
-      <c r="C84" s="7" t="s">
+      <c r="C84" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D84" s="7" t="s">
+      <c r="D84" s="6" t="s">
         <v>370</v>
       </c>
-      <c r="E84" s="7" t="s">
+      <c r="E84" s="6" t="s">
         <v>371</v>
       </c>
-      <c r="F84" s="7" t="s">
+      <c r="F84" s="6" t="s">
         <v>372</v>
       </c>
-      <c r="G84" s="7" t="s">
+      <c r="G84" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="H84" s="7" t="s">
+      <c r="H84" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="I84" s="7" t="s">
+      <c r="I84" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="J84" s="8">
+      <c r="J84" s="7">
         <v>1</v>
       </c>
     </row>
@@ -5354,31 +5364,31 @@
       <c r="A85" s="3" t="s">
         <v>653</v>
       </c>
-      <c r="B85" s="7">
+      <c r="B85" s="6">
         <v>2</v>
       </c>
-      <c r="C85" s="7" t="s">
+      <c r="C85" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D85" s="7" t="s">
+      <c r="D85" s="6" t="s">
         <v>427</v>
       </c>
-      <c r="E85" s="7" t="s">
+      <c r="E85" s="6" t="s">
         <v>428</v>
       </c>
-      <c r="F85" s="7" t="s">
+      <c r="F85" s="6" t="s">
         <v>429</v>
       </c>
-      <c r="G85" s="7" t="s">
+      <c r="G85" s="6" t="s">
         <v>430</v>
       </c>
-      <c r="H85" s="7" t="s">
+      <c r="H85" s="6" t="s">
         <v>431</v>
       </c>
-      <c r="I85" s="7" t="s">
+      <c r="I85" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="J85" s="8">
+      <c r="J85" s="7">
         <v>1</v>
       </c>
     </row>
@@ -5386,31 +5396,31 @@
       <c r="A86" s="3" t="s">
         <v>654</v>
       </c>
-      <c r="B86" s="7">
+      <c r="B86" s="6">
         <v>2</v>
       </c>
-      <c r="C86" s="7" t="s">
+      <c r="C86" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D86" s="7" t="s">
+      <c r="D86" s="6" t="s">
         <v>495</v>
       </c>
-      <c r="E86" s="7" t="s">
+      <c r="E86" s="6" t="s">
         <v>496</v>
       </c>
-      <c r="F86" s="7" t="s">
+      <c r="F86" s="6" t="s">
         <v>497</v>
       </c>
-      <c r="G86" s="7" t="s">
+      <c r="G86" s="6" t="s">
         <v>498</v>
       </c>
-      <c r="H86" s="7" t="s">
+      <c r="H86" s="6" t="s">
         <v>499</v>
       </c>
-      <c r="I86" s="7" t="s">
+      <c r="I86" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="J86" s="8">
+      <c r="J86" s="7">
         <v>1</v>
       </c>
     </row>
@@ -5418,31 +5428,31 @@
       <c r="A87" s="3" t="s">
         <v>655</v>
       </c>
-      <c r="B87" s="7">
+      <c r="B87" s="6">
         <v>2</v>
       </c>
-      <c r="C87" s="7" t="s">
+      <c r="C87" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D87" s="7" t="s">
+      <c r="D87" s="6" t="s">
         <v>432</v>
       </c>
-      <c r="E87" s="7" t="s">
+      <c r="E87" s="6" t="s">
         <v>433</v>
       </c>
-      <c r="F87" s="7" t="s">
+      <c r="F87" s="6" t="s">
         <v>434</v>
       </c>
-      <c r="G87" s="7" t="s">
+      <c r="G87" s="6" t="s">
         <v>435</v>
       </c>
-      <c r="H87" s="7" t="s">
+      <c r="H87" s="6" t="s">
         <v>436</v>
       </c>
-      <c r="I87" s="7" t="s">
+      <c r="I87" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="J87" s="8">
+      <c r="J87" s="7">
         <v>1</v>
       </c>
     </row>
@@ -5450,23 +5460,23 @@
       <c r="A88" s="3" t="s">
         <v>656</v>
       </c>
-      <c r="B88" s="7">
+      <c r="B88" s="6">
         <v>3</v>
       </c>
-      <c r="C88" s="7" t="s">
+      <c r="C88" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D88" s="7" t="s">
+      <c r="D88" s="6" t="s">
         <v>437</v>
       </c>
-      <c r="E88" s="7"/>
-      <c r="F88" s="7"/>
-      <c r="G88" s="7"/>
-      <c r="H88" s="7"/>
-      <c r="I88" s="7" t="s">
+      <c r="E88" s="6"/>
+      <c r="F88" s="6"/>
+      <c r="G88" s="6"/>
+      <c r="H88" s="6"/>
+      <c r="I88" s="6" t="s">
         <v>403</v>
       </c>
-      <c r="J88" s="8" t="s">
+      <c r="J88" s="7" t="s">
         <v>566</v>
       </c>
     </row>
@@ -5474,23 +5484,23 @@
       <c r="A89" s="3" t="s">
         <v>657</v>
       </c>
-      <c r="B89" s="7">
+      <c r="B89" s="6">
         <v>3</v>
       </c>
-      <c r="C89" s="7" t="s">
+      <c r="C89" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D89" s="7" t="s">
+      <c r="D89" s="6" t="s">
         <v>438</v>
       </c>
-      <c r="E89" s="7"/>
-      <c r="F89" s="7"/>
-      <c r="G89" s="7"/>
-      <c r="H89" s="7"/>
-      <c r="I89" s="7" t="s">
+      <c r="E89" s="6"/>
+      <c r="F89" s="6"/>
+      <c r="G89" s="6"/>
+      <c r="H89" s="6"/>
+      <c r="I89" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="J89" s="8" t="s">
+      <c r="J89" s="7" t="s">
         <v>566</v>
       </c>
     </row>
@@ -5498,31 +5508,31 @@
       <c r="A90" s="3" t="s">
         <v>658</v>
       </c>
-      <c r="B90" s="7">
-        <v>1</v>
-      </c>
-      <c r="C90" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D90" s="7" t="s">
+      <c r="B90" s="6">
+        <v>1</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D90" s="6" t="s">
         <v>508</v>
       </c>
-      <c r="E90" s="7" t="s">
+      <c r="E90" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="F90" s="7" t="s">
+      <c r="F90" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="G90" s="7" t="s">
+      <c r="G90" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="H90" s="7" t="s">
+      <c r="H90" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="I90" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J90" s="7" t="s">
+      <c r="I90" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J90" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -5530,31 +5540,31 @@
       <c r="A91" s="3" t="s">
         <v>659</v>
       </c>
-      <c r="B91" s="7">
-        <v>1</v>
-      </c>
-      <c r="C91" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D91" s="7" t="s">
+      <c r="B91" s="6">
+        <v>1</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D91" s="6" t="s">
         <v>509</v>
       </c>
-      <c r="E91" s="7" t="s">
+      <c r="E91" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="F91" s="7" t="s">
+      <c r="F91" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="G91" s="7" t="s">
+      <c r="G91" s="6" t="s">
         <v>321</v>
       </c>
-      <c r="H91" s="7" t="s">
+      <c r="H91" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="I91" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J91" s="7" t="s">
+      <c r="I91" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J91" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -5562,31 +5572,31 @@
       <c r="A92" s="3" t="s">
         <v>660</v>
       </c>
-      <c r="B92" s="7">
-        <v>1</v>
-      </c>
-      <c r="C92" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D92" s="7" t="s">
+      <c r="B92" s="6">
+        <v>1</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D92" s="6" t="s">
         <v>510</v>
       </c>
-      <c r="E92" s="7" t="s">
+      <c r="E92" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="F92" s="7" t="s">
+      <c r="F92" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="G92" s="7" t="s">
+      <c r="G92" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="H92" s="7" t="s">
+      <c r="H92" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="I92" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J92" s="7" t="s">
+      <c r="I92" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J92" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -5594,31 +5604,31 @@
       <c r="A93" s="3" t="s">
         <v>661</v>
       </c>
-      <c r="B93" s="7">
-        <v>1</v>
-      </c>
-      <c r="C93" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D93" s="7" t="s">
+      <c r="B93" s="6">
+        <v>1</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D93" s="6" t="s">
         <v>511</v>
       </c>
-      <c r="E93" s="7" t="s">
+      <c r="E93" s="6" t="s">
         <v>512</v>
       </c>
-      <c r="F93" s="7" t="s">
+      <c r="F93" s="6" t="s">
         <v>513</v>
       </c>
-      <c r="G93" s="7" t="s">
+      <c r="G93" s="6" t="s">
         <v>514</v>
       </c>
-      <c r="H93" s="7" t="s">
+      <c r="H93" s="6" t="s">
         <v>515</v>
       </c>
-      <c r="I93" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J93" s="7" t="s">
+      <c r="I93" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J93" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -5626,31 +5636,31 @@
       <c r="A94" s="3" t="s">
         <v>662</v>
       </c>
-      <c r="B94" s="7">
-        <v>1</v>
-      </c>
-      <c r="C94" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D94" s="7" t="s">
+      <c r="B94" s="6">
+        <v>1</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D94" s="6" t="s">
         <v>516</v>
       </c>
-      <c r="E94" s="7" t="s">
+      <c r="E94" s="6" t="s">
         <v>517</v>
       </c>
-      <c r="F94" s="7" t="s">
+      <c r="F94" s="6" t="s">
         <v>518</v>
       </c>
-      <c r="G94" s="7" t="s">
+      <c r="G94" s="6" t="s">
         <v>519</v>
       </c>
-      <c r="H94" s="7" t="s">
+      <c r="H94" s="6" t="s">
         <v>520</v>
       </c>
-      <c r="I94" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J94" s="7" t="s">
+      <c r="I94" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J94" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -5658,31 +5668,31 @@
       <c r="A95" s="3" t="s">
         <v>663</v>
       </c>
-      <c r="B95" s="7">
-        <v>1</v>
-      </c>
-      <c r="C95" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D95" s="7" t="s">
+      <c r="B95" s="6">
+        <v>1</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D95" s="6" t="s">
         <v>521</v>
       </c>
-      <c r="E95" s="7" t="s">
+      <c r="E95" s="6" t="s">
         <v>522</v>
       </c>
-      <c r="F95" s="7" t="s">
+      <c r="F95" s="6" t="s">
         <v>523</v>
       </c>
-      <c r="G95" s="7" t="s">
+      <c r="G95" s="6" t="s">
         <v>524</v>
       </c>
-      <c r="H95" s="7" t="s">
+      <c r="H95" s="6" t="s">
         <v>525</v>
       </c>
-      <c r="I95" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J95" s="7" t="s">
+      <c r="I95" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J95" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -5690,31 +5700,31 @@
       <c r="A96" s="3" t="s">
         <v>664</v>
       </c>
-      <c r="B96" s="7">
-        <v>1</v>
-      </c>
-      <c r="C96" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D96" s="7" t="s">
+      <c r="B96" s="6">
+        <v>1</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D96" s="6" t="s">
         <v>526</v>
       </c>
-      <c r="E96" s="7" t="s">
+      <c r="E96" s="6" t="s">
         <v>527</v>
       </c>
-      <c r="F96" s="7" t="s">
+      <c r="F96" s="6" t="s">
         <v>528</v>
       </c>
-      <c r="G96" s="7" t="s">
+      <c r="G96" s="6" t="s">
         <v>529</v>
       </c>
-      <c r="H96" s="7" t="s">
+      <c r="H96" s="6" t="s">
         <v>530</v>
       </c>
-      <c r="I96" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J96" s="7" t="s">
+      <c r="I96" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J96" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -5722,31 +5732,31 @@
       <c r="A97" s="3" t="s">
         <v>665</v>
       </c>
-      <c r="B97" s="7">
-        <v>1</v>
-      </c>
-      <c r="C97" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D97" s="7" t="s">
+      <c r="B97" s="6">
+        <v>1</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D97" s="6" t="s">
         <v>531</v>
       </c>
-      <c r="E97" s="7" t="s">
+      <c r="E97" s="6" t="s">
         <v>532</v>
       </c>
-      <c r="F97" s="7" t="s">
+      <c r="F97" s="6" t="s">
         <v>533</v>
       </c>
-      <c r="G97" s="7" t="s">
+      <c r="G97" s="6" t="s">
         <v>534</v>
       </c>
-      <c r="H97" s="7" t="s">
+      <c r="H97" s="6" t="s">
         <v>535</v>
       </c>
-      <c r="I97" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J97" s="7" t="s">
+      <c r="I97" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J97" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -5754,31 +5764,31 @@
       <c r="A98" s="3" t="s">
         <v>666</v>
       </c>
-      <c r="B98" s="7">
-        <v>1</v>
-      </c>
-      <c r="C98" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D98" s="7" t="s">
+      <c r="B98" s="6">
+        <v>1</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D98" s="6" t="s">
         <v>536</v>
       </c>
-      <c r="E98" s="7" t="s">
+      <c r="E98" s="6" t="s">
         <v>537</v>
       </c>
-      <c r="F98" s="7" t="s">
+      <c r="F98" s="6" t="s">
         <v>472</v>
       </c>
-      <c r="G98" s="7" t="s">
+      <c r="G98" s="6" t="s">
         <v>473</v>
       </c>
-      <c r="H98" s="7" t="s">
+      <c r="H98" s="6" t="s">
         <v>538</v>
       </c>
-      <c r="I98" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J98" s="7" t="s">
+      <c r="I98" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J98" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -5786,31 +5796,31 @@
       <c r="A99" s="3" t="s">
         <v>667</v>
       </c>
-      <c r="B99" s="7">
-        <v>1</v>
-      </c>
-      <c r="C99" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D99" s="7" t="s">
+      <c r="B99" s="6">
+        <v>1</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D99" s="6" t="s">
         <v>539</v>
       </c>
-      <c r="E99" s="7" t="s">
+      <c r="E99" s="6" t="s">
         <v>540</v>
       </c>
-      <c r="F99" s="7" t="s">
+      <c r="F99" s="6" t="s">
         <v>541</v>
       </c>
-      <c r="G99" s="7" t="s">
+      <c r="G99" s="6" t="s">
         <v>542</v>
       </c>
-      <c r="H99" s="7" t="s">
+      <c r="H99" s="6" t="s">
         <v>543</v>
       </c>
-      <c r="I99" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J99" s="7" t="s">
+      <c r="I99" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J99" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -5818,31 +5828,31 @@
       <c r="A100" s="3" t="s">
         <v>668</v>
       </c>
-      <c r="B100" s="7">
-        <v>1</v>
-      </c>
-      <c r="C100" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D100" s="7" t="s">
+      <c r="B100" s="6">
+        <v>1</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D100" s="6" t="s">
         <v>544</v>
       </c>
-      <c r="E100" s="7" t="s">
+      <c r="E100" s="6" t="s">
         <v>545</v>
       </c>
-      <c r="F100" s="7" t="s">
+      <c r="F100" s="6" t="s">
         <v>546</v>
       </c>
-      <c r="G100" s="7" t="s">
+      <c r="G100" s="6" t="s">
         <v>547</v>
       </c>
-      <c r="H100" s="7" t="s">
+      <c r="H100" s="6" t="s">
         <v>548</v>
       </c>
-      <c r="I100" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J100" s="7" t="s">
+      <c r="I100" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J100" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -5850,31 +5860,31 @@
       <c r="A101" s="3" t="s">
         <v>669</v>
       </c>
-      <c r="B101" s="7">
-        <v>1</v>
-      </c>
-      <c r="C101" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D101" s="7" t="s">
+      <c r="B101" s="6">
+        <v>1</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D101" s="6" t="s">
         <v>549</v>
       </c>
-      <c r="E101" s="7" t="s">
+      <c r="E101" s="6" t="s">
         <v>550</v>
       </c>
-      <c r="F101" s="7" t="s">
+      <c r="F101" s="6" t="s">
         <v>551</v>
       </c>
-      <c r="G101" s="7" t="s">
+      <c r="G101" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="H101" s="7" t="s">
+      <c r="H101" s="6" t="s">
         <v>552</v>
       </c>
-      <c r="I101" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J101" s="7" t="s">
+      <c r="I101" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J101" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -5882,31 +5892,31 @@
       <c r="A102" s="3" t="s">
         <v>670</v>
       </c>
-      <c r="B102" s="7">
-        <v>1</v>
-      </c>
-      <c r="C102" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D102" s="7" t="s">
+      <c r="B102" s="6">
+        <v>1</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D102" s="6" t="s">
         <v>439</v>
       </c>
-      <c r="E102" s="7" t="s">
+      <c r="E102" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="F102" s="7" t="s">
+      <c r="F102" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="G102" s="7" t="s">
+      <c r="G102" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="H102" s="7" t="s">
+      <c r="H102" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="I102" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J102" s="7" t="s">
+      <c r="I102" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J102" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -5914,31 +5924,31 @@
       <c r="A103" s="3" t="s">
         <v>671</v>
       </c>
-      <c r="B103" s="7">
-        <v>1</v>
-      </c>
-      <c r="C103" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D103" s="7" t="s">
+      <c r="B103" s="6">
+        <v>1</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D103" s="6" t="s">
         <v>440</v>
       </c>
-      <c r="E103" s="7" t="s">
+      <c r="E103" s="6" t="s">
         <v>441</v>
       </c>
-      <c r="F103" s="7" t="s">
+      <c r="F103" s="6" t="s">
         <v>442</v>
       </c>
-      <c r="G103" s="7" t="s">
+      <c r="G103" s="6" t="s">
         <v>443</v>
       </c>
-      <c r="H103" s="7" t="s">
+      <c r="H103" s="6" t="s">
         <v>444</v>
       </c>
-      <c r="I103" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J103" s="7" t="s">
+      <c r="I103" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J103" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -5946,31 +5956,31 @@
       <c r="A104" s="3" t="s">
         <v>672</v>
       </c>
-      <c r="B104" s="7">
-        <v>1</v>
-      </c>
-      <c r="C104" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D104" s="7" t="s">
+      <c r="B104" s="6">
+        <v>1</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D104" s="6" t="s">
         <v>445</v>
       </c>
-      <c r="E104" s="7" t="s">
+      <c r="E104" s="6" t="s">
         <v>446</v>
       </c>
-      <c r="F104" s="7" t="s">
+      <c r="F104" s="6" t="s">
         <v>447</v>
       </c>
-      <c r="G104" s="7" t="s">
+      <c r="G104" s="6" t="s">
         <v>448</v>
       </c>
-      <c r="H104" s="7" t="s">
+      <c r="H104" s="6" t="s">
         <v>449</v>
       </c>
-      <c r="I104" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J104" s="7" t="s">
+      <c r="I104" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J104" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -5978,31 +5988,31 @@
       <c r="A105" s="3" t="s">
         <v>673</v>
       </c>
-      <c r="B105" s="7">
-        <v>1</v>
-      </c>
-      <c r="C105" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D105" s="7" t="s">
+      <c r="B105" s="6">
+        <v>1</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D105" s="6" t="s">
         <v>450</v>
       </c>
-      <c r="E105" s="7" t="s">
+      <c r="E105" s="6" t="s">
         <v>451</v>
       </c>
-      <c r="F105" s="7" t="s">
+      <c r="F105" s="6" t="s">
         <v>452</v>
       </c>
-      <c r="G105" s="7" t="s">
+      <c r="G105" s="6" t="s">
         <v>453</v>
       </c>
-      <c r="H105" s="7" t="s">
+      <c r="H105" s="6" t="s">
         <v>454</v>
       </c>
-      <c r="I105" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J105" s="7" t="s">
+      <c r="I105" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J105" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -6010,31 +6020,31 @@
       <c r="A106" s="3" t="s">
         <v>674</v>
       </c>
-      <c r="B106" s="7">
-        <v>1</v>
-      </c>
-      <c r="C106" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D106" s="7" t="s">
+      <c r="B106" s="6">
+        <v>1</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D106" s="6" t="s">
         <v>455</v>
       </c>
-      <c r="E106" s="7" t="s">
+      <c r="E106" s="6" t="s">
         <v>456</v>
       </c>
-      <c r="F106" s="7" t="s">
+      <c r="F106" s="6" t="s">
         <v>457</v>
       </c>
-      <c r="G106" s="7" t="s">
+      <c r="G106" s="6" t="s">
         <v>458</v>
       </c>
-      <c r="H106" s="7" t="s">
+      <c r="H106" s="6" t="s">
         <v>459</v>
       </c>
-      <c r="I106" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J106" s="7" t="s">
+      <c r="I106" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J106" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -6042,31 +6052,31 @@
       <c r="A107" s="3" t="s">
         <v>675</v>
       </c>
-      <c r="B107" s="7">
-        <v>1</v>
-      </c>
-      <c r="C107" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D107" s="7" t="s">
+      <c r="B107" s="6">
+        <v>1</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D107" s="6" t="s">
         <v>460</v>
       </c>
-      <c r="E107" s="7" t="s">
+      <c r="E107" s="6" t="s">
         <v>461</v>
       </c>
-      <c r="F107" s="7" t="s">
+      <c r="F107" s="6" t="s">
         <v>462</v>
       </c>
-      <c r="G107" s="7" t="s">
+      <c r="G107" s="6" t="s">
         <v>463</v>
       </c>
-      <c r="H107" s="7" t="s">
+      <c r="H107" s="6" t="s">
         <v>464</v>
       </c>
-      <c r="I107" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J107" s="7" t="s">
+      <c r="I107" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J107" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -6074,31 +6084,31 @@
       <c r="A108" s="3" t="s">
         <v>676</v>
       </c>
-      <c r="B108" s="7">
-        <v>1</v>
-      </c>
-      <c r="C108" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D108" s="7" t="s">
+      <c r="B108" s="6">
+        <v>1</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D108" s="6" t="s">
         <v>465</v>
       </c>
-      <c r="E108" s="7" t="s">
+      <c r="E108" s="6" t="s">
         <v>466</v>
       </c>
-      <c r="F108" s="7" t="s">
+      <c r="F108" s="6" t="s">
         <v>467</v>
       </c>
-      <c r="G108" s="7" t="s">
+      <c r="G108" s="6" t="s">
         <v>468</v>
       </c>
-      <c r="H108" s="7" t="s">
+      <c r="H108" s="6" t="s">
         <v>469</v>
       </c>
-      <c r="I108" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J108" s="7" t="s">
+      <c r="I108" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J108" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -6106,31 +6116,31 @@
       <c r="A109" s="3" t="s">
         <v>677</v>
       </c>
-      <c r="B109" s="7">
-        <v>1</v>
-      </c>
-      <c r="C109" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D109" s="7" t="s">
+      <c r="B109" s="6">
+        <v>1</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D109" s="6" t="s">
         <v>470</v>
       </c>
-      <c r="E109" s="7" t="s">
+      <c r="E109" s="6" t="s">
         <v>471</v>
       </c>
-      <c r="F109" s="7" t="s">
+      <c r="F109" s="6" t="s">
         <v>472</v>
       </c>
-      <c r="G109" s="7" t="s">
+      <c r="G109" s="6" t="s">
         <v>473</v>
       </c>
-      <c r="H109" s="7" t="s">
+      <c r="H109" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="I109" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J109" s="7" t="s">
+      <c r="I109" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J109" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -6138,31 +6148,31 @@
       <c r="A110" s="3" t="s">
         <v>678</v>
       </c>
-      <c r="B110" s="7">
-        <v>1</v>
-      </c>
-      <c r="C110" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D110" s="7" t="s">
+      <c r="B110" s="6">
+        <v>1</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D110" s="6" t="s">
         <v>475</v>
       </c>
-      <c r="E110" s="7" t="s">
+      <c r="E110" s="6" t="s">
         <v>476</v>
       </c>
-      <c r="F110" s="7" t="s">
+      <c r="F110" s="6" t="s">
         <v>477</v>
       </c>
-      <c r="G110" s="7" t="s">
+      <c r="G110" s="6" t="s">
         <v>478</v>
       </c>
-      <c r="H110" s="7" t="s">
+      <c r="H110" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="I110" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J110" s="7" t="s">
+      <c r="I110" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J110" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -6170,31 +6180,31 @@
       <c r="A111" s="3" t="s">
         <v>679</v>
       </c>
-      <c r="B111" s="7">
-        <v>1</v>
-      </c>
-      <c r="C111" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D111" s="7" t="s">
+      <c r="B111" s="6">
+        <v>1</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D111" s="6" t="s">
         <v>480</v>
       </c>
-      <c r="E111" s="7" t="s">
+      <c r="E111" s="6" t="s">
         <v>481</v>
       </c>
-      <c r="F111" s="7" t="s">
+      <c r="F111" s="6" t="s">
         <v>482</v>
       </c>
-      <c r="G111" s="7" t="s">
+      <c r="G111" s="6" t="s">
         <v>483</v>
       </c>
-      <c r="H111" s="7" t="s">
+      <c r="H111" s="6" t="s">
         <v>484</v>
       </c>
-      <c r="I111" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J111" s="7" t="s">
+      <c r="I111" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J111" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -6202,31 +6212,31 @@
       <c r="A112" s="3" t="s">
         <v>680</v>
       </c>
-      <c r="B112" s="7">
-        <v>1</v>
-      </c>
-      <c r="C112" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D112" s="7" t="s">
+      <c r="B112" s="6">
+        <v>1</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D112" s="6" t="s">
         <v>485</v>
       </c>
-      <c r="E112" s="7" t="s">
+      <c r="E112" s="6" t="s">
         <v>486</v>
       </c>
-      <c r="F112" s="7" t="s">
+      <c r="F112" s="6" t="s">
         <v>487</v>
       </c>
-      <c r="G112" s="7" t="s">
+      <c r="G112" s="6" t="s">
         <v>488</v>
       </c>
-      <c r="H112" s="7" t="s">
+      <c r="H112" s="6" t="s">
         <v>489</v>
       </c>
-      <c r="I112" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J112" s="7" t="s">
+      <c r="I112" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J112" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -6234,31 +6244,31 @@
       <c r="A113" s="3" t="s">
         <v>681</v>
       </c>
-      <c r="B113" s="7">
-        <v>1</v>
-      </c>
-      <c r="C113" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D113" s="7" t="s">
+      <c r="B113" s="6">
+        <v>1</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D113" s="6" t="s">
         <v>490</v>
       </c>
-      <c r="E113" s="7" t="s">
+      <c r="E113" s="6" t="s">
         <v>491</v>
       </c>
-      <c r="F113" s="7" t="s">
+      <c r="F113" s="6" t="s">
         <v>492</v>
       </c>
-      <c r="G113" s="7" t="s">
+      <c r="G113" s="6" t="s">
         <v>493</v>
       </c>
-      <c r="H113" s="7" t="s">
+      <c r="H113" s="6" t="s">
         <v>494</v>
       </c>
-      <c r="I113" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J113" s="7" t="s">
+      <c r="I113" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J113" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -6266,31 +6276,31 @@
       <c r="A114" s="3" t="s">
         <v>682</v>
       </c>
-      <c r="B114" s="7">
+      <c r="B114" s="6">
         <v>2</v>
       </c>
-      <c r="C114" s="7" t="s">
+      <c r="C114" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D114" s="7" t="s">
+      <c r="D114" s="6" t="s">
         <v>495</v>
       </c>
-      <c r="E114" s="7" t="s">
+      <c r="E114" s="6" t="s">
         <v>496</v>
       </c>
-      <c r="F114" s="7" t="s">
+      <c r="F114" s="6" t="s">
         <v>497</v>
       </c>
-      <c r="G114" s="7" t="s">
+      <c r="G114" s="6" t="s">
         <v>498</v>
       </c>
-      <c r="H114" s="7" t="s">
+      <c r="H114" s="6" t="s">
         <v>499</v>
       </c>
-      <c r="I114" s="7" t="s">
+      <c r="I114" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="J114" s="8">
+      <c r="J114" s="7">
         <v>1</v>
       </c>
     </row>
@@ -6298,31 +6308,31 @@
       <c r="A115" s="3" t="s">
         <v>683</v>
       </c>
-      <c r="B115" s="7">
+      <c r="B115" s="6">
         <v>2</v>
       </c>
-      <c r="C115" s="7" t="s">
+      <c r="C115" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D115" s="7" t="s">
+      <c r="D115" s="6" t="s">
         <v>553</v>
       </c>
-      <c r="E115" s="7" t="s">
+      <c r="E115" s="6" t="s">
         <v>554</v>
       </c>
-      <c r="F115" s="7" t="s">
+      <c r="F115" s="6" t="s">
         <v>555</v>
       </c>
-      <c r="G115" s="7" t="s">
+      <c r="G115" s="6" t="s">
         <v>556</v>
       </c>
-      <c r="H115" s="7" t="s">
+      <c r="H115" s="6" t="s">
         <v>557</v>
       </c>
-      <c r="I115" s="7" t="s">
+      <c r="I115" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="J115" s="8">
+      <c r="J115" s="7">
         <v>1</v>
       </c>
     </row>
@@ -6330,31 +6340,31 @@
       <c r="A116" s="3" t="s">
         <v>684</v>
       </c>
-      <c r="B116" s="7">
+      <c r="B116" s="6">
         <v>2</v>
       </c>
-      <c r="C116" s="7" t="s">
+      <c r="C116" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D116" s="7" t="s">
+      <c r="D116" s="6" t="s">
         <v>500</v>
       </c>
-      <c r="E116" s="7" t="s">
+      <c r="E116" s="6" t="s">
         <v>501</v>
       </c>
-      <c r="F116" s="7" t="s">
+      <c r="F116" s="6" t="s">
         <v>502</v>
       </c>
-      <c r="G116" s="7" t="s">
+      <c r="G116" s="6" t="s">
         <v>503</v>
       </c>
-      <c r="H116" s="7" t="s">
+      <c r="H116" s="6" t="s">
         <v>504</v>
       </c>
-      <c r="I116" s="7" t="s">
+      <c r="I116" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="J116" s="8">
+      <c r="J116" s="7">
         <v>1</v>
       </c>
     </row>
@@ -6362,23 +6372,23 @@
       <c r="A117" s="3" t="s">
         <v>685</v>
       </c>
-      <c r="B117" s="7">
+      <c r="B117" s="6">
         <v>3</v>
       </c>
-      <c r="C117" s="7" t="s">
+      <c r="C117" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D117" s="7" t="s">
+      <c r="D117" s="6" t="s">
         <v>505</v>
       </c>
-      <c r="E117" s="7"/>
-      <c r="F117" s="7"/>
-      <c r="G117" s="7"/>
-      <c r="H117" s="7"/>
-      <c r="I117" s="7" t="s">
+      <c r="E117" s="6"/>
+      <c r="F117" s="6"/>
+      <c r="G117" s="6"/>
+      <c r="H117" s="6"/>
+      <c r="I117" s="6" t="s">
         <v>506</v>
       </c>
-      <c r="J117" s="8" t="s">
+      <c r="J117" s="7" t="s">
         <v>566</v>
       </c>
     </row>
@@ -6386,23 +6396,23 @@
       <c r="A118" s="3" t="s">
         <v>686</v>
       </c>
-      <c r="B118" s="7">
+      <c r="B118" s="6">
         <v>3</v>
       </c>
-      <c r="C118" s="7" t="s">
+      <c r="C118" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D118" s="7" t="s">
+      <c r="D118" s="6" t="s">
         <v>507</v>
       </c>
-      <c r="E118" s="7"/>
-      <c r="F118" s="7"/>
-      <c r="G118" s="7"/>
-      <c r="H118" s="7"/>
-      <c r="I118" s="7" t="s">
+      <c r="E118" s="6"/>
+      <c r="F118" s="6"/>
+      <c r="G118" s="6"/>
+      <c r="H118" s="6"/>
+      <c r="I118" s="6" t="s">
         <v>381</v>
       </c>
-      <c r="J118" s="8" t="s">
+      <c r="J118" s="7" t="s">
         <v>566</v>
       </c>
     </row>
@@ -6410,31 +6420,31 @@
       <c r="A119" s="3" t="s">
         <v>687</v>
       </c>
-      <c r="B119" s="7">
-        <v>1</v>
-      </c>
-      <c r="C119" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D119" s="7" t="s">
+      <c r="B119" s="6">
+        <v>1</v>
+      </c>
+      <c r="C119" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D119" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="E119" s="7" t="s">
+      <c r="E119" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="F119" s="7" t="s">
+      <c r="F119" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="G119" s="7" t="s">
+      <c r="G119" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="H119" s="7" t="s">
+      <c r="H119" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="I119" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J119" s="7" t="s">
+      <c r="I119" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J119" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -6442,31 +6452,31 @@
       <c r="A120" s="3" t="s">
         <v>688</v>
       </c>
-      <c r="B120" s="7">
-        <v>1</v>
-      </c>
-      <c r="C120" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D120" s="7" t="s">
+      <c r="B120" s="6">
+        <v>1</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D120" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="E120" s="7" t="s">
+      <c r="E120" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F120" s="7" t="s">
+      <c r="F120" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="G120" s="7" t="s">
+      <c r="G120" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="H120" s="7" t="s">
+      <c r="H120" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="I120" s="7" t="s">
+      <c r="I120" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J120" s="7" t="s">
+      <c r="J120" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -6474,31 +6484,31 @@
       <c r="A121" s="3" t="s">
         <v>689</v>
       </c>
-      <c r="B121" s="7">
-        <v>1</v>
-      </c>
-      <c r="C121" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D121" s="7" t="s">
+      <c r="B121" s="6">
+        <v>1</v>
+      </c>
+      <c r="C121" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D121" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="E121" s="7" t="s">
+      <c r="E121" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="F121" s="7" t="s">
+      <c r="F121" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="G121" s="7" t="s">
+      <c r="G121" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="H121" s="7" t="s">
+      <c r="H121" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="I121" s="7" t="s">
+      <c r="I121" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J121" s="7" t="s">
+      <c r="J121" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -6506,31 +6516,31 @@
       <c r="A122" s="3" t="s">
         <v>690</v>
       </c>
-      <c r="B122" s="7">
-        <v>1</v>
-      </c>
-      <c r="C122" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D122" s="7" t="s">
+      <c r="B122" s="6">
+        <v>1</v>
+      </c>
+      <c r="C122" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D122" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="E122" s="7" t="s">
+      <c r="E122" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="F122" s="7" t="s">
+      <c r="F122" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="G122" s="7" t="s">
+      <c r="G122" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="H122" s="7" t="s">
+      <c r="H122" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="I122" s="7" t="s">
+      <c r="I122" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J122" s="7" t="s">
+      <c r="J122" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -6538,31 +6548,31 @@
       <c r="A123" s="3" t="s">
         <v>691</v>
       </c>
-      <c r="B123" s="7">
-        <v>1</v>
-      </c>
-      <c r="C123" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D123" s="7" t="s">
+      <c r="B123" s="6">
+        <v>1</v>
+      </c>
+      <c r="C123" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D123" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="E123" s="7" t="s">
+      <c r="E123" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="F123" s="7" t="s">
+      <c r="F123" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="G123" s="7" t="s">
+      <c r="G123" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="H123" s="7" t="s">
+      <c r="H123" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="I123" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J123" s="7" t="s">
+      <c r="I123" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J123" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -6570,31 +6580,31 @@
       <c r="A124" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="B124" s="7">
-        <v>1</v>
-      </c>
-      <c r="C124" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D124" s="7" t="s">
+      <c r="B124" s="6">
+        <v>1</v>
+      </c>
+      <c r="C124" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D124" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="E124" s="7" t="s">
+      <c r="E124" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="F124" s="7" t="s">
+      <c r="F124" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="G124" s="7" t="s">
+      <c r="G124" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="H124" s="7" t="s">
+      <c r="H124" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="I124" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J124" s="7" t="s">
+      <c r="I124" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J124" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -6602,31 +6612,31 @@
       <c r="A125" s="3" t="s">
         <v>693</v>
       </c>
-      <c r="B125" s="7">
-        <v>1</v>
-      </c>
-      <c r="C125" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D125" s="7" t="s">
+      <c r="B125" s="6">
+        <v>1</v>
+      </c>
+      <c r="C125" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D125" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="E125" s="7" t="s">
+      <c r="E125" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="F125" s="7" t="s">
+      <c r="F125" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="G125" s="7" t="s">
+      <c r="G125" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="H125" s="7" t="s">
+      <c r="H125" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="I125" s="7" t="s">
+      <c r="I125" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J125" s="7" t="s">
+      <c r="J125" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -6634,31 +6644,31 @@
       <c r="A126" s="3" t="s">
         <v>694</v>
       </c>
-      <c r="B126" s="7">
-        <v>1</v>
-      </c>
-      <c r="C126" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D126" s="7" t="s">
+      <c r="B126" s="6">
+        <v>1</v>
+      </c>
+      <c r="C126" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D126" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="E126" s="7" t="s">
+      <c r="E126" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="F126" s="7" t="s">
+      <c r="F126" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="G126" s="7" t="s">
+      <c r="G126" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="H126" s="7" t="s">
+      <c r="H126" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="I126" s="7" t="s">
+      <c r="I126" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J126" s="7" t="s">
+      <c r="J126" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -6666,31 +6676,31 @@
       <c r="A127" s="3" t="s">
         <v>695</v>
       </c>
-      <c r="B127" s="7">
-        <v>1</v>
-      </c>
-      <c r="C127" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D127" s="7" t="s">
+      <c r="B127" s="6">
+        <v>1</v>
+      </c>
+      <c r="C127" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D127" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="E127" s="7" t="s">
+      <c r="E127" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="F127" s="7" t="s">
+      <c r="F127" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="G127" s="7" t="s">
+      <c r="G127" s="6" t="s">
         <v>285</v>
       </c>
-      <c r="H127" s="7" t="s">
+      <c r="H127" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="I127" s="7" t="s">
+      <c r="I127" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J127" s="7" t="s">
+      <c r="J127" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -6698,31 +6708,31 @@
       <c r="A128" s="3" t="s">
         <v>696</v>
       </c>
-      <c r="B128" s="7">
-        <v>1</v>
-      </c>
-      <c r="C128" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D128" s="7" t="s">
+      <c r="B128" s="6">
+        <v>1</v>
+      </c>
+      <c r="C128" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D128" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="E128" s="7" t="s">
+      <c r="E128" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="F128" s="7" t="s">
+      <c r="F128" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="G128" s="7" t="s">
+      <c r="G128" s="6" t="s">
         <v>290</v>
       </c>
-      <c r="H128" s="7" t="s">
+      <c r="H128" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="I128" s="7" t="s">
+      <c r="I128" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J128" s="7" t="s">
+      <c r="J128" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -6730,31 +6740,31 @@
       <c r="A129" s="3" t="s">
         <v>697</v>
       </c>
-      <c r="B129" s="7">
-        <v>1</v>
-      </c>
-      <c r="C129" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D129" s="7" t="s">
+      <c r="B129" s="6">
+        <v>1</v>
+      </c>
+      <c r="C129" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D129" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="E129" s="7" t="s">
+      <c r="E129" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="F129" s="7" t="s">
+      <c r="F129" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="G129" s="7" t="s">
+      <c r="G129" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="H129" s="7" t="s">
+      <c r="H129" s="6" t="s">
         <v>296</v>
       </c>
-      <c r="I129" s="7" t="s">
+      <c r="I129" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J129" s="7" t="s">
+      <c r="J129" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -6762,31 +6772,31 @@
       <c r="A130" s="3" t="s">
         <v>698</v>
       </c>
-      <c r="B130" s="7">
-        <v>1</v>
-      </c>
-      <c r="C130" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D130" s="7" t="s">
+      <c r="B130" s="6">
+        <v>1</v>
+      </c>
+      <c r="C130" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D130" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="E130" s="7" t="s">
+      <c r="E130" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="F130" s="7" t="s">
+      <c r="F130" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="G130" s="7" t="s">
+      <c r="G130" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="H130" s="7" t="s">
+      <c r="H130" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="I130" s="7" t="s">
+      <c r="I130" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J130" s="7" t="s">
+      <c r="J130" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -6794,31 +6804,31 @@
       <c r="A131" s="3" t="s">
         <v>699</v>
       </c>
-      <c r="B131" s="7">
-        <v>1</v>
-      </c>
-      <c r="C131" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D131" s="7" t="s">
+      <c r="B131" s="6">
+        <v>1</v>
+      </c>
+      <c r="C131" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D131" s="6" t="s">
         <v>508</v>
       </c>
-      <c r="E131" s="7" t="s">
+      <c r="E131" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="F131" s="7" t="s">
+      <c r="F131" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="G131" s="7" t="s">
+      <c r="G131" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="H131" s="7" t="s">
+      <c r="H131" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="I131" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J131" s="7" t="s">
+      <c r="I131" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J131" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -6826,31 +6836,31 @@
       <c r="A132" s="3" t="s">
         <v>700</v>
       </c>
-      <c r="B132" s="7">
-        <v>1</v>
-      </c>
-      <c r="C132" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D132" s="7" t="s">
+      <c r="B132" s="6">
+        <v>1</v>
+      </c>
+      <c r="C132" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D132" s="6" t="s">
         <v>509</v>
       </c>
-      <c r="E132" s="7" t="s">
+      <c r="E132" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="F132" s="7" t="s">
+      <c r="F132" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="G132" s="7" t="s">
+      <c r="G132" s="6" t="s">
         <v>321</v>
       </c>
-      <c r="H132" s="7" t="s">
+      <c r="H132" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="I132" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J132" s="7" t="s">
+      <c r="I132" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J132" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -6858,31 +6868,31 @@
       <c r="A133" s="3" t="s">
         <v>701</v>
       </c>
-      <c r="B133" s="7">
-        <v>1</v>
-      </c>
-      <c r="C133" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D133" s="7" t="s">
+      <c r="B133" s="6">
+        <v>1</v>
+      </c>
+      <c r="C133" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D133" s="6" t="s">
         <v>510</v>
       </c>
-      <c r="E133" s="7" t="s">
+      <c r="E133" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="F133" s="7" t="s">
+      <c r="F133" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="G133" s="7" t="s">
+      <c r="G133" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="H133" s="7" t="s">
+      <c r="H133" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="I133" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J133" s="7" t="s">
+      <c r="I133" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J133" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -6890,31 +6900,31 @@
       <c r="A134" s="3" t="s">
         <v>702</v>
       </c>
-      <c r="B134" s="7">
-        <v>1</v>
-      </c>
-      <c r="C134" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D134" s="7" t="s">
+      <c r="B134" s="6">
+        <v>1</v>
+      </c>
+      <c r="C134" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D134" s="6" t="s">
         <v>511</v>
       </c>
-      <c r="E134" s="7" t="s">
+      <c r="E134" s="6" t="s">
         <v>512</v>
       </c>
-      <c r="F134" s="7" t="s">
+      <c r="F134" s="6" t="s">
         <v>513</v>
       </c>
-      <c r="G134" s="7" t="s">
+      <c r="G134" s="6" t="s">
         <v>514</v>
       </c>
-      <c r="H134" s="7" t="s">
+      <c r="H134" s="6" t="s">
         <v>515</v>
       </c>
-      <c r="I134" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J134" s="7" t="s">
+      <c r="I134" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J134" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -6922,31 +6932,31 @@
       <c r="A135" s="3" t="s">
         <v>703</v>
       </c>
-      <c r="B135" s="7">
-        <v>1</v>
-      </c>
-      <c r="C135" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D135" s="7" t="s">
+      <c r="B135" s="6">
+        <v>1</v>
+      </c>
+      <c r="C135" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D135" s="6" t="s">
         <v>516</v>
       </c>
-      <c r="E135" s="7" t="s">
+      <c r="E135" s="6" t="s">
         <v>517</v>
       </c>
-      <c r="F135" s="7" t="s">
+      <c r="F135" s="6" t="s">
         <v>518</v>
       </c>
-      <c r="G135" s="7" t="s">
+      <c r="G135" s="6" t="s">
         <v>519</v>
       </c>
-      <c r="H135" s="7" t="s">
+      <c r="H135" s="6" t="s">
         <v>520</v>
       </c>
-      <c r="I135" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J135" s="7" t="s">
+      <c r="I135" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J135" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -6954,31 +6964,31 @@
       <c r="A136" s="3" t="s">
         <v>704</v>
       </c>
-      <c r="B136" s="7">
-        <v>1</v>
-      </c>
-      <c r="C136" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D136" s="7" t="s">
+      <c r="B136" s="6">
+        <v>1</v>
+      </c>
+      <c r="C136" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D136" s="6" t="s">
         <v>521</v>
       </c>
-      <c r="E136" s="7" t="s">
+      <c r="E136" s="6" t="s">
         <v>522</v>
       </c>
-      <c r="F136" s="7" t="s">
+      <c r="F136" s="6" t="s">
         <v>523</v>
       </c>
-      <c r="G136" s="7" t="s">
+      <c r="G136" s="6" t="s">
         <v>524</v>
       </c>
-      <c r="H136" s="7" t="s">
+      <c r="H136" s="6" t="s">
         <v>525</v>
       </c>
-      <c r="I136" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J136" s="7" t="s">
+      <c r="I136" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J136" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -6986,31 +6996,31 @@
       <c r="A137" s="3" t="s">
         <v>705</v>
       </c>
-      <c r="B137" s="7">
-        <v>1</v>
-      </c>
-      <c r="C137" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D137" s="7" t="s">
+      <c r="B137" s="6">
+        <v>1</v>
+      </c>
+      <c r="C137" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D137" s="6" t="s">
         <v>526</v>
       </c>
-      <c r="E137" s="7" t="s">
+      <c r="E137" s="6" t="s">
         <v>527</v>
       </c>
-      <c r="F137" s="7" t="s">
+      <c r="F137" s="6" t="s">
         <v>528</v>
       </c>
-      <c r="G137" s="7" t="s">
+      <c r="G137" s="6" t="s">
         <v>529</v>
       </c>
-      <c r="H137" s="7" t="s">
+      <c r="H137" s="6" t="s">
         <v>530</v>
       </c>
-      <c r="I137" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J137" s="7" t="s">
+      <c r="I137" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J137" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -7018,31 +7028,31 @@
       <c r="A138" s="3" t="s">
         <v>706</v>
       </c>
-      <c r="B138" s="7">
-        <v>1</v>
-      </c>
-      <c r="C138" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D138" s="7" t="s">
+      <c r="B138" s="6">
+        <v>1</v>
+      </c>
+      <c r="C138" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D138" s="6" t="s">
         <v>531</v>
       </c>
-      <c r="E138" s="7" t="s">
+      <c r="E138" s="6" t="s">
         <v>532</v>
       </c>
-      <c r="F138" s="7" t="s">
+      <c r="F138" s="6" t="s">
         <v>533</v>
       </c>
-      <c r="G138" s="7" t="s">
+      <c r="G138" s="6" t="s">
         <v>534</v>
       </c>
-      <c r="H138" s="7" t="s">
+      <c r="H138" s="6" t="s">
         <v>535</v>
       </c>
-      <c r="I138" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J138" s="7" t="s">
+      <c r="I138" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J138" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -7050,31 +7060,31 @@
       <c r="A139" s="3" t="s">
         <v>707</v>
       </c>
-      <c r="B139" s="7">
-        <v>1</v>
-      </c>
-      <c r="C139" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D139" s="7" t="s">
+      <c r="B139" s="6">
+        <v>1</v>
+      </c>
+      <c r="C139" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D139" s="6" t="s">
         <v>536</v>
       </c>
-      <c r="E139" s="7" t="s">
+      <c r="E139" s="6" t="s">
         <v>537</v>
       </c>
-      <c r="F139" s="7" t="s">
+      <c r="F139" s="6" t="s">
         <v>472</v>
       </c>
-      <c r="G139" s="7" t="s">
+      <c r="G139" s="6" t="s">
         <v>473</v>
       </c>
-      <c r="H139" s="7" t="s">
+      <c r="H139" s="6" t="s">
         <v>538</v>
       </c>
-      <c r="I139" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J139" s="7" t="s">
+      <c r="I139" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J139" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -7082,31 +7092,31 @@
       <c r="A140" s="3" t="s">
         <v>708</v>
       </c>
-      <c r="B140" s="7">
-        <v>1</v>
-      </c>
-      <c r="C140" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D140" s="7" t="s">
+      <c r="B140" s="6">
+        <v>1</v>
+      </c>
+      <c r="C140" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D140" s="6" t="s">
         <v>539</v>
       </c>
-      <c r="E140" s="7" t="s">
+      <c r="E140" s="6" t="s">
         <v>540</v>
       </c>
-      <c r="F140" s="7" t="s">
+      <c r="F140" s="6" t="s">
         <v>541</v>
       </c>
-      <c r="G140" s="7" t="s">
+      <c r="G140" s="6" t="s">
         <v>542</v>
       </c>
-      <c r="H140" s="7" t="s">
+      <c r="H140" s="6" t="s">
         <v>543</v>
       </c>
-      <c r="I140" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J140" s="7" t="s">
+      <c r="I140" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J140" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -7114,31 +7124,31 @@
       <c r="A141" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="B141" s="7">
-        <v>1</v>
-      </c>
-      <c r="C141" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D141" s="7" t="s">
+      <c r="B141" s="6">
+        <v>1</v>
+      </c>
+      <c r="C141" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D141" s="6" t="s">
         <v>544</v>
       </c>
-      <c r="E141" s="7" t="s">
+      <c r="E141" s="6" t="s">
         <v>545</v>
       </c>
-      <c r="F141" s="7" t="s">
+      <c r="F141" s="6" t="s">
         <v>546</v>
       </c>
-      <c r="G141" s="7" t="s">
+      <c r="G141" s="6" t="s">
         <v>547</v>
       </c>
-      <c r="H141" s="7" t="s">
+      <c r="H141" s="6" t="s">
         <v>548</v>
       </c>
-      <c r="I141" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J141" s="7" t="s">
+      <c r="I141" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J141" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -7146,31 +7156,31 @@
       <c r="A142" s="3" t="s">
         <v>710</v>
       </c>
-      <c r="B142" s="7">
-        <v>1</v>
-      </c>
-      <c r="C142" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D142" s="7" t="s">
+      <c r="B142" s="6">
+        <v>1</v>
+      </c>
+      <c r="C142" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D142" s="6" t="s">
         <v>549</v>
       </c>
-      <c r="E142" s="7" t="s">
+      <c r="E142" s="6" t="s">
         <v>550</v>
       </c>
-      <c r="F142" s="7" t="s">
+      <c r="F142" s="6" t="s">
         <v>551</v>
       </c>
-      <c r="G142" s="7" t="s">
+      <c r="G142" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="H142" s="7" t="s">
+      <c r="H142" s="6" t="s">
         <v>552</v>
       </c>
-      <c r="I142" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J142" s="7" t="s">
+      <c r="I142" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J142" s="6" t="s">
         <v>569</v>
       </c>
     </row>
@@ -7178,31 +7188,31 @@
       <c r="A143" s="3" t="s">
         <v>711</v>
       </c>
-      <c r="B143" s="7">
+      <c r="B143" s="6">
         <v>2</v>
       </c>
-      <c r="C143" s="7" t="s">
+      <c r="C143" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D143" s="7" t="s">
+      <c r="D143" s="6" t="s">
         <v>553</v>
       </c>
-      <c r="E143" s="7" t="s">
+      <c r="E143" s="6" t="s">
         <v>554</v>
       </c>
-      <c r="F143" s="7" t="s">
+      <c r="F143" s="6" t="s">
         <v>555</v>
       </c>
-      <c r="G143" s="7" t="s">
+      <c r="G143" s="6" t="s">
         <v>556</v>
       </c>
-      <c r="H143" s="7" t="s">
+      <c r="H143" s="6" t="s">
         <v>557</v>
       </c>
-      <c r="I143" s="7" t="s">
+      <c r="I143" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="J143" s="8">
+      <c r="J143" s="7">
         <v>1</v>
       </c>
     </row>
@@ -7210,31 +7220,31 @@
       <c r="A144" s="3" t="s">
         <v>712</v>
       </c>
-      <c r="B144" s="7">
+      <c r="B144" s="6">
         <v>2</v>
       </c>
-      <c r="C144" s="7" t="s">
+      <c r="C144" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D144" s="7" t="s">
+      <c r="D144" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="E144" s="7" t="s">
+      <c r="E144" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="F144" s="7" t="s">
+      <c r="F144" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="G144" s="7" t="s">
+      <c r="G144" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="H144" s="7" t="s">
+      <c r="H144" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="I144" s="7" t="s">
+      <c r="I144" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="J144" s="8">
+      <c r="J144" s="7">
         <v>1</v>
       </c>
     </row>
@@ -7242,31 +7252,31 @@
       <c r="A145" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="B145" s="7">
+      <c r="B145" s="6">
         <v>2</v>
       </c>
-      <c r="C145" s="7" t="s">
+      <c r="C145" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D145" s="7" t="s">
+      <c r="D145" s="6" t="s">
         <v>558</v>
       </c>
-      <c r="E145" s="7" t="s">
+      <c r="E145" s="6" t="s">
         <v>559</v>
       </c>
-      <c r="F145" s="7" t="s">
+      <c r="F145" s="6" t="s">
         <v>560</v>
       </c>
-      <c r="G145" s="7" t="s">
+      <c r="G145" s="6" t="s">
         <v>561</v>
       </c>
-      <c r="H145" s="7" t="s">
+      <c r="H145" s="6" t="s">
         <v>562</v>
       </c>
-      <c r="I145" s="7" t="s">
+      <c r="I145" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="J145" s="8">
+      <c r="J145" s="7">
         <v>1</v>
       </c>
     </row>
@@ -7274,23 +7284,23 @@
       <c r="A146" s="3" t="s">
         <v>714</v>
       </c>
-      <c r="B146" s="7">
+      <c r="B146" s="6">
         <v>3</v>
       </c>
-      <c r="C146" s="7" t="s">
+      <c r="C146" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D146" s="7" t="s">
+      <c r="D146" s="6" t="s">
         <v>563</v>
       </c>
-      <c r="E146" s="7"/>
-      <c r="F146" s="7"/>
-      <c r="G146" s="7"/>
-      <c r="H146" s="7"/>
-      <c r="I146" s="7" t="s">
+      <c r="E146" s="6"/>
+      <c r="F146" s="6"/>
+      <c r="G146" s="6"/>
+      <c r="H146" s="6"/>
+      <c r="I146" s="6" t="s">
         <v>564</v>
       </c>
-      <c r="J146" s="8" t="s">
+      <c r="J146" s="7" t="s">
         <v>566</v>
       </c>
     </row>
@@ -7298,23 +7308,23 @@
       <c r="A147" s="3" t="s">
         <v>715</v>
       </c>
-      <c r="B147" s="7">
+      <c r="B147" s="6">
         <v>3</v>
       </c>
-      <c r="C147" s="7" t="s">
+      <c r="C147" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D147" s="7" t="s">
+      <c r="D147" s="6" t="s">
         <v>565</v>
       </c>
-      <c r="E147" s="7"/>
-      <c r="F147" s="7"/>
-      <c r="G147" s="7"/>
-      <c r="H147" s="7"/>
-      <c r="I147" s="7" t="s">
+      <c r="E147" s="6"/>
+      <c r="F147" s="6"/>
+      <c r="G147" s="6"/>
+      <c r="H147" s="6"/>
+      <c r="I147" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="J147" s="8" t="s">
+      <c r="J147" s="7" t="s">
         <v>566</v>
       </c>
     </row>
@@ -7376,7 +7386,7 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A2" s="9"/>
+      <c r="A2" s="8"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -7389,13 +7399,13 @@
       <c r="K2" s="3"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A3" s="10"/>
+      <c r="A3" s="9"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" s="10"/>
+      <c r="A4" s="9"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A5" s="10"/>
+      <c r="A5" s="9"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K2" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
@@ -7693,1427 +7703,1427 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>65</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="4" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="4" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="4" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="4" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="4" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="4" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="4" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="4" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="4" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="4" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="4" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="4" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="4" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="4" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="4" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="4" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="4" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="4" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="4" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A34" s="5" t="s">
+      <c r="A34" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="4" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="4" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A36" s="5" t="s">
+      <c r="A36" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="4" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="4" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="4" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="4" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="4" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A41" s="5" t="s">
+      <c r="A41" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B41" s="4" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A42" s="6" t="s">
+      <c r="A42" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="5" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A43" s="6" t="s">
+      <c r="A43" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="5" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A44" s="6" t="s">
+      <c r="A44" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="5" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A45" s="6" t="s">
+      <c r="A45" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="5" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A46" s="6" t="s">
+      <c r="A46" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="5" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A47" s="6" t="s">
+      <c r="A47" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="B47" s="5" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A48" s="6" t="s">
+      <c r="A48" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B48" s="6" t="s">
+      <c r="B48" s="5" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A49" s="6" t="s">
+      <c r="A49" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B49" s="5" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A50" s="6" t="s">
+      <c r="A50" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="5" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A51" s="6" t="s">
+      <c r="A51" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B51" s="6" t="s">
+      <c r="B51" s="5" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A52" s="6" t="s">
+      <c r="A52" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="B52" s="5" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A53" s="6" t="s">
+      <c r="A53" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="B53" s="5" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A54" s="6" t="s">
+      <c r="A54" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="5" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A55" s="6" t="s">
+      <c r="A55" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B55" s="6" t="s">
+      <c r="B55" s="5" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A56" s="6" t="s">
+      <c r="A56" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B56" s="6" t="s">
+      <c r="B56" s="5" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A57" s="6" t="s">
+      <c r="A57" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B57" s="6" t="s">
+      <c r="B57" s="5" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A58" s="6" t="s">
+      <c r="A58" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="5" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A59" s="6" t="s">
+      <c r="A59" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="B59" s="5" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A60" s="6" t="s">
+      <c r="A60" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B60" s="6" t="s">
+      <c r="B60" s="5" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A61" s="6" t="s">
+      <c r="A61" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="6" t="s">
+      <c r="B61" s="5" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A62" s="6" t="s">
+      <c r="A62" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="5" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A63" s="6" t="s">
+      <c r="A63" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B63" s="6" t="s">
+      <c r="B63" s="5" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A64" s="6" t="s">
+      <c r="A64" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B64" s="6" t="s">
+      <c r="B64" s="5" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A65" s="6" t="s">
+      <c r="A65" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B65" s="6" t="s">
+      <c r="B65" s="5" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A66" s="6" t="s">
+      <c r="A66" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B66" s="6" t="s">
+      <c r="B66" s="5" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A67" s="6" t="s">
+      <c r="A67" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B67" s="6" t="s">
+      <c r="B67" s="5" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A68" s="6" t="s">
+      <c r="A68" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B68" s="6" t="s">
+      <c r="B68" s="5" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A69" s="6" t="s">
+      <c r="A69" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B69" s="6" t="s">
+      <c r="B69" s="5" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A70" s="6" t="s">
+      <c r="A70" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="5" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A71" s="6" t="s">
+      <c r="A71" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B71" s="6" t="s">
+      <c r="B71" s="5" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A72" s="6" t="s">
+      <c r="A72" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B72" s="6" t="s">
+      <c r="B72" s="5" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A73" s="6" t="s">
+      <c r="A73" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B73" s="6" t="s">
+      <c r="B73" s="5" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A74" s="6" t="s">
+      <c r="A74" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B74" s="6" t="s">
+      <c r="B74" s="5" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A75" s="6" t="s">
+      <c r="A75" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B75" s="6" t="s">
+      <c r="B75" s="5" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A76" s="6" t="s">
+      <c r="A76" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B76" s="6" t="s">
+      <c r="B76" s="5" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A77" s="6" t="s">
+      <c r="A77" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B77" s="6" t="s">
+      <c r="B77" s="5" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A78" s="6" t="s">
+      <c r="A78" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B78" s="6" t="s">
+      <c r="B78" s="5" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A79" s="6" t="s">
+      <c r="A79" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B79" s="6" t="s">
+      <c r="B79" s="5" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A80" s="6" t="s">
+      <c r="A80" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B80" s="6" t="s">
+      <c r="B80" s="5" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A81" s="6" t="s">
+      <c r="A81" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B81" s="6" t="s">
+      <c r="B81" s="5" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A82" s="6" t="s">
+      <c r="A82" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B82" s="6" t="s">
+      <c r="B82" s="5" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A83" s="6" t="s">
+      <c r="A83" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B83" s="6" t="s">
+      <c r="B83" s="5" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A84" s="6" t="s">
+      <c r="A84" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B84" s="6" t="s">
+      <c r="B84" s="5" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A85" s="6" t="s">
+      <c r="A85" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B85" s="6" t="s">
+      <c r="B85" s="5" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A86" s="6" t="s">
+      <c r="A86" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B86" s="6" t="s">
+      <c r="B86" s="5" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A87" s="6" t="s">
+      <c r="A87" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B87" s="6" t="s">
+      <c r="B87" s="5" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A88" s="6" t="s">
+      <c r="A88" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B88" s="6" t="s">
+      <c r="B88" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A89" s="6" t="s">
+      <c r="A89" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B89" s="6" t="s">
+      <c r="B89" s="5" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A90" s="6" t="s">
+      <c r="A90" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B90" s="6" t="s">
+      <c r="B90" s="5" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A91" s="6" t="s">
+      <c r="A91" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B91" s="6" t="s">
+      <c r="B91" s="5" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A92" s="6" t="s">
+      <c r="A92" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B92" s="6" t="s">
+      <c r="B92" s="5" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A93" s="6" t="s">
+      <c r="A93" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B93" s="6" t="s">
+      <c r="B93" s="5" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A94" s="6" t="s">
+      <c r="A94" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B94" s="6" t="s">
+      <c r="B94" s="5" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A95" s="6" t="s">
+      <c r="A95" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B95" s="6" t="s">
+      <c r="B95" s="5" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A96" s="6" t="s">
+      <c r="A96" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B96" s="6" t="s">
+      <c r="B96" s="5" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A97" s="6" t="s">
+      <c r="A97" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B97" s="6" t="s">
+      <c r="B97" s="5" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A98" s="6" t="s">
+      <c r="A98" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B98" s="6" t="s">
+      <c r="B98" s="5" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A99" s="6" t="s">
+      <c r="A99" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B99" s="6" t="s">
+      <c r="B99" s="5" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A100" s="6" t="s">
+      <c r="A100" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B100" s="6" t="s">
+      <c r="B100" s="5" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A101" s="6" t="s">
+      <c r="A101" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B101" s="6" t="s">
+      <c r="B101" s="5" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A102" s="6" t="s">
+      <c r="A102" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B102" s="6" t="s">
+      <c r="B102" s="5" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A103" s="6" t="s">
+      <c r="A103" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B103" s="6" t="s">
+      <c r="B103" s="5" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A104" s="6" t="s">
+      <c r="A104" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B104" s="6" t="s">
+      <c r="B104" s="5" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A105" s="6" t="s">
+      <c r="A105" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B105" s="6" t="s">
+      <c r="B105" s="5" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A106" s="6" t="s">
+      <c r="A106" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B106" s="6" t="s">
+      <c r="B106" s="5" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A107" s="6" t="s">
+      <c r="A107" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B107" s="6" t="s">
+      <c r="B107" s="5" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A108" s="6" t="s">
+      <c r="A108" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B108" s="6" t="s">
+      <c r="B108" s="5" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A109" s="6" t="s">
+      <c r="A109" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B109" s="6" t="s">
+      <c r="B109" s="5" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A110" s="6" t="s">
+      <c r="A110" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B110" s="6" t="s">
+      <c r="B110" s="5" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A111" s="6" t="s">
+      <c r="A111" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B111" s="6" t="s">
+      <c r="B111" s="5" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A112" s="6" t="s">
+      <c r="A112" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B112" s="6" t="s">
+      <c r="B112" s="5" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A113" s="6" t="s">
+      <c r="A113" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B113" s="6" t="s">
+      <c r="B113" s="5" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A114" s="6" t="s">
+      <c r="A114" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B114" s="6" t="s">
+      <c r="B114" s="5" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A115" s="6" t="s">
+      <c r="A115" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B115" s="6" t="s">
+      <c r="B115" s="5" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A116" s="6" t="s">
+      <c r="A116" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B116" s="6" t="s">
+      <c r="B116" s="5" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A117" s="6" t="s">
+      <c r="A117" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B117" s="6" t="s">
+      <c r="B117" s="5" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A118" s="6" t="s">
+      <c r="A118" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B118" s="6" t="s">
+      <c r="B118" s="5" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A119" s="6" t="s">
+      <c r="A119" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B119" s="6" t="s">
+      <c r="B119" s="5" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A120" s="6" t="s">
+      <c r="A120" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B120" s="6" t="s">
+      <c r="B120" s="5" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A121" s="6" t="s">
+      <c r="A121" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B121" s="6" t="s">
+      <c r="B121" s="5" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A122" s="6" t="s">
+      <c r="A122" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B122" s="6" t="s">
+      <c r="B122" s="5" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A123" s="6" t="s">
+      <c r="A123" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B123" s="6" t="s">
+      <c r="B123" s="5" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A124" s="6" t="s">
+      <c r="A124" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B124" s="6" t="s">
+      <c r="B124" s="5" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A125" s="6" t="s">
+      <c r="A125" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B125" s="6" t="s">
+      <c r="B125" s="5" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A126" s="6" t="s">
+      <c r="A126" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B126" s="6" t="s">
+      <c r="B126" s="5" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A127" s="6" t="s">
+      <c r="A127" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B127" s="6" t="s">
+      <c r="B127" s="5" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A128" s="6" t="s">
+      <c r="A128" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B128" s="6" t="s">
+      <c r="B128" s="5" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A129" s="6" t="s">
+      <c r="A129" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B129" s="6" t="s">
+      <c r="B129" s="5" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A130" s="6" t="s">
+      <c r="A130" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B130" s="6" t="s">
+      <c r="B130" s="5" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A131" s="6" t="s">
+      <c r="A131" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B131" s="6" t="s">
+      <c r="B131" s="5" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A132" s="6" t="s">
+      <c r="A132" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B132" s="6" t="s">
+      <c r="B132" s="5" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A133" s="6" t="s">
+      <c r="A133" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B133" s="6" t="s">
+      <c r="B133" s="5" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A134" s="6" t="s">
+      <c r="A134" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B134" s="6" t="s">
+      <c r="B134" s="5" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A135" s="6" t="s">
+      <c r="A135" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B135" s="6" t="s">
+      <c r="B135" s="5" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A136" s="6" t="s">
+      <c r="A136" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B136" s="6" t="s">
+      <c r="B136" s="5" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A137" s="6" t="s">
+      <c r="A137" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B137" s="6" t="s">
+      <c r="B137" s="5" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A138" s="6" t="s">
+      <c r="A138" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B138" s="6" t="s">
+      <c r="B138" s="5" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A139" s="6" t="s">
+      <c r="A139" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B139" s="6" t="s">
+      <c r="B139" s="5" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A140" s="6" t="s">
+      <c r="A140" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B140" s="6" t="s">
+      <c r="B140" s="5" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A141" s="6" t="s">
+      <c r="A141" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B141" s="6" t="s">
+      <c r="B141" s="5" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A142" s="6" t="s">
+      <c r="A142" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B142" s="6" t="s">
+      <c r="B142" s="5" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A143" s="6" t="s">
+      <c r="A143" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B143" s="6" t="s">
+      <c r="B143" s="5" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A144" s="6" t="s">
+      <c r="A144" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B144" s="6" t="s">
+      <c r="B144" s="5" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A145" s="6" t="s">
+      <c r="A145" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B145" s="6" t="s">
+      <c r="B145" s="5" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A146" s="6" t="s">
+      <c r="A146" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B146" s="6" t="s">
+      <c r="B146" s="5" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A147" s="6" t="s">
+      <c r="A147" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B147" s="6" t="s">
+      <c r="B147" s="5" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A148" s="6" t="s">
+      <c r="A148" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B148" s="6" t="s">
+      <c r="B148" s="5" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A149" s="6" t="s">
+      <c r="A149" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B149" s="6" t="s">
+      <c r="B149" s="5" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A150" s="6" t="s">
+      <c r="A150" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B150" s="6" t="s">
+      <c r="B150" s="5" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A151" s="6" t="s">
+      <c r="A151" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B151" s="6" t="s">
+      <c r="B151" s="5" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A152" s="6" t="s">
+      <c r="A152" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B152" s="6" t="s">
+      <c r="B152" s="5" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A153" s="6" t="s">
+      <c r="A153" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B153" s="6" t="s">
+      <c r="B153" s="5" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A154" s="6" t="s">
+      <c r="A154" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B154" s="6" t="s">
+      <c r="B154" s="5" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A155" s="6" t="s">
+      <c r="A155" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B155" s="6" t="s">
+      <c r="B155" s="5" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A156" s="6" t="s">
+      <c r="A156" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B156" s="6" t="s">
+      <c r="B156" s="5" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A157" s="6" t="s">
+      <c r="A157" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B157" s="6" t="s">
+      <c r="B157" s="5" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A158" s="6" t="s">
+      <c r="A158" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B158" s="6" t="s">
+      <c r="B158" s="5" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A159" s="6" t="s">
+      <c r="A159" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B159" s="6" t="s">
+      <c r="B159" s="5" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A160" s="6" t="s">
+      <c r="A160" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B160" s="6" t="s">
+      <c r="B160" s="5" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A161" s="6" t="s">
+      <c r="A161" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B161" s="6" t="s">
+      <c r="B161" s="5" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A162" s="6" t="s">
+      <c r="A162" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B162" s="6" t="s">
+      <c r="B162" s="5" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A163" s="6" t="s">
+      <c r="A163" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B163" s="6" t="s">
+      <c r="B163" s="5" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A164" s="6" t="s">
+      <c r="A164" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B164" s="6" t="s">
+      <c r="B164" s="5" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A165" s="6" t="s">
+      <c r="A165" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B165" s="6" t="s">
+      <c r="B165" s="5" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A166" s="6" t="s">
+      <c r="A166" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B166" s="6" t="s">
+      <c r="B166" s="5" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A167" s="6" t="s">
+      <c r="A167" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B167" s="6" t="s">
+      <c r="B167" s="5" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A168" s="6" t="s">
+      <c r="A168" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B168" s="6" t="s">
+      <c r="B168" s="5" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A169" s="6" t="s">
+      <c r="A169" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B169" s="6" t="s">
+      <c r="B169" s="5" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A170" s="6" t="s">
+      <c r="A170" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B170" s="6" t="s">
+      <c r="B170" s="5" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A171" s="6" t="s">
+      <c r="A171" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B171" s="6" t="s">
+      <c r="B171" s="5" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A172" s="6" t="s">
+      <c r="A172" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B172" s="6" t="s">
+      <c r="B172" s="5" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A173" s="6" t="s">
+      <c r="A173" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B173" s="6" t="s">
+      <c r="B173" s="5" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A174" s="6" t="s">
+      <c r="A174" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B174" s="6" t="s">
+      <c r="B174" s="5" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A175" s="6" t="s">
+      <c r="A175" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B175" s="6" t="s">
+      <c r="B175" s="5" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A176" s="6" t="s">
+      <c r="A176" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B176" s="6" t="s">
+      <c r="B176" s="5" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A177" s="6" t="s">
+      <c r="A177" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B177" s="6" t="s">
+      <c r="B177" s="5" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A178" s="6" t="s">
+      <c r="A178" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B178" s="6" t="s">
+      <c r="B178" s="5" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A179" s="6" t="s">
+      <c r="A179" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B179" s="6" t="s">
+      <c r="B179" s="5" t="s">
         <v>242</v>
       </c>
     </row>
@@ -9150,19 +9160,19 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" s="10">
+        <v>1</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="4">
-        <v>46244</v>
-      </c>
-      <c r="D2" s="11">
+      <c r="C2" s="11" t="s">
+        <v>716</v>
+      </c>
+      <c r="D2" s="12">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E2" s="11">
+      <c r="E2" s="12">
         <v>0.97916666666666663</v>
       </c>
     </row>

--- a/data/KTTX_TIN12.xlsx
+++ b/data/KTTX_TIN12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WEBH2T\GITHUB 2026\KIEM TRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF038625-F681-4B55-8CA7-88D6F13B90E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{044E1C91-77ED-45DE-94B3-6A17CD7537CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2188,7 +2188,7 @@
     <t>Q0429</t>
   </si>
   <si>
-    <t>8/10/2026</t>
+    <t>08/10/2026</t>
   </si>
 </sst>
 </file>
@@ -2292,10 +2292,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2864,7 +2864,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="75" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="62.5" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>574</v>
       </c>
@@ -3280,7 +3280,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="87.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" ht="75" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>587</v>
       </c>
@@ -9138,7 +9138,9 @@
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="4" width="10" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
     <col min="5" max="5" width="10.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9166,13 +9168,13 @@
       <c r="B2" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="12" t="s">
         <v>716</v>
       </c>
-      <c r="D2" s="12">
+      <c r="D2" s="11">
         <v>0.29166666666666669</v>
       </c>
-      <c r="E2" s="12">
+      <c r="E2" s="11">
         <v>0.97916666666666663</v>
       </c>
     </row>

--- a/data/KTTX_TIN12.xlsx
+++ b/data/KTTX_TIN12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WEBH2T\GITHUB 2026\KIEM TRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{044E1C91-77ED-45DE-94B3-6A17CD7537CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07E285FA-F7B9-42D8-B7D7-8A8240A98B08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1714" uniqueCount="717">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1713" uniqueCount="716">
   <si>
     <t>Mục</t>
   </si>
@@ -2186,15 +2186,15 @@
   </si>
   <si>
     <t>Q0429</t>
-  </si>
-  <si>
-    <t>08/10/2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="m/d/yyyy;@"/>
+  </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2295,7 +2295,7 @@
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -9168,8 +9168,8 @@
       <c r="B2" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="12" t="s">
-        <v>716</v>
+      <c r="C2" s="12">
+        <v>46303</v>
       </c>
       <c r="D2" s="11">
         <v>0.29166666666666669</v>

--- a/data/KTTX_TIN12.xlsx
+++ b/data/KTTX_TIN12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WEBH2T\GITHUB 2026\KIEM TRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07E285FA-F7B9-42D8-B7D7-8A8240A98B08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFD65273-50A5-4038-B64E-B662998E9F6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2193,7 +2193,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="m/d/yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="m/d/yyyy;@"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -2295,7 +2295,7 @@
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -9169,7 +9169,7 @@
         <v>63</v>
       </c>
       <c r="C2" s="12">
-        <v>46303</v>
+        <v>46244</v>
       </c>
       <c r="D2" s="11">
         <v>0.29166666666666669</v>

--- a/data/KTTX_TIN12.xlsx
+++ b/data/KTTX_TIN12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WEBH2T\GITHUB 2026\KIEM TRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFD65273-50A5-4038-B64E-B662998E9F6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB7B16A5-D82B-4359-942A-109F683866B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1713" uniqueCount="716">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1714" uniqueCount="717">
   <si>
     <t>Mục</t>
   </si>
@@ -2186,15 +2186,15 @@
   </si>
   <si>
     <t>Q0429</t>
+  </si>
+  <si>
+    <t>8/10/2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="m/d/yyyy;@"/>
-  </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2290,13 +2290,13 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9168,8 +9168,8 @@
       <c r="B2" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="12">
-        <v>46244</v>
+      <c r="C2" s="12" t="s">
+        <v>716</v>
       </c>
       <c r="D2" s="11">
         <v>0.29166666666666669</v>

--- a/data/KTTX_TIN12.xlsx
+++ b/data/KTTX_TIN12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tdtam\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DB56BFA-6D81-46ED-A4BF-C6FF80DA7C01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F20214C-AE8E-4B72-974B-B64ECBE9985C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1099" uniqueCount="682">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="682">
   <si>
     <t>QID</t>
   </si>
@@ -234,12 +234,6 @@
     <t>SMTP</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3f/NetworkTopology-Star.svg/320px-NetworkTopology-Star.svg.png</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b1/Ethernet_RJ45_connector_p1160054.jpg/320px-Ethernet_RJ45_connector_p1160054.jpg</t>
-  </si>
-  <si>
     <t>Q002</t>
   </si>
   <si>
@@ -258,9 +252,6 @@
     <t>Cổng ứng dụng</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/37/MAC_address.svg/320px-MAC_address.svg.png</t>
-  </si>
-  <si>
     <t>Q003</t>
   </si>
   <si>
@@ -276,9 +267,6 @@
     <t>IMAP</t>
   </si>
   <si>
-    <t>https://www.youtube.com/watch?v=PpsEaqJV_A0</t>
-  </si>
-  <si>
     <t>Q004</t>
   </si>
   <si>
@@ -2083,13 +2071,25 @@
   </si>
   <si>
     <t>Kiểm tra: Điểm lưu − Điểm tính lại. Chênh lệch ≠ 0 → cần xem lại.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://webh2t.github.io/assets/tin12/DNS.png </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/webh2t/webh2t.github.io/blob/main/assets/tin12/ipv4.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://webh2t.github.io/assets/tin12/Ethernet.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=PpsEaqJV_A0 </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2126,6 +2126,14 @@
       <sz val="11"/>
       <color rgb="FF0D9488"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="14">
@@ -2235,10 +2243,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -2285,8 +2294,15 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2841,7 +2857,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="17" t="s">
         <v>58</v>
       </c>
@@ -2872,20 +2888,20 @@
       <c r="J2" s="17">
         <v>0.25</v>
       </c>
-      <c r="K2" s="18" t="s">
-        <v>65</v>
+      <c r="K2" s="23" t="s">
+        <v>680</v>
       </c>
       <c r="L2" s="17"/>
-      <c r="M2" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="N2" s="17"/>
+      <c r="M2" s="18"/>
+      <c r="N2" s="22" t="s">
+        <v>678</v>
+      </c>
       <c r="O2" s="17"/>
       <c r="P2" s="17"/>
     </row>
-    <row r="3" spans="1:16" ht="58" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" s="17" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B3" s="17">
         <v>1</v>
@@ -2894,19 +2910,19 @@
         <v>59</v>
       </c>
       <c r="D3" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="F3" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="G3" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="H3" s="17" t="s">
         <v>70</v>
-      </c>
-      <c r="G3" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="H3" s="17" t="s">
-        <v>72</v>
       </c>
       <c r="I3" s="17" t="s">
         <v>9</v>
@@ -2914,9 +2930,7 @@
       <c r="J3" s="17">
         <v>0.25</v>
       </c>
-      <c r="K3" s="18" t="s">
-        <v>73</v>
-      </c>
+      <c r="K3" s="18"/>
       <c r="L3" s="17"/>
       <c r="M3" s="17"/>
       <c r="N3" s="17"/>
@@ -2925,7 +2939,7 @@
     </row>
     <row r="4" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="17" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B4" s="17">
         <v>1</v>
@@ -2934,19 +2948,19 @@
         <v>59</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F4" s="17" t="s">
         <v>62</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="I4" s="17" t="s">
         <v>8</v>
@@ -2955,8 +2969,8 @@
         <v>0.25</v>
       </c>
       <c r="K4" s="17"/>
-      <c r="L4" s="18" t="s">
-        <v>79</v>
+      <c r="L4" s="23" t="s">
+        <v>681</v>
       </c>
       <c r="M4" s="17"/>
       <c r="N4" s="17"/>
@@ -2965,7 +2979,7 @@
     </row>
     <row r="5" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A5" s="17" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B5" s="17">
         <v>1</v>
@@ -2974,19 +2988,19 @@
         <v>59</v>
       </c>
       <c r="D5" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="H5" s="17" t="s">
         <v>81</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="F5" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="G5" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="H5" s="17" t="s">
-        <v>85</v>
       </c>
       <c r="I5" s="17" t="s">
         <v>8</v>
@@ -3003,7 +3017,7 @@
     </row>
     <row r="6" spans="1:16" ht="58" x14ac:dyDescent="0.35">
       <c r="A6" s="17" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B6" s="17">
         <v>1</v>
@@ -3012,19 +3026,19 @@
         <v>59</v>
       </c>
       <c r="D6" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H6" s="17" t="s">
         <v>87</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="G6" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="H6" s="17" t="s">
-        <v>91</v>
       </c>
       <c r="I6" s="17" t="s">
         <v>8</v>
@@ -3041,7 +3055,7 @@
     </row>
     <row r="7" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A7" s="17" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B7" s="17">
         <v>1</v>
@@ -3050,19 +3064,19 @@
         <v>59</v>
       </c>
       <c r="D7" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="H7" s="17" t="s">
         <v>93</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="F7" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="H7" s="17" t="s">
-        <v>97</v>
       </c>
       <c r="I7" s="17" t="s">
         <v>8</v>
@@ -3079,7 +3093,7 @@
     </row>
     <row r="8" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="17" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B8" s="17">
         <v>1</v>
@@ -3088,19 +3102,19 @@
         <v>59</v>
       </c>
       <c r="D8" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="H8" s="17" t="s">
         <v>99</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="F8" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="G8" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="H8" s="17" t="s">
-        <v>103</v>
       </c>
       <c r="I8" s="17" t="s">
         <v>8</v>
@@ -3117,7 +3131,7 @@
     </row>
     <row r="9" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A9" s="17" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B9" s="17">
         <v>1</v>
@@ -3126,19 +3140,19 @@
         <v>59</v>
       </c>
       <c r="D9" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="H9" s="17" t="s">
         <v>105</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="F9" s="17" t="s">
-        <v>107</v>
-      </c>
-      <c r="G9" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="H9" s="17" t="s">
-        <v>109</v>
       </c>
       <c r="I9" s="17" t="s">
         <v>9</v>
@@ -3155,7 +3169,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" s="17" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B10" s="17">
         <v>1</v>
@@ -3164,19 +3178,19 @@
         <v>59</v>
       </c>
       <c r="D10" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="H10" s="17" t="s">
         <v>111</v>
-      </c>
-      <c r="E10" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="F10" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="G10" s="17" t="s">
-        <v>114</v>
-      </c>
-      <c r="H10" s="17" t="s">
-        <v>115</v>
       </c>
       <c r="I10" s="17" t="s">
         <v>10</v>
@@ -3193,7 +3207,7 @@
     </row>
     <row r="11" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A11" s="17" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B11" s="17">
         <v>1</v>
@@ -3202,7 +3216,7 @@
         <v>59</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E11" s="17" t="s">
         <v>62</v>
@@ -3211,7 +3225,7 @@
         <v>61</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="H11" s="17" t="s">
         <v>64</v>
@@ -3231,7 +3245,7 @@
     </row>
     <row r="12" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A12" s="17" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B12" s="17">
         <v>1</v>
@@ -3240,19 +3254,19 @@
         <v>59</v>
       </c>
       <c r="D12" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="H12" s="17" t="s">
         <v>119</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="F12" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="G12" s="17" t="s">
-        <v>122</v>
-      </c>
-      <c r="H12" s="17" t="s">
-        <v>123</v>
       </c>
       <c r="I12" s="17" t="s">
         <v>8</v>
@@ -3269,7 +3283,7 @@
     </row>
     <row r="13" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A13" s="17" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B13" s="17">
         <v>1</v>
@@ -3278,19 +3292,19 @@
         <v>59</v>
       </c>
       <c r="D13" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="G13" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="H13" s="17" t="s">
         <v>125</v>
-      </c>
-      <c r="E13" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="F13" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="G13" s="17" t="s">
-        <v>128</v>
-      </c>
-      <c r="H13" s="17" t="s">
-        <v>129</v>
       </c>
       <c r="I13" s="17" t="s">
         <v>8</v>
@@ -3307,7 +3321,7 @@
     </row>
     <row r="14" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" s="17" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B14" s="17">
         <v>1</v>
@@ -3316,19 +3330,19 @@
         <v>59</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E14" s="17" t="s">
         <v>63</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G14" s="17" t="s">
         <v>62</v>
       </c>
       <c r="H14" s="17" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I14" s="17" t="s">
         <v>8</v>
@@ -3345,7 +3359,7 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A15" s="17" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B15" s="17">
         <v>1</v>
@@ -3354,10 +3368,10 @@
         <v>59</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="F15" s="17" t="s">
         <v>64</v>
@@ -3381,9 +3395,9 @@
       <c r="O15" s="17"/>
       <c r="P15" s="17"/>
     </row>
-    <row r="16" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:16" ht="58" x14ac:dyDescent="0.35">
       <c r="A16" s="17" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B16" s="17">
         <v>1</v>
@@ -3392,19 +3406,19 @@
         <v>59</v>
       </c>
       <c r="D16" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="F16" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="G16" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="H16" s="17" t="s">
         <v>136</v>
-      </c>
-      <c r="E16" s="17" t="s">
-        <v>137</v>
-      </c>
-      <c r="F16" s="17" t="s">
-        <v>138</v>
-      </c>
-      <c r="G16" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="H16" s="17" t="s">
-        <v>140</v>
       </c>
       <c r="I16" s="17" t="s">
         <v>9</v>
@@ -3412,7 +3426,9 @@
       <c r="J16" s="17">
         <v>0.25</v>
       </c>
-      <c r="K16" s="17"/>
+      <c r="K16" s="22" t="s">
+        <v>679</v>
+      </c>
       <c r="L16" s="17"/>
       <c r="M16" s="17"/>
       <c r="N16" s="17"/>
@@ -3421,7 +3437,7 @@
     </row>
     <row r="17" spans="1:16" ht="58" x14ac:dyDescent="0.35">
       <c r="A17" s="17" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B17" s="17">
         <v>1</v>
@@ -3430,19 +3446,19 @@
         <v>59</v>
       </c>
       <c r="D17" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="F17" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="G17" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="H17" s="17" t="s">
         <v>142</v>
-      </c>
-      <c r="E17" s="17" t="s">
-        <v>143</v>
-      </c>
-      <c r="F17" s="17" t="s">
-        <v>144</v>
-      </c>
-      <c r="G17" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="H17" s="17" t="s">
-        <v>146</v>
       </c>
       <c r="I17" s="17" t="s">
         <v>8</v>
@@ -3459,7 +3475,7 @@
     </row>
     <row r="18" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A18" s="17" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B18" s="17">
         <v>1</v>
@@ -3468,19 +3484,19 @@
         <v>59</v>
       </c>
       <c r="D18" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="F18" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="G18" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="H18" s="17" t="s">
         <v>148</v>
-      </c>
-      <c r="E18" s="17" t="s">
-        <v>149</v>
-      </c>
-      <c r="F18" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="G18" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="H18" s="17" t="s">
-        <v>152</v>
       </c>
       <c r="I18" s="17" t="s">
         <v>8</v>
@@ -3497,7 +3513,7 @@
     </row>
     <row r="19" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A19" s="17" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B19" s="17">
         <v>1</v>
@@ -3506,19 +3522,19 @@
         <v>59</v>
       </c>
       <c r="D19" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="F19" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="G19" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="H19" s="17" t="s">
         <v>154</v>
-      </c>
-      <c r="E19" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="F19" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="G19" s="17" t="s">
-        <v>157</v>
-      </c>
-      <c r="H19" s="17" t="s">
-        <v>158</v>
       </c>
       <c r="I19" s="17" t="s">
         <v>8</v>
@@ -3526,7 +3542,9 @@
       <c r="J19" s="17">
         <v>0.25</v>
       </c>
-      <c r="K19" s="17"/>
+      <c r="K19" s="22" t="s">
+        <v>678</v>
+      </c>
       <c r="L19" s="17"/>
       <c r="M19" s="17"/>
       <c r="N19" s="17"/>
@@ -3535,7 +3553,7 @@
     </row>
     <row r="20" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A20" s="17" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B20" s="17">
         <v>1</v>
@@ -3544,19 +3562,19 @@
         <v>59</v>
       </c>
       <c r="D20" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="G20" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="H20" s="17" t="s">
         <v>160</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>161</v>
-      </c>
-      <c r="F20" s="17" t="s">
-        <v>162</v>
-      </c>
-      <c r="G20" s="17" t="s">
-        <v>163</v>
-      </c>
-      <c r="H20" s="17" t="s">
-        <v>164</v>
       </c>
       <c r="I20" s="17" t="s">
         <v>8</v>
@@ -3573,7 +3591,7 @@
     </row>
     <row r="21" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A21" s="17" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B21" s="17">
         <v>1</v>
@@ -3582,19 +3600,19 @@
         <v>59</v>
       </c>
       <c r="D21" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="F21" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="G21" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="H21" s="17" t="s">
         <v>166</v>
-      </c>
-      <c r="E21" s="17" t="s">
-        <v>167</v>
-      </c>
-      <c r="F21" s="17" t="s">
-        <v>168</v>
-      </c>
-      <c r="G21" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="H21" s="17" t="s">
-        <v>170</v>
       </c>
       <c r="I21" s="17" t="s">
         <v>8</v>
@@ -3611,7 +3629,7 @@
     </row>
     <row r="22" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" s="17" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B22" s="17">
         <v>1</v>
@@ -3620,19 +3638,19 @@
         <v>59</v>
       </c>
       <c r="D22" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="F22" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="G22" s="17" t="s">
+        <v>171</v>
+      </c>
+      <c r="H22" s="17" t="s">
         <v>172</v>
-      </c>
-      <c r="E22" s="17" t="s">
-        <v>173</v>
-      </c>
-      <c r="F22" s="17" t="s">
-        <v>174</v>
-      </c>
-      <c r="G22" s="17" t="s">
-        <v>175</v>
-      </c>
-      <c r="H22" s="17" t="s">
-        <v>176</v>
       </c>
       <c r="I22" s="17" t="s">
         <v>8</v>
@@ -3649,7 +3667,7 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A23" s="17" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B23" s="17">
         <v>1</v>
@@ -3658,19 +3676,19 @@
         <v>59</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F23" s="17" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="G23" s="17" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H23" s="17" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="I23" s="17" t="s">
         <v>10</v>
@@ -3687,7 +3705,7 @@
     </row>
     <row r="24" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" s="17" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B24" s="17">
         <v>1</v>
@@ -3696,19 +3714,19 @@
         <v>59</v>
       </c>
       <c r="D24" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>177</v>
+      </c>
+      <c r="F24" s="17" t="s">
+        <v>178</v>
+      </c>
+      <c r="G24" s="17" t="s">
+        <v>179</v>
+      </c>
+      <c r="H24" s="17" t="s">
         <v>180</v>
-      </c>
-      <c r="E24" s="17" t="s">
-        <v>181</v>
-      </c>
-      <c r="F24" s="17" t="s">
-        <v>182</v>
-      </c>
-      <c r="G24" s="17" t="s">
-        <v>183</v>
-      </c>
-      <c r="H24" s="17" t="s">
-        <v>184</v>
       </c>
       <c r="I24" s="17" t="s">
         <v>8</v>
@@ -3725,7 +3743,7 @@
     </row>
     <row r="25" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A25" s="17" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B25" s="17">
         <v>1</v>
@@ -3734,19 +3752,19 @@
         <v>59</v>
       </c>
       <c r="D25" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="E25" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="F25" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="G25" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="H25" s="17" t="s">
         <v>186</v>
-      </c>
-      <c r="E25" s="17" t="s">
-        <v>187</v>
-      </c>
-      <c r="F25" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="G25" s="17" t="s">
-        <v>189</v>
-      </c>
-      <c r="H25" s="17" t="s">
-        <v>190</v>
       </c>
       <c r="I25" s="17" t="s">
         <v>8</v>
@@ -3763,7 +3781,7 @@
     </row>
     <row r="26" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A26" s="17" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B26" s="17">
         <v>1</v>
@@ -3772,16 +3790,16 @@
         <v>59</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F26" s="17" t="s">
         <v>64</v>
       </c>
       <c r="G26" s="17" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="H26" s="17" t="s">
         <v>63</v>
@@ -3801,7 +3819,7 @@
     </row>
     <row r="27" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A27" s="17" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B27" s="17">
         <v>1</v>
@@ -3810,19 +3828,19 @@
         <v>59</v>
       </c>
       <c r="D27" s="17" t="s">
+        <v>191</v>
+      </c>
+      <c r="E27" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="F27" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="G27" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="H27" s="17" t="s">
         <v>195</v>
-      </c>
-      <c r="E27" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="F27" s="17" t="s">
-        <v>197</v>
-      </c>
-      <c r="G27" s="17" t="s">
-        <v>198</v>
-      </c>
-      <c r="H27" s="17" t="s">
-        <v>199</v>
       </c>
       <c r="I27" s="17" t="s">
         <v>8</v>
@@ -3839,7 +3857,7 @@
     </row>
     <row r="28" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A28" s="17" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B28" s="17">
         <v>1</v>
@@ -3848,19 +3866,19 @@
         <v>59</v>
       </c>
       <c r="D28" s="17" t="s">
+        <v>197</v>
+      </c>
+      <c r="E28" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="F28" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="G28" s="17" t="s">
+        <v>200</v>
+      </c>
+      <c r="H28" s="17" t="s">
         <v>201</v>
-      </c>
-      <c r="E28" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="F28" s="17" t="s">
-        <v>203</v>
-      </c>
-      <c r="G28" s="17" t="s">
-        <v>204</v>
-      </c>
-      <c r="H28" s="17" t="s">
-        <v>205</v>
       </c>
       <c r="I28" s="17" t="s">
         <v>8</v>
@@ -3877,7 +3895,7 @@
     </row>
     <row r="29" spans="1:16" ht="87" x14ac:dyDescent="0.35">
       <c r="A29" s="17" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B29" s="17">
         <v>1</v>
@@ -3886,19 +3904,19 @@
         <v>59</v>
       </c>
       <c r="D29" s="17" t="s">
+        <v>203</v>
+      </c>
+      <c r="E29" s="17" t="s">
+        <v>204</v>
+      </c>
+      <c r="F29" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="G29" s="17" t="s">
+        <v>206</v>
+      </c>
+      <c r="H29" s="17" t="s">
         <v>207</v>
-      </c>
-      <c r="E29" s="17" t="s">
-        <v>208</v>
-      </c>
-      <c r="F29" s="17" t="s">
-        <v>209</v>
-      </c>
-      <c r="G29" s="17" t="s">
-        <v>210</v>
-      </c>
-      <c r="H29" s="17" t="s">
-        <v>211</v>
       </c>
       <c r="I29" s="17" t="s">
         <v>8</v>
@@ -3915,7 +3933,7 @@
     </row>
     <row r="30" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A30" s="17" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B30" s="17">
         <v>1</v>
@@ -3924,19 +3942,19 @@
         <v>59</v>
       </c>
       <c r="D30" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="E30" s="17" t="s">
+        <v>210</v>
+      </c>
+      <c r="F30" s="17" t="s">
+        <v>211</v>
+      </c>
+      <c r="G30" s="17" t="s">
+        <v>212</v>
+      </c>
+      <c r="H30" s="17" t="s">
         <v>213</v>
-      </c>
-      <c r="E30" s="17" t="s">
-        <v>214</v>
-      </c>
-      <c r="F30" s="17" t="s">
-        <v>215</v>
-      </c>
-      <c r="G30" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="H30" s="17" t="s">
-        <v>217</v>
       </c>
       <c r="I30" s="17" t="s">
         <v>8</v>
@@ -3953,7 +3971,7 @@
     </row>
     <row r="31" spans="1:16" ht="58" x14ac:dyDescent="0.35">
       <c r="A31" s="17" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B31" s="17">
         <v>1</v>
@@ -3962,19 +3980,19 @@
         <v>59</v>
       </c>
       <c r="D31" s="17" t="s">
+        <v>215</v>
+      </c>
+      <c r="E31" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="F31" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="G31" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="H31" s="17" t="s">
         <v>219</v>
-      </c>
-      <c r="E31" s="17" t="s">
-        <v>220</v>
-      </c>
-      <c r="F31" s="17" t="s">
-        <v>221</v>
-      </c>
-      <c r="G31" s="17" t="s">
-        <v>222</v>
-      </c>
-      <c r="H31" s="17" t="s">
-        <v>223</v>
       </c>
       <c r="I31" s="17" t="s">
         <v>8</v>
@@ -3991,7 +4009,7 @@
     </row>
     <row r="32" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A32" s="17" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B32" s="17">
         <v>1</v>
@@ -4000,19 +4018,19 @@
         <v>59</v>
       </c>
       <c r="D32" s="17" t="s">
+        <v>221</v>
+      </c>
+      <c r="E32" s="17" t="s">
+        <v>222</v>
+      </c>
+      <c r="F32" s="17" t="s">
+        <v>223</v>
+      </c>
+      <c r="G32" s="17" t="s">
+        <v>224</v>
+      </c>
+      <c r="H32" s="17" t="s">
         <v>225</v>
-      </c>
-      <c r="E32" s="17" t="s">
-        <v>226</v>
-      </c>
-      <c r="F32" s="17" t="s">
-        <v>227</v>
-      </c>
-      <c r="G32" s="17" t="s">
-        <v>228</v>
-      </c>
-      <c r="H32" s="17" t="s">
-        <v>229</v>
       </c>
       <c r="I32" s="17" t="s">
         <v>8</v>
@@ -4029,7 +4047,7 @@
     </row>
     <row r="33" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A33" s="17" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B33" s="17">
         <v>1</v>
@@ -4038,19 +4056,19 @@
         <v>59</v>
       </c>
       <c r="D33" s="17" t="s">
+        <v>227</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>228</v>
+      </c>
+      <c r="F33" s="17" t="s">
+        <v>229</v>
+      </c>
+      <c r="G33" s="17" t="s">
+        <v>230</v>
+      </c>
+      <c r="H33" s="17" t="s">
         <v>231</v>
-      </c>
-      <c r="E33" s="17" t="s">
-        <v>232</v>
-      </c>
-      <c r="F33" s="17" t="s">
-        <v>233</v>
-      </c>
-      <c r="G33" s="17" t="s">
-        <v>234</v>
-      </c>
-      <c r="H33" s="17" t="s">
-        <v>235</v>
       </c>
       <c r="I33" s="17" t="s">
         <v>8</v>
@@ -4067,7 +4085,7 @@
     </row>
     <row r="34" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A34" s="17" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B34" s="17">
         <v>1</v>
@@ -4076,19 +4094,19 @@
         <v>59</v>
       </c>
       <c r="D34" s="17" t="s">
+        <v>233</v>
+      </c>
+      <c r="E34" s="17" t="s">
+        <v>234</v>
+      </c>
+      <c r="F34" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="G34" s="17" t="s">
+        <v>236</v>
+      </c>
+      <c r="H34" s="17" t="s">
         <v>237</v>
-      </c>
-      <c r="E34" s="17" t="s">
-        <v>238</v>
-      </c>
-      <c r="F34" s="17" t="s">
-        <v>239</v>
-      </c>
-      <c r="G34" s="17" t="s">
-        <v>240</v>
-      </c>
-      <c r="H34" s="17" t="s">
-        <v>241</v>
       </c>
       <c r="I34" s="17" t="s">
         <v>8</v>
@@ -4105,7 +4123,7 @@
     </row>
     <row r="35" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A35" s="17" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="B35" s="17">
         <v>1</v>
@@ -4114,19 +4132,19 @@
         <v>59</v>
       </c>
       <c r="D35" s="17" t="s">
+        <v>239</v>
+      </c>
+      <c r="E35" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="F35" s="17" t="s">
+        <v>241</v>
+      </c>
+      <c r="G35" s="17" t="s">
+        <v>242</v>
+      </c>
+      <c r="H35" s="17" t="s">
         <v>243</v>
-      </c>
-      <c r="E35" s="17" t="s">
-        <v>244</v>
-      </c>
-      <c r="F35" s="17" t="s">
-        <v>245</v>
-      </c>
-      <c r="G35" s="17" t="s">
-        <v>246</v>
-      </c>
-      <c r="H35" s="17" t="s">
-        <v>247</v>
       </c>
       <c r="I35" s="17" t="s">
         <v>8</v>
@@ -4143,7 +4161,7 @@
     </row>
     <row r="36" spans="1:16" ht="58" x14ac:dyDescent="0.35">
       <c r="A36" s="17" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="B36" s="17">
         <v>1</v>
@@ -4152,19 +4170,19 @@
         <v>59</v>
       </c>
       <c r="D36" s="17" t="s">
+        <v>245</v>
+      </c>
+      <c r="E36" s="17" t="s">
+        <v>246</v>
+      </c>
+      <c r="F36" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="G36" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="H36" s="17" t="s">
         <v>249</v>
-      </c>
-      <c r="E36" s="17" t="s">
-        <v>250</v>
-      </c>
-      <c r="F36" s="17" t="s">
-        <v>251</v>
-      </c>
-      <c r="G36" s="17" t="s">
-        <v>252</v>
-      </c>
-      <c r="H36" s="17" t="s">
-        <v>253</v>
       </c>
       <c r="I36" s="17" t="s">
         <v>8</v>
@@ -4181,7 +4199,7 @@
     </row>
     <row r="37" spans="1:16" ht="58" x14ac:dyDescent="0.35">
       <c r="A37" s="17" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B37" s="17">
         <v>1</v>
@@ -4190,19 +4208,19 @@
         <v>59</v>
       </c>
       <c r="D37" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="E37" s="17" t="s">
+        <v>252</v>
+      </c>
+      <c r="F37" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="G37" s="17" t="s">
+        <v>254</v>
+      </c>
+      <c r="H37" s="17" t="s">
         <v>255</v>
-      </c>
-      <c r="E37" s="17" t="s">
-        <v>256</v>
-      </c>
-      <c r="F37" s="17" t="s">
-        <v>257</v>
-      </c>
-      <c r="G37" s="17" t="s">
-        <v>258</v>
-      </c>
-      <c r="H37" s="17" t="s">
-        <v>259</v>
       </c>
       <c r="I37" s="17" t="s">
         <v>8</v>
@@ -4219,7 +4237,7 @@
     </row>
     <row r="38" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A38" s="17" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B38" s="17">
         <v>1</v>
@@ -4228,16 +4246,16 @@
         <v>59</v>
       </c>
       <c r="D38" s="17" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="E38" s="17" t="s">
         <v>64</v>
       </c>
       <c r="F38" s="17" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="G38" s="17" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H38" s="17" t="s">
         <v>62</v>
@@ -4257,7 +4275,7 @@
     </row>
     <row r="39" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A39" s="17" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B39" s="17">
         <v>1</v>
@@ -4266,19 +4284,19 @@
         <v>59</v>
       </c>
       <c r="D39" s="17" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="E39" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="F39" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="G39" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="H39" s="17" t="s">
         <v>70</v>
-      </c>
-      <c r="F39" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="G39" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="H39" s="17" t="s">
-        <v>72</v>
       </c>
       <c r="I39" s="17" t="s">
         <v>8</v>
@@ -4295,7 +4313,7 @@
     </row>
     <row r="40" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A40" s="17" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B40" s="17">
         <v>1</v>
@@ -4304,10 +4322,10 @@
         <v>59</v>
       </c>
       <c r="D40" s="17" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="E40" s="17" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F40" s="17" t="s">
         <v>64</v>
@@ -4316,7 +4334,7 @@
         <v>63</v>
       </c>
       <c r="H40" s="17" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I40" s="17" t="s">
         <v>8</v>
@@ -4333,7 +4351,7 @@
     </row>
     <row r="41" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A41" s="17" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B41" s="17">
         <v>1</v>
@@ -4342,19 +4360,19 @@
         <v>59</v>
       </c>
       <c r="D41" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="E41" s="17" t="s">
+        <v>264</v>
+      </c>
+      <c r="F41" s="17" t="s">
+        <v>265</v>
+      </c>
+      <c r="G41" s="17" t="s">
+        <v>266</v>
+      </c>
+      <c r="H41" s="17" t="s">
         <v>267</v>
-      </c>
-      <c r="E41" s="17" t="s">
-        <v>268</v>
-      </c>
-      <c r="F41" s="17" t="s">
-        <v>269</v>
-      </c>
-      <c r="G41" s="17" t="s">
-        <v>270</v>
-      </c>
-      <c r="H41" s="17" t="s">
-        <v>271</v>
       </c>
       <c r="I41" s="17" t="s">
         <v>8</v>
@@ -4371,7 +4389,7 @@
     </row>
     <row r="42" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A42" s="17" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B42" s="17">
         <v>1</v>
@@ -4380,19 +4398,19 @@
         <v>59</v>
       </c>
       <c r="D42" s="17" t="s">
+        <v>269</v>
+      </c>
+      <c r="E42" s="17" t="s">
+        <v>270</v>
+      </c>
+      <c r="F42" s="17" t="s">
+        <v>271</v>
+      </c>
+      <c r="G42" s="17" t="s">
+        <v>272</v>
+      </c>
+      <c r="H42" s="17" t="s">
         <v>273</v>
-      </c>
-      <c r="E42" s="17" t="s">
-        <v>274</v>
-      </c>
-      <c r="F42" s="17" t="s">
-        <v>275</v>
-      </c>
-      <c r="G42" s="17" t="s">
-        <v>276</v>
-      </c>
-      <c r="H42" s="17" t="s">
-        <v>277</v>
       </c>
       <c r="I42" s="17" t="s">
         <v>8</v>
@@ -4409,7 +4427,7 @@
     </row>
     <row r="43" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A43" s="17" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B43" s="17">
         <v>1</v>
@@ -4418,19 +4436,19 @@
         <v>59</v>
       </c>
       <c r="D43" s="17" t="s">
+        <v>275</v>
+      </c>
+      <c r="E43" s="17" t="s">
+        <v>276</v>
+      </c>
+      <c r="F43" s="17" t="s">
+        <v>277</v>
+      </c>
+      <c r="G43" s="17" t="s">
+        <v>278</v>
+      </c>
+      <c r="H43" s="17" t="s">
         <v>279</v>
-      </c>
-      <c r="E43" s="17" t="s">
-        <v>280</v>
-      </c>
-      <c r="F43" s="17" t="s">
-        <v>281</v>
-      </c>
-      <c r="G43" s="17" t="s">
-        <v>282</v>
-      </c>
-      <c r="H43" s="17" t="s">
-        <v>283</v>
       </c>
       <c r="I43" s="17" t="s">
         <v>8</v>
@@ -4447,7 +4465,7 @@
     </row>
     <row r="44" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A44" s="17" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B44" s="17">
         <v>1</v>
@@ -4456,19 +4474,19 @@
         <v>59</v>
       </c>
       <c r="D44" s="17" t="s">
+        <v>281</v>
+      </c>
+      <c r="E44" s="17" t="s">
+        <v>282</v>
+      </c>
+      <c r="F44" s="17" t="s">
+        <v>283</v>
+      </c>
+      <c r="G44" s="17" t="s">
+        <v>284</v>
+      </c>
+      <c r="H44" s="17" t="s">
         <v>285</v>
-      </c>
-      <c r="E44" s="17" t="s">
-        <v>286</v>
-      </c>
-      <c r="F44" s="17" t="s">
-        <v>287</v>
-      </c>
-      <c r="G44" s="17" t="s">
-        <v>288</v>
-      </c>
-      <c r="H44" s="17" t="s">
-        <v>289</v>
       </c>
       <c r="I44" s="17" t="s">
         <v>8</v>
@@ -4485,7 +4503,7 @@
     </row>
     <row r="45" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A45" s="17" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B45" s="17">
         <v>1</v>
@@ -4494,19 +4512,19 @@
         <v>59</v>
       </c>
       <c r="D45" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="E45" s="17" t="s">
+        <v>288</v>
+      </c>
+      <c r="F45" s="17" t="s">
+        <v>289</v>
+      </c>
+      <c r="G45" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="H45" s="17" t="s">
         <v>291</v>
-      </c>
-      <c r="E45" s="17" t="s">
-        <v>292</v>
-      </c>
-      <c r="F45" s="17" t="s">
-        <v>293</v>
-      </c>
-      <c r="G45" s="17" t="s">
-        <v>294</v>
-      </c>
-      <c r="H45" s="17" t="s">
-        <v>295</v>
       </c>
       <c r="I45" s="17" t="s">
         <v>8</v>
@@ -4523,7 +4541,7 @@
     </row>
     <row r="46" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A46" s="17" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B46" s="17">
         <v>1</v>
@@ -4532,19 +4550,19 @@
         <v>59</v>
       </c>
       <c r="D46" s="17" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="E46" s="17" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="F46" s="17" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="G46" s="17" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="H46" s="17" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="I46" s="17" t="s">
         <v>8</v>
@@ -4561,7 +4579,7 @@
     </row>
     <row r="47" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A47" s="17" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B47" s="17">
         <v>1</v>
@@ -4570,19 +4588,19 @@
         <v>59</v>
       </c>
       <c r="D47" s="17" t="s">
+        <v>297</v>
+      </c>
+      <c r="E47" s="17" t="s">
+        <v>298</v>
+      </c>
+      <c r="F47" s="17" t="s">
+        <v>299</v>
+      </c>
+      <c r="G47" s="17" t="s">
+        <v>300</v>
+      </c>
+      <c r="H47" s="17" t="s">
         <v>301</v>
-      </c>
-      <c r="E47" s="17" t="s">
-        <v>302</v>
-      </c>
-      <c r="F47" s="17" t="s">
-        <v>303</v>
-      </c>
-      <c r="G47" s="17" t="s">
-        <v>304</v>
-      </c>
-      <c r="H47" s="17" t="s">
-        <v>305</v>
       </c>
       <c r="I47" s="17" t="s">
         <v>8</v>
@@ -4599,7 +4617,7 @@
     </row>
     <row r="48" spans="1:16" ht="87" x14ac:dyDescent="0.35">
       <c r="A48" s="17" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B48" s="17">
         <v>1</v>
@@ -4608,19 +4626,19 @@
         <v>59</v>
       </c>
       <c r="D48" s="17" t="s">
+        <v>303</v>
+      </c>
+      <c r="E48" s="17" t="s">
+        <v>304</v>
+      </c>
+      <c r="F48" s="17" t="s">
+        <v>305</v>
+      </c>
+      <c r="G48" s="17" t="s">
+        <v>306</v>
+      </c>
+      <c r="H48" s="17" t="s">
         <v>307</v>
-      </c>
-      <c r="E48" s="17" t="s">
-        <v>308</v>
-      </c>
-      <c r="F48" s="17" t="s">
-        <v>309</v>
-      </c>
-      <c r="G48" s="17" t="s">
-        <v>310</v>
-      </c>
-      <c r="H48" s="17" t="s">
-        <v>311</v>
       </c>
       <c r="I48" s="17" t="s">
         <v>8</v>
@@ -4637,7 +4655,7 @@
     </row>
     <row r="49" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A49" s="17" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B49" s="17">
         <v>1</v>
@@ -4646,19 +4664,19 @@
         <v>59</v>
       </c>
       <c r="D49" s="17" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="E49" s="17" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="F49" s="17" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="G49" s="17" t="s">
         <v>64</v>
       </c>
       <c r="H49" s="17" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="I49" s="17" t="s">
         <v>8</v>
@@ -4675,7 +4693,7 @@
     </row>
     <row r="50" spans="1:16" ht="87" x14ac:dyDescent="0.35">
       <c r="A50" s="17" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B50" s="17">
         <v>1</v>
@@ -4684,19 +4702,19 @@
         <v>59</v>
       </c>
       <c r="D50" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="E50" s="17" t="s">
+        <v>315</v>
+      </c>
+      <c r="F50" s="17" t="s">
+        <v>316</v>
+      </c>
+      <c r="G50" s="17" t="s">
+        <v>317</v>
+      </c>
+      <c r="H50" s="17" t="s">
         <v>318</v>
-      </c>
-      <c r="E50" s="17" t="s">
-        <v>319</v>
-      </c>
-      <c r="F50" s="17" t="s">
-        <v>320</v>
-      </c>
-      <c r="G50" s="17" t="s">
-        <v>321</v>
-      </c>
-      <c r="H50" s="17" t="s">
-        <v>322</v>
       </c>
       <c r="I50" s="17" t="s">
         <v>8</v>
@@ -4713,7 +4731,7 @@
     </row>
     <row r="51" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A51" s="17" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="B51" s="17">
         <v>1</v>
@@ -4722,16 +4740,16 @@
         <v>59</v>
       </c>
       <c r="D51" s="17" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="E51" s="17" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F51" s="17" t="s">
         <v>64</v>
       </c>
       <c r="G51" s="17" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H51" s="17" t="s">
         <v>62</v>
@@ -4751,7 +4769,7 @@
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A52" s="17" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B52" s="17">
         <v>1</v>
@@ -4760,19 +4778,19 @@
         <v>59</v>
       </c>
       <c r="D52" s="17" t="s">
+        <v>322</v>
+      </c>
+      <c r="E52" s="17" t="s">
+        <v>323</v>
+      </c>
+      <c r="F52" s="17" t="s">
+        <v>324</v>
+      </c>
+      <c r="G52" s="17" t="s">
+        <v>325</v>
+      </c>
+      <c r="H52" s="17" t="s">
         <v>326</v>
-      </c>
-      <c r="E52" s="17" t="s">
-        <v>327</v>
-      </c>
-      <c r="F52" s="17" t="s">
-        <v>328</v>
-      </c>
-      <c r="G52" s="17" t="s">
-        <v>329</v>
-      </c>
-      <c r="H52" s="17" t="s">
-        <v>330</v>
       </c>
       <c r="I52" s="17" t="s">
         <v>9</v>
@@ -4789,7 +4807,7 @@
     </row>
     <row r="53" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A53" s="17" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="B53" s="17">
         <v>1</v>
@@ -4798,19 +4816,19 @@
         <v>59</v>
       </c>
       <c r="D53" s="17" t="s">
+        <v>328</v>
+      </c>
+      <c r="E53" s="17" t="s">
+        <v>329</v>
+      </c>
+      <c r="F53" s="17" t="s">
+        <v>330</v>
+      </c>
+      <c r="G53" s="17" t="s">
+        <v>331</v>
+      </c>
+      <c r="H53" s="17" t="s">
         <v>332</v>
-      </c>
-      <c r="E53" s="17" t="s">
-        <v>333</v>
-      </c>
-      <c r="F53" s="17" t="s">
-        <v>334</v>
-      </c>
-      <c r="G53" s="17" t="s">
-        <v>335</v>
-      </c>
-      <c r="H53" s="17" t="s">
-        <v>336</v>
       </c>
       <c r="I53" s="17" t="s">
         <v>9</v>
@@ -4827,7 +4845,7 @@
     </row>
     <row r="54" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A54" s="17" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="B54" s="17">
         <v>1</v>
@@ -4836,19 +4854,19 @@
         <v>59</v>
       </c>
       <c r="D54" s="17" t="s">
+        <v>334</v>
+      </c>
+      <c r="E54" s="17" t="s">
+        <v>335</v>
+      </c>
+      <c r="F54" s="17" t="s">
+        <v>336</v>
+      </c>
+      <c r="G54" s="17" t="s">
+        <v>337</v>
+      </c>
+      <c r="H54" s="17" t="s">
         <v>338</v>
-      </c>
-      <c r="E54" s="17" t="s">
-        <v>339</v>
-      </c>
-      <c r="F54" s="17" t="s">
-        <v>340</v>
-      </c>
-      <c r="G54" s="17" t="s">
-        <v>341</v>
-      </c>
-      <c r="H54" s="17" t="s">
-        <v>342</v>
       </c>
       <c r="I54" s="17" t="s">
         <v>8</v>
@@ -4865,7 +4883,7 @@
     </row>
     <row r="55" spans="1:16" ht="58" x14ac:dyDescent="0.35">
       <c r="A55" s="17" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="B55" s="17">
         <v>1</v>
@@ -4874,19 +4892,19 @@
         <v>59</v>
       </c>
       <c r="D55" s="17" t="s">
+        <v>340</v>
+      </c>
+      <c r="E55" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="F55" s="17" t="s">
+        <v>342</v>
+      </c>
+      <c r="G55" s="17" t="s">
+        <v>343</v>
+      </c>
+      <c r="H55" s="17" t="s">
         <v>344</v>
-      </c>
-      <c r="E55" s="17" t="s">
-        <v>345</v>
-      </c>
-      <c r="F55" s="17" t="s">
-        <v>346</v>
-      </c>
-      <c r="G55" s="17" t="s">
-        <v>347</v>
-      </c>
-      <c r="H55" s="17" t="s">
-        <v>348</v>
       </c>
       <c r="I55" s="17" t="s">
         <v>8</v>
@@ -4903,7 +4921,7 @@
     </row>
     <row r="56" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A56" s="17" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="B56" s="17">
         <v>1</v>
@@ -4912,19 +4930,19 @@
         <v>59</v>
       </c>
       <c r="D56" s="17" t="s">
+        <v>346</v>
+      </c>
+      <c r="E56" s="17" t="s">
+        <v>347</v>
+      </c>
+      <c r="F56" s="17" t="s">
+        <v>348</v>
+      </c>
+      <c r="G56" s="17" t="s">
+        <v>349</v>
+      </c>
+      <c r="H56" s="17" t="s">
         <v>350</v>
-      </c>
-      <c r="E56" s="17" t="s">
-        <v>351</v>
-      </c>
-      <c r="F56" s="17" t="s">
-        <v>352</v>
-      </c>
-      <c r="G56" s="17" t="s">
-        <v>353</v>
-      </c>
-      <c r="H56" s="17" t="s">
-        <v>354</v>
       </c>
       <c r="I56" s="17" t="s">
         <v>9</v>
@@ -4941,7 +4959,7 @@
     </row>
     <row r="57" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A57" s="17" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="B57" s="17">
         <v>1</v>
@@ -4950,19 +4968,19 @@
         <v>59</v>
       </c>
       <c r="D57" s="17" t="s">
+        <v>352</v>
+      </c>
+      <c r="E57" s="17" t="s">
+        <v>353</v>
+      </c>
+      <c r="F57" s="17" t="s">
+        <v>354</v>
+      </c>
+      <c r="G57" s="17" t="s">
+        <v>355</v>
+      </c>
+      <c r="H57" s="17" t="s">
         <v>356</v>
-      </c>
-      <c r="E57" s="17" t="s">
-        <v>357</v>
-      </c>
-      <c r="F57" s="17" t="s">
-        <v>358</v>
-      </c>
-      <c r="G57" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="H57" s="17" t="s">
-        <v>360</v>
       </c>
       <c r="I57" s="17" t="s">
         <v>9</v>
@@ -4979,7 +4997,7 @@
     </row>
     <row r="58" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A58" s="17" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="B58" s="17">
         <v>1</v>
@@ -4988,19 +5006,19 @@
         <v>59</v>
       </c>
       <c r="D58" s="17" t="s">
+        <v>358</v>
+      </c>
+      <c r="E58" s="17" t="s">
+        <v>359</v>
+      </c>
+      <c r="F58" s="17" t="s">
+        <v>360</v>
+      </c>
+      <c r="G58" s="17" t="s">
+        <v>361</v>
+      </c>
+      <c r="H58" s="17" t="s">
         <v>362</v>
-      </c>
-      <c r="E58" s="17" t="s">
-        <v>363</v>
-      </c>
-      <c r="F58" s="17" t="s">
-        <v>364</v>
-      </c>
-      <c r="G58" s="17" t="s">
-        <v>365</v>
-      </c>
-      <c r="H58" s="17" t="s">
-        <v>366</v>
       </c>
       <c r="I58" s="17" t="s">
         <v>9</v>
@@ -5017,7 +5035,7 @@
     </row>
     <row r="59" spans="1:16" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A59" s="17" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="B59" s="17">
         <v>1</v>
@@ -5026,19 +5044,19 @@
         <v>59</v>
       </c>
       <c r="D59" s="17" t="s">
+        <v>364</v>
+      </c>
+      <c r="E59" s="17" t="s">
+        <v>365</v>
+      </c>
+      <c r="F59" s="17" t="s">
+        <v>366</v>
+      </c>
+      <c r="G59" s="17" t="s">
+        <v>367</v>
+      </c>
+      <c r="H59" s="17" t="s">
         <v>368</v>
-      </c>
-      <c r="E59" s="17" t="s">
-        <v>369</v>
-      </c>
-      <c r="F59" s="17" t="s">
-        <v>370</v>
-      </c>
-      <c r="G59" s="17" t="s">
-        <v>371</v>
-      </c>
-      <c r="H59" s="17" t="s">
-        <v>372</v>
       </c>
       <c r="I59" s="17" t="s">
         <v>9</v>
@@ -5055,7 +5073,7 @@
     </row>
     <row r="60" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A60" s="17" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="B60" s="17">
         <v>1</v>
@@ -5064,19 +5082,19 @@
         <v>59</v>
       </c>
       <c r="D60" s="17" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="E60" s="17" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="F60" s="17" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="G60" s="17" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="H60" s="17" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="I60" s="17" t="s">
         <v>9</v>
@@ -5093,7 +5111,7 @@
     </row>
     <row r="61" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A61" s="17" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="B61" s="17">
         <v>1</v>
@@ -5102,10 +5120,10 @@
         <v>59</v>
       </c>
       <c r="D61" s="17" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="E61" s="17" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F61" s="17" t="s">
         <v>62</v>
@@ -5114,7 +5132,7 @@
         <v>61</v>
       </c>
       <c r="H61" s="17" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I61" s="17" t="s">
         <v>9</v>
@@ -5131,31 +5149,31 @@
     </row>
     <row r="62" spans="1:16" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A62" s="17" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="B62" s="17">
         <v>2</v>
       </c>
       <c r="C62" s="17" t="s">
+        <v>377</v>
+      </c>
+      <c r="D62" s="17" t="s">
+        <v>378</v>
+      </c>
+      <c r="E62" s="17" t="s">
+        <v>379</v>
+      </c>
+      <c r="F62" s="17" t="s">
+        <v>380</v>
+      </c>
+      <c r="G62" s="17" t="s">
         <v>381</v>
       </c>
-      <c r="D62" s="17" t="s">
+      <c r="H62" s="17" t="s">
         <v>382</v>
       </c>
-      <c r="E62" s="17" t="s">
+      <c r="I62" s="17" t="s">
         <v>383</v>
-      </c>
-      <c r="F62" s="17" t="s">
-        <v>384</v>
-      </c>
-      <c r="G62" s="17" t="s">
-        <v>385</v>
-      </c>
-      <c r="H62" s="17" t="s">
-        <v>386</v>
-      </c>
-      <c r="I62" s="17" t="s">
-        <v>387</v>
       </c>
       <c r="J62" s="17">
         <v>1</v>
@@ -5169,31 +5187,31 @@
     </row>
     <row r="63" spans="1:16" ht="87" x14ac:dyDescent="0.35">
       <c r="A63" s="17" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="B63" s="17">
         <v>2</v>
       </c>
       <c r="C63" s="17" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="D63" s="17" t="s">
+        <v>385</v>
+      </c>
+      <c r="E63" s="17" t="s">
+        <v>386</v>
+      </c>
+      <c r="F63" s="17" t="s">
+        <v>387</v>
+      </c>
+      <c r="G63" s="17" t="s">
+        <v>388</v>
+      </c>
+      <c r="H63" s="17" t="s">
         <v>389</v>
       </c>
-      <c r="E63" s="17" t="s">
-        <v>390</v>
-      </c>
-      <c r="F63" s="17" t="s">
-        <v>391</v>
-      </c>
-      <c r="G63" s="17" t="s">
-        <v>392</v>
-      </c>
-      <c r="H63" s="17" t="s">
-        <v>393</v>
-      </c>
       <c r="I63" s="17" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="J63" s="17">
         <v>1</v>
@@ -5207,31 +5225,31 @@
     </row>
     <row r="64" spans="1:16" ht="116" x14ac:dyDescent="0.35">
       <c r="A64" s="17" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="B64" s="17">
         <v>2</v>
       </c>
       <c r="C64" s="17" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="D64" s="17" t="s">
+        <v>391</v>
+      </c>
+      <c r="E64" s="17" t="s">
+        <v>392</v>
+      </c>
+      <c r="F64" s="17" t="s">
+        <v>393</v>
+      </c>
+      <c r="G64" s="17" t="s">
+        <v>394</v>
+      </c>
+      <c r="H64" s="17" t="s">
         <v>395</v>
       </c>
-      <c r="E64" s="17" t="s">
-        <v>396</v>
-      </c>
-      <c r="F64" s="17" t="s">
-        <v>397</v>
-      </c>
-      <c r="G64" s="17" t="s">
-        <v>398</v>
-      </c>
-      <c r="H64" s="17" t="s">
-        <v>399</v>
-      </c>
       <c r="I64" s="17" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="J64" s="17">
         <v>1</v>
@@ -5245,31 +5263,31 @@
     </row>
     <row r="65" spans="1:16" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A65" s="17" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="B65" s="17">
         <v>2</v>
       </c>
       <c r="C65" s="17" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="D65" s="17" t="s">
+        <v>397</v>
+      </c>
+      <c r="E65" s="17" t="s">
+        <v>398</v>
+      </c>
+      <c r="F65" s="17" t="s">
+        <v>399</v>
+      </c>
+      <c r="G65" s="17" t="s">
+        <v>400</v>
+      </c>
+      <c r="H65" s="17" t="s">
         <v>401</v>
       </c>
-      <c r="E65" s="17" t="s">
-        <v>402</v>
-      </c>
-      <c r="F65" s="17" t="s">
-        <v>403</v>
-      </c>
-      <c r="G65" s="17" t="s">
-        <v>404</v>
-      </c>
-      <c r="H65" s="17" t="s">
-        <v>405</v>
-      </c>
       <c r="I65" s="17" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="J65" s="17">
         <v>1</v>
@@ -5283,31 +5301,31 @@
     </row>
     <row r="66" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A66" s="17" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="B66" s="17">
         <v>2</v>
       </c>
       <c r="C66" s="17" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="D66" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="E66" s="17" t="s">
+        <v>404</v>
+      </c>
+      <c r="F66" s="17" t="s">
+        <v>405</v>
+      </c>
+      <c r="G66" s="17" t="s">
+        <v>406</v>
+      </c>
+      <c r="H66" s="17" t="s">
         <v>407</v>
       </c>
-      <c r="E66" s="17" t="s">
-        <v>408</v>
-      </c>
-      <c r="F66" s="17" t="s">
-        <v>409</v>
-      </c>
-      <c r="G66" s="17" t="s">
-        <v>410</v>
-      </c>
-      <c r="H66" s="17" t="s">
-        <v>411</v>
-      </c>
       <c r="I66" s="17" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="J66" s="17">
         <v>1</v>
@@ -5321,31 +5339,31 @@
     </row>
     <row r="67" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A67" s="17" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="B67" s="17">
         <v>2</v>
       </c>
       <c r="C67" s="17" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="D67" s="17" t="s">
+        <v>409</v>
+      </c>
+      <c r="E67" s="17" t="s">
+        <v>410</v>
+      </c>
+      <c r="F67" s="17" t="s">
+        <v>411</v>
+      </c>
+      <c r="G67" s="17" t="s">
+        <v>412</v>
+      </c>
+      <c r="H67" s="17" t="s">
         <v>413</v>
       </c>
-      <c r="E67" s="17" t="s">
-        <v>414</v>
-      </c>
-      <c r="F67" s="17" t="s">
-        <v>415</v>
-      </c>
-      <c r="G67" s="17" t="s">
-        <v>416</v>
-      </c>
-      <c r="H67" s="17" t="s">
-        <v>417</v>
-      </c>
       <c r="I67" s="17" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="J67" s="17">
         <v>1</v>
@@ -5359,31 +5377,31 @@
     </row>
     <row r="68" spans="1:16" ht="87" x14ac:dyDescent="0.35">
       <c r="A68" s="17" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="B68" s="17">
         <v>2</v>
       </c>
       <c r="C68" s="17" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="D68" s="17" t="s">
+        <v>415</v>
+      </c>
+      <c r="E68" s="17" t="s">
+        <v>416</v>
+      </c>
+      <c r="F68" s="17" t="s">
+        <v>417</v>
+      </c>
+      <c r="G68" s="17" t="s">
+        <v>418</v>
+      </c>
+      <c r="H68" s="17" t="s">
         <v>419</v>
       </c>
-      <c r="E68" s="17" t="s">
-        <v>420</v>
-      </c>
-      <c r="F68" s="17" t="s">
-        <v>421</v>
-      </c>
-      <c r="G68" s="17" t="s">
-        <v>422</v>
-      </c>
-      <c r="H68" s="17" t="s">
-        <v>423</v>
-      </c>
       <c r="I68" s="17" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="J68" s="17">
         <v>1</v>
@@ -5397,31 +5415,31 @@
     </row>
     <row r="69" spans="1:16" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A69" s="17" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="B69" s="17">
         <v>2</v>
       </c>
       <c r="C69" s="17" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="D69" s="17" t="s">
+        <v>421</v>
+      </c>
+      <c r="E69" s="17" t="s">
+        <v>422</v>
+      </c>
+      <c r="F69" s="17" t="s">
+        <v>423</v>
+      </c>
+      <c r="G69" s="17" t="s">
+        <v>424</v>
+      </c>
+      <c r="H69" s="17" t="s">
         <v>425</v>
       </c>
-      <c r="E69" s="17" t="s">
-        <v>426</v>
-      </c>
-      <c r="F69" s="17" t="s">
-        <v>427</v>
-      </c>
-      <c r="G69" s="17" t="s">
-        <v>428</v>
-      </c>
-      <c r="H69" s="17" t="s">
-        <v>429</v>
-      </c>
       <c r="I69" s="17" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="J69" s="17">
         <v>1</v>
@@ -5435,31 +5453,31 @@
     </row>
     <row r="70" spans="1:16" ht="87" x14ac:dyDescent="0.35">
       <c r="A70" s="17" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="B70" s="17">
         <v>2</v>
       </c>
       <c r="C70" s="17" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="D70" s="17" t="s">
+        <v>427</v>
+      </c>
+      <c r="E70" s="17" t="s">
+        <v>428</v>
+      </c>
+      <c r="F70" s="17" t="s">
+        <v>429</v>
+      </c>
+      <c r="G70" s="17" t="s">
+        <v>430</v>
+      </c>
+      <c r="H70" s="17" t="s">
         <v>431</v>
       </c>
-      <c r="E70" s="17" t="s">
-        <v>432</v>
-      </c>
-      <c r="F70" s="17" t="s">
-        <v>433</v>
-      </c>
-      <c r="G70" s="17" t="s">
-        <v>434</v>
-      </c>
-      <c r="H70" s="17" t="s">
-        <v>435</v>
-      </c>
       <c r="I70" s="17" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="J70" s="17">
         <v>1</v>
@@ -5473,31 +5491,31 @@
     </row>
     <row r="71" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A71" s="17" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="B71" s="17">
         <v>2</v>
       </c>
       <c r="C71" s="17" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="D71" s="17" t="s">
+        <v>433</v>
+      </c>
+      <c r="E71" s="17" t="s">
+        <v>434</v>
+      </c>
+      <c r="F71" s="17" t="s">
+        <v>435</v>
+      </c>
+      <c r="G71" s="17" t="s">
+        <v>436</v>
+      </c>
+      <c r="H71" s="17" t="s">
         <v>437</v>
       </c>
-      <c r="E71" s="17" t="s">
-        <v>438</v>
-      </c>
-      <c r="F71" s="17" t="s">
-        <v>439</v>
-      </c>
-      <c r="G71" s="17" t="s">
-        <v>440</v>
-      </c>
-      <c r="H71" s="17" t="s">
-        <v>441</v>
-      </c>
       <c r="I71" s="17" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="J71" s="17">
         <v>1</v>
@@ -5511,23 +5529,23 @@
     </row>
     <row r="72" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A72" s="17" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="B72" s="17">
         <v>3</v>
       </c>
       <c r="C72" s="17" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="D72" s="17" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="E72" s="17"/>
       <c r="F72" s="17"/>
       <c r="G72" s="17"/>
       <c r="H72" s="17"/>
       <c r="I72" s="17" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="J72" s="17">
         <v>0.5</v>
@@ -5541,23 +5559,23 @@
     </row>
     <row r="73" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A73" s="17" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="B73" s="17">
         <v>3</v>
       </c>
       <c r="C73" s="17" t="s">
+        <v>439</v>
+      </c>
+      <c r="D73" s="17" t="s">
         <v>443</v>
-      </c>
-      <c r="D73" s="17" t="s">
-        <v>447</v>
       </c>
       <c r="E73" s="17"/>
       <c r="F73" s="17"/>
       <c r="G73" s="17"/>
       <c r="H73" s="17"/>
       <c r="I73" s="17" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="J73" s="17">
         <v>0.5</v>
@@ -5571,23 +5589,23 @@
     </row>
     <row r="74" spans="1:16" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A74" s="17" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="B74" s="17">
         <v>3</v>
       </c>
       <c r="C74" s="17" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="D74" s="17" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="E74" s="17"/>
       <c r="F74" s="17"/>
       <c r="G74" s="17"/>
       <c r="H74" s="17"/>
       <c r="I74" s="17" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="J74" s="17">
         <v>0.5</v>
@@ -5601,23 +5619,23 @@
     </row>
     <row r="75" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A75" s="17" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="B75" s="17">
         <v>3</v>
       </c>
       <c r="C75" s="17" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="D75" s="17" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="E75" s="17"/>
       <c r="F75" s="17"/>
       <c r="G75" s="17"/>
       <c r="H75" s="17"/>
       <c r="I75" s="17" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="J75" s="17">
         <v>0.5</v>
@@ -5631,23 +5649,23 @@
     </row>
     <row r="76" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A76" s="17" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="B76" s="17">
         <v>3</v>
       </c>
       <c r="C76" s="17" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="D76" s="17" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="E76" s="17"/>
       <c r="F76" s="17"/>
       <c r="G76" s="17"/>
       <c r="H76" s="17"/>
       <c r="I76" s="17" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="J76" s="17">
         <v>0.5</v>
@@ -5661,16 +5679,16 @@
     </row>
     <row r="77" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A77" s="17" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B77" s="17">
         <v>3</v>
       </c>
       <c r="C77" s="17" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="D77" s="17" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="E77" s="17"/>
       <c r="F77" s="17"/>
@@ -5691,23 +5709,23 @@
     </row>
     <row r="78" spans="1:16" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A78" s="17" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B78" s="17">
         <v>3</v>
       </c>
       <c r="C78" s="17" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="D78" s="17" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="E78" s="17"/>
       <c r="F78" s="17"/>
       <c r="G78" s="17"/>
       <c r="H78" s="17"/>
       <c r="I78" s="17" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="J78" s="17">
         <v>0.5</v>
@@ -5721,23 +5739,23 @@
     </row>
     <row r="79" spans="1:16" ht="58" x14ac:dyDescent="0.35">
       <c r="A79" s="17" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="B79" s="17">
         <v>3</v>
       </c>
       <c r="C79" s="17" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="D79" s="17" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="E79" s="17"/>
       <c r="F79" s="17"/>
       <c r="G79" s="17"/>
       <c r="H79" s="17"/>
       <c r="I79" s="17" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="J79" s="17">
         <v>0.5</v>
@@ -5751,23 +5769,23 @@
     </row>
     <row r="80" spans="1:16" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A80" s="17" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="B80" s="17">
         <v>3</v>
       </c>
       <c r="C80" s="17" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="D80" s="17" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="E80" s="17"/>
       <c r="F80" s="17"/>
       <c r="G80" s="17"/>
       <c r="H80" s="17"/>
       <c r="I80" s="17" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="J80" s="17">
         <v>0.5</v>
@@ -5781,16 +5799,16 @@
     </row>
     <row r="81" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A81" s="17" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="B81" s="17">
         <v>3</v>
       </c>
       <c r="C81" s="17" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="D81" s="17" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="E81" s="17"/>
       <c r="F81" s="17"/>
@@ -5810,6 +5828,13 @@
       <c r="P81" s="17"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="K19" r:id="rId1" xr:uid="{202E5181-2A3D-4109-BC35-9D36400D5734}"/>
+    <hyperlink ref="K16" r:id="rId2" xr:uid="{9F3847AE-80E6-4D65-B7C4-88DEC7F24D8E}"/>
+    <hyperlink ref="K2" r:id="rId3" xr:uid="{31D7AE3F-8DA7-410E-B193-15D2C61D0C1A}"/>
+    <hyperlink ref="L4" r:id="rId4" xr:uid="{989F5613-D7AF-4C67-B557-A25BC5C098E6}"/>
+    <hyperlink ref="N2" r:id="rId5" xr:uid="{E5A2A950-3048-4AB4-A72D-A9A5CCF7CD37}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5832,1608 +5857,1608 @@
         <v>4</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="C2" s="5"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="C3" s="5"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="C4" s="5"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>470</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>474</v>
       </c>
       <c r="C5" s="5"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="C6" s="5"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="C7" s="5"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="C8" s="5"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="C9" s="5"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="C10" s="5"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="C11" s="5"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="C12" s="5"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="C13" s="5"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="C14" s="5"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="C15" s="5"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="C16" s="5"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="C17" s="5"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="C18" s="5"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="C19" s="5"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="C20" s="5"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="C21" s="5"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="C22" s="5"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="C23" s="5"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="C24" s="5"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="C25" s="5"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="C26" s="5"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="C27" s="5"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C28" s="5"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="C29" s="5"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="C30" s="5"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="5" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="C31" s="5"/>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="C32" s="5"/>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="5" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="C33" s="5"/>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="5" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="C34" s="5"/>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" s="5" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="C35" s="5"/>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="C36" s="5"/>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" s="5" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="C37" s="5"/>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="5" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="C38" s="5"/>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" s="5" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="C39" s="5"/>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" s="5" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="C40" s="5"/>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" s="5" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="C41" s="5"/>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" s="5" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="C42" s="5"/>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" s="5" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="C43" s="5"/>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" s="5" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="C44" s="5"/>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" s="5" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="C45" s="5"/>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" s="5" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="C46" s="5"/>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" s="5" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="C47" s="5"/>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" s="5" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="C48" s="5"/>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" s="5" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="C49" s="5"/>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" s="5" t="s">
+        <v>512</v>
+      </c>
+      <c r="B50" s="5" t="s">
         <v>516</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>520</v>
       </c>
       <c r="C50" s="5"/>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" s="5" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="C51" s="5"/>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" s="5" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="C52" s="5"/>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" s="5" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="C53" s="5"/>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" s="5" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="C54" s="5"/>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" s="5" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="C55" s="5"/>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" s="5" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="C56" s="5"/>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" s="5" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="C57" s="5"/>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" s="5" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="C58" s="5"/>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" s="5" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="C59" s="5"/>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" s="5" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="C60" s="5"/>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" s="5" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="C61" s="5"/>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" s="5" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="C62" s="5"/>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" s="5" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="C63" s="5"/>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" s="5" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="C64" s="5"/>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" s="5" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="C65" s="5"/>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" s="5" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="C66" s="5"/>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" s="5" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="C67" s="5"/>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" s="5" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="C68" s="5"/>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" s="5" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="C69" s="5"/>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" s="5" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="C70" s="5"/>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" s="5" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="C71" s="5"/>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" s="5" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="C72" s="5"/>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" s="5" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="C73" s="5"/>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" s="5" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="C74" s="5"/>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" s="5" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="C75" s="5"/>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" s="5" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="C76" s="5"/>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" s="5" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="C77" s="5"/>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" s="5" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="C78" s="5"/>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" s="5" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="C79" s="5"/>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" s="5" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="C80" s="5"/>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" s="5" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="C81" s="5"/>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" s="5" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C82" s="5"/>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" s="5" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="C83" s="5"/>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" s="5" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="C84" s="5"/>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" s="5" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="C85" s="5"/>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" s="5" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="C86" s="5"/>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" s="5" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="C87" s="5"/>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" s="5" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="C88" s="5"/>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" s="5" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="C89" s="5"/>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" s="5" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="C90" s="5"/>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" s="5" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="C91" s="5"/>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" s="5" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="C92" s="5"/>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" s="5" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="C93" s="5"/>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" s="5" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="C94" s="5"/>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" s="5" t="s">
+        <v>558</v>
+      </c>
+      <c r="B95" s="5" t="s">
         <v>562</v>
-      </c>
-      <c r="B95" s="5" t="s">
-        <v>566</v>
       </c>
       <c r="C95" s="5"/>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" s="5" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="C96" s="5"/>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" s="5" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="C97" s="5"/>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" s="5" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="C98" s="5"/>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" s="5" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="C99" s="5"/>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" s="5" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="C100" s="5"/>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" s="5" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="C101" s="5"/>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" s="5" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="C102" s="5"/>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" s="5" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="C103" s="5"/>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" s="5" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="C104" s="5"/>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" s="5" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="C105" s="5"/>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" s="5" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="C106" s="5"/>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" s="5" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="C107" s="5"/>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" s="5" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="C108" s="5"/>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" s="5" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="C109" s="5"/>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" s="5" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="C110" s="5"/>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" s="5" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="C111" s="5"/>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" s="5" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="C112" s="5"/>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" s="5" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="C113" s="5"/>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" s="5" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="C114" s="5"/>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" s="5" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="C115" s="5"/>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" s="5" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="C116" s="5"/>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" s="5" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="C117" s="5"/>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" s="5" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="C118" s="5"/>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" s="5" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="C119" s="5"/>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" s="5" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="C120" s="5"/>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" s="5" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="C121" s="5"/>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122" s="5" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="C122" s="5"/>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" s="5" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="C123" s="5"/>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" s="5" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="C124" s="5"/>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" s="5" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="C125" s="5"/>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" s="5" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="C126" s="5"/>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127" s="5" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="C127" s="5"/>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" s="5" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="C128" s="5"/>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" s="5" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="C129" s="5"/>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" s="5" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="C130" s="5"/>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" s="5" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="C131" s="5"/>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" s="5" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="C132" s="5"/>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" s="5" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="C133" s="5"/>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" s="5" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="C134" s="5"/>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" s="5" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="C135" s="5"/>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" s="5" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="C136" s="5"/>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" s="5" t="s">
+        <v>601</v>
+      </c>
+      <c r="B137" s="5" t="s">
         <v>605</v>
-      </c>
-      <c r="B137" s="5" t="s">
-        <v>609</v>
       </c>
       <c r="C137" s="5"/>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" s="5" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="C138" s="5"/>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" s="5" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="C139" s="5"/>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" s="5" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="C140" s="5"/>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" s="5" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="C141" s="5"/>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" s="5" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="C142" s="5"/>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143" s="5" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="C143" s="5"/>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A144" s="5" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="C144" s="5"/>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A145" s="5" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="C145" s="5"/>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146" s="5" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="C146" s="5"/>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A147" s="5" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="C147" s="5"/>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A148" s="5" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="C148" s="5"/>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A149" s="5" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="C149" s="5"/>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A150" s="5" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="C150" s="5"/>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A151" s="5" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="C151" s="5"/>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A152" s="5" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="C152" s="5"/>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A153" s="5" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="C153" s="5"/>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A154" s="5" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="C154" s="5"/>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A155" s="5" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="C155" s="5"/>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A156" s="5" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="C156" s="5"/>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A157" s="5" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="C157" s="5"/>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A158" s="5" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="C158" s="5"/>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A159" s="5" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="C159" s="5"/>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A160" s="5" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="C160" s="5"/>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A161" s="5" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="C161" s="5"/>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A162" s="5" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="C162" s="5"/>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A163" s="5" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="C163" s="5"/>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A164" s="5" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="C164" s="5"/>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A165" s="5" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="C165" s="5"/>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A166" s="5" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="C166" s="5"/>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A167" s="5" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="C167" s="5"/>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A168" s="5" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="C168" s="5"/>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A169" s="5" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="C169" s="5"/>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A170" s="5" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="C170" s="5"/>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A171" s="5" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="C171" s="5"/>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A172" s="5" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="C172" s="5"/>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A173" s="5" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="C173" s="5"/>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A174" s="5" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="C174" s="5"/>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A175" s="5" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="C175" s="5"/>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A176" s="5" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="C176" s="5"/>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A177" s="5" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="C177" s="5"/>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A178" s="5" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="C178" s="5"/>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A179" s="5" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="C179" s="5"/>
     </row>
@@ -7459,76 +7484,76 @@
         <v>3</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="C2" s="11"/>
       <c r="D2" s="11"/>
       <c r="E2" s="11" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="11" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="C3" s="11"/>
       <c r="D3" s="11"/>
       <c r="E3" s="11" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="12" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C4" s="12"/>
       <c r="D4" s="12"/>
       <c r="E4" s="12" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="12" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C5" s="12"/>
       <c r="D5" s="12"/>
       <c r="E5" s="12" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="C7" s="20"/>
       <c r="D7" s="20"/>
@@ -7560,43 +7585,43 @@
         <v>3</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>14</v>
       </c>
       <c r="D1" s="6" t="s">
+        <v>657</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>658</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>659</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>660</v>
+      </c>
+      <c r="H1" s="6" t="s">
         <v>661</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="I1" s="6" t="s">
         <v>662</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>663</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>664</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>665</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>666</v>
       </c>
       <c r="J1" s="6" t="s">
         <v>2</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
@@ -7607,7 +7632,7 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="19" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="B3" s="20"/>
       <c r="C3" s="20"/>
@@ -7653,27 +7678,27 @@
         <v>3</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="G1" s="8" t="s">
         <v>14</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="19" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -7718,33 +7743,33 @@
         <v>4</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="19" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -7881,21 +7906,21 @@
         <v>4</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="19" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>

--- a/data/KTTX_TIN12.xlsx
+++ b/data/KTTX_TIN12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tdtam\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F20214C-AE8E-4B72-974B-B64ECBE9985C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{152CB866-2808-4661-B98E-F17A409B4F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="682">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1105" uniqueCount="685">
   <si>
     <t>QID</t>
   </si>
@@ -2076,13 +2076,22 @@
     <t xml:space="preserve">https://webh2t.github.io/assets/tin12/DNS.png </t>
   </si>
   <si>
-    <t xml:space="preserve">https://github.com/webh2t/webh2t.github.io/blob/main/assets/tin12/ipv4.jpg </t>
-  </si>
-  <si>
     <t xml:space="preserve">https://webh2t.github.io/assets/tin12/Ethernet.jpg </t>
   </si>
   <si>
     <t xml:space="preserve">https://www.youtube.com/watch?v=PpsEaqJV_A0 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://webh2t.github.io/assets/tin12/DNS.png  </t>
+  </si>
+  <si>
+    <t>https://webh2t.github.io/assets/tin12/ipv4.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://webh2t.github.io/assets/tin12/ipv4.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/webh2t/assets/tin12/tcp.jpg </t>
   </si>
 </sst>
 </file>
@@ -2291,15 +2300,15 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2614,7 +2623,7 @@
       <c r="A1" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="20"/>
+      <c r="B1" s="22"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
@@ -2888,12 +2897,12 @@
       <c r="J2" s="17">
         <v>0.25</v>
       </c>
-      <c r="K2" s="23" t="s">
-        <v>680</v>
+      <c r="K2" s="20" t="s">
+        <v>679</v>
       </c>
       <c r="L2" s="17"/>
       <c r="M2" s="18"/>
-      <c r="N2" s="22" t="s">
+      <c r="N2" s="19" t="s">
         <v>678</v>
       </c>
       <c r="O2" s="17"/>
@@ -2969,8 +2978,8 @@
         <v>0.25</v>
       </c>
       <c r="K4" s="17"/>
-      <c r="L4" s="23" t="s">
-        <v>681</v>
+      <c r="L4" s="20" t="s">
+        <v>680</v>
       </c>
       <c r="M4" s="17"/>
       <c r="N4" s="17"/>
@@ -3046,7 +3055,9 @@
       <c r="J6" s="17">
         <v>0.25</v>
       </c>
-      <c r="K6" s="17"/>
+      <c r="K6" s="19" t="s">
+        <v>684</v>
+      </c>
       <c r="L6" s="17"/>
       <c r="M6" s="17"/>
       <c r="N6" s="17"/>
@@ -3426,8 +3437,8 @@
       <c r="J16" s="17">
         <v>0.25</v>
       </c>
-      <c r="K16" s="22" t="s">
-        <v>679</v>
+      <c r="K16" s="19" t="s">
+        <v>682</v>
       </c>
       <c r="L16" s="17"/>
       <c r="M16" s="17"/>
@@ -3473,7 +3484,7 @@
       <c r="O17" s="17"/>
       <c r="P17" s="17"/>
     </row>
-    <row r="18" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:16" ht="58" x14ac:dyDescent="0.35">
       <c r="A18" s="17" t="s">
         <v>143</v>
       </c>
@@ -3504,7 +3515,9 @@
       <c r="J18" s="17">
         <v>0.25</v>
       </c>
-      <c r="K18" s="17"/>
+      <c r="K18" s="17" t="s">
+        <v>684</v>
+      </c>
       <c r="L18" s="17"/>
       <c r="M18" s="17"/>
       <c r="N18" s="17"/>
@@ -3542,7 +3555,7 @@
       <c r="J19" s="17">
         <v>0.25</v>
       </c>
-      <c r="K19" s="22" t="s">
+      <c r="K19" s="19" t="s">
         <v>678</v>
       </c>
       <c r="L19" s="17"/>
@@ -3848,7 +3861,9 @@
       <c r="J27" s="17">
         <v>0.25</v>
       </c>
-      <c r="K27" s="17"/>
+      <c r="K27" s="17" t="s">
+        <v>684</v>
+      </c>
       <c r="L27" s="17"/>
       <c r="M27" s="17"/>
       <c r="N27" s="17"/>
@@ -4000,7 +4015,9 @@
       <c r="J31" s="17">
         <v>0.25</v>
       </c>
-      <c r="K31" s="17"/>
+      <c r="K31" s="19" t="s">
+        <v>681</v>
+      </c>
       <c r="L31" s="17"/>
       <c r="M31" s="17"/>
       <c r="N31" s="17"/>
@@ -4456,7 +4473,7 @@
       <c r="J43" s="17">
         <v>0.25</v>
       </c>
-      <c r="K43" s="17"/>
+      <c r="K43" s="19"/>
       <c r="L43" s="17"/>
       <c r="M43" s="17"/>
       <c r="N43" s="17"/>
@@ -4767,7 +4784,7 @@
       <c r="O51" s="17"/>
       <c r="P51" s="17"/>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A52" s="17" t="s">
         <v>321</v>
       </c>
@@ -4798,7 +4815,9 @@
       <c r="J52" s="17">
         <v>0.25</v>
       </c>
-      <c r="K52" s="17"/>
+      <c r="K52" s="19" t="s">
+        <v>683</v>
+      </c>
       <c r="L52" s="17"/>
       <c r="M52" s="17"/>
       <c r="N52" s="17"/>
@@ -5830,10 +5849,13 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="K19" r:id="rId1" xr:uid="{202E5181-2A3D-4109-BC35-9D36400D5734}"/>
-    <hyperlink ref="K16" r:id="rId2" xr:uid="{9F3847AE-80E6-4D65-B7C4-88DEC7F24D8E}"/>
-    <hyperlink ref="K2" r:id="rId3" xr:uid="{31D7AE3F-8DA7-410E-B193-15D2C61D0C1A}"/>
-    <hyperlink ref="L4" r:id="rId4" xr:uid="{989F5613-D7AF-4C67-B557-A25BC5C098E6}"/>
-    <hyperlink ref="N2" r:id="rId5" xr:uid="{E5A2A950-3048-4AB4-A72D-A9A5CCF7CD37}"/>
+    <hyperlink ref="K2" r:id="rId2" xr:uid="{31D7AE3F-8DA7-410E-B193-15D2C61D0C1A}"/>
+    <hyperlink ref="L4" r:id="rId3" xr:uid="{989F5613-D7AF-4C67-B557-A25BC5C098E6}"/>
+    <hyperlink ref="N2" r:id="rId4" xr:uid="{E5A2A950-3048-4AB4-A72D-A9A5CCF7CD37}"/>
+    <hyperlink ref="K31" r:id="rId5" xr:uid="{479A808B-1458-4BC5-A66E-04B39265F12A}"/>
+    <hyperlink ref="K16" r:id="rId6" xr:uid="{E7D15EB1-11AD-4726-8C4E-5C5CF7BF3F0D}"/>
+    <hyperlink ref="K52" r:id="rId7" xr:uid="{4FD869F4-DA42-4184-8F60-EA2769774AFD}"/>
+    <hyperlink ref="K6" r:id="rId8" xr:uid="{7B81E776-8E65-464F-B6CE-DFE95029D33B}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7552,11 +7574,11 @@
       <c r="A7" t="s">
         <v>654</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="22" t="s">
         <v>655</v>
       </c>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
@@ -7631,22 +7653,22 @@
       <c r="M2" s="7"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="23" t="s">
         <v>667</v>
       </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
-      <c r="J3" s="20"/>
-      <c r="K3" s="20"/>
-      <c r="L3" s="20"/>
-      <c r="M3" s="20"/>
-      <c r="N3" s="20"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+      <c r="J3" s="22"/>
+      <c r="K3" s="22"/>
+      <c r="L3" s="22"/>
+      <c r="M3" s="22"/>
+      <c r="N3" s="22"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N1" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
@@ -7697,16 +7719,16 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="23" t="s">
         <v>671</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H1" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
@@ -7768,19 +7790,19 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="23" t="s">
         <v>673</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K1" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
@@ -7858,24 +7880,24 @@
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
-      <c r="N2" s="20"/>
-      <c r="O2" s="20"/>
-      <c r="P2" s="20"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="22"/>
+      <c r="N2" s="22"/>
+      <c r="O2" s="22"/>
+      <c r="P2" s="22"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:P1" xr:uid="{00000000-0009-0000-0000-000007000000}"/>
@@ -7919,14 +7941,14 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="23" t="s">
         <v>677</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000008000000}"/>

--- a/data/KTTX_TIN12.xlsx
+++ b/data/KTTX_TIN12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tdtam\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{152CB866-2808-4661-B98E-F17A409B4F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{526E733E-6F5C-430D-9A13-AA7578426894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1105" uniqueCount="685">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1105" uniqueCount="686">
   <si>
     <t>QID</t>
   </si>
@@ -2092,6 +2092,9 @@
   </si>
   <si>
     <t xml:space="preserve">https://github.com/webh2t/assets/tin12/tcp.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://webh2t.github.io/assets/tin12/tcp.jpg </t>
   </si>
 </sst>
 </file>
@@ -2902,9 +2905,7 @@
       </c>
       <c r="L2" s="17"/>
       <c r="M2" s="18"/>
-      <c r="N2" s="19" t="s">
-        <v>678</v>
-      </c>
+      <c r="N2" s="19"/>
       <c r="O2" s="17"/>
       <c r="P2" s="17"/>
     </row>
@@ -3056,7 +3057,7 @@
         <v>0.25</v>
       </c>
       <c r="K6" s="19" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="L6" s="17"/>
       <c r="M6" s="17"/>
@@ -3406,7 +3407,7 @@
       <c r="O15" s="17"/>
       <c r="P15" s="17"/>
     </row>
-    <row r="16" spans="1:16" ht="58" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A16" s="17" t="s">
         <v>131</v>
       </c>
@@ -3484,7 +3485,7 @@
       <c r="O17" s="17"/>
       <c r="P17" s="17"/>
     </row>
-    <row r="18" spans="1:16" ht="58" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A18" s="17" t="s">
         <v>143</v>
       </c>
@@ -3785,7 +3786,9 @@
       <c r="J25" s="17">
         <v>0.25</v>
       </c>
-      <c r="K25" s="17"/>
+      <c r="K25" s="17" t="s">
+        <v>685</v>
+      </c>
       <c r="L25" s="17"/>
       <c r="M25" s="17"/>
       <c r="N25" s="17"/>
@@ -3862,7 +3865,7 @@
         <v>0.25</v>
       </c>
       <c r="K27" s="17" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="L27" s="17"/>
       <c r="M27" s="17"/>
@@ -5851,11 +5854,10 @@
     <hyperlink ref="K19" r:id="rId1" xr:uid="{202E5181-2A3D-4109-BC35-9D36400D5734}"/>
     <hyperlink ref="K2" r:id="rId2" xr:uid="{31D7AE3F-8DA7-410E-B193-15D2C61D0C1A}"/>
     <hyperlink ref="L4" r:id="rId3" xr:uid="{989F5613-D7AF-4C67-B557-A25BC5C098E6}"/>
-    <hyperlink ref="N2" r:id="rId4" xr:uid="{E5A2A950-3048-4AB4-A72D-A9A5CCF7CD37}"/>
-    <hyperlink ref="K31" r:id="rId5" xr:uid="{479A808B-1458-4BC5-A66E-04B39265F12A}"/>
-    <hyperlink ref="K16" r:id="rId6" xr:uid="{E7D15EB1-11AD-4726-8C4E-5C5CF7BF3F0D}"/>
-    <hyperlink ref="K52" r:id="rId7" xr:uid="{4FD869F4-DA42-4184-8F60-EA2769774AFD}"/>
-    <hyperlink ref="K6" r:id="rId8" xr:uid="{7B81E776-8E65-464F-B6CE-DFE95029D33B}"/>
+    <hyperlink ref="K31" r:id="rId4" xr:uid="{479A808B-1458-4BC5-A66E-04B39265F12A}"/>
+    <hyperlink ref="K16" r:id="rId5" xr:uid="{E7D15EB1-11AD-4726-8C4E-5C5CF7BF3F0D}"/>
+    <hyperlink ref="K52" r:id="rId6" xr:uid="{4FD869F4-DA42-4184-8F60-EA2769774AFD}"/>
+    <hyperlink ref="K6" r:id="rId7" xr:uid="{7B81E776-8E65-464F-B6CE-DFE95029D33B}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7536,12 +7538,12 @@
         <v>601</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C3" s="11"/>
       <c r="D3" s="11"/>
       <c r="E3" s="11" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
